--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -199,12 +199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$2:$U$2</f>
+              <f>'Data'!$B$2:$V$2</f>
             </numRef>
           </val>
         </ser>
@@ -231,12 +231,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$3:$U$3</f>
+              <f>'Data'!$B$3:$V$3</f>
             </numRef>
           </val>
         </ser>
@@ -263,12 +263,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$4:$U$4</f>
+              <f>'Data'!$B$4:$V$4</f>
             </numRef>
           </val>
         </ser>
@@ -295,12 +295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$5:$U$5</f>
+              <f>'Data'!$B$5:$V$5</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$6:$U$6</f>
+              <f>'Data'!$B$6:$V$6</f>
             </numRef>
           </val>
         </ser>
@@ -359,12 +359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$7:$U$7</f>
+              <f>'Data'!$B$7:$V$7</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$8:$U$8</f>
+              <f>'Data'!$B$8:$V$8</f>
             </numRef>
           </val>
         </ser>
@@ -423,12 +423,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$9:$U$9</f>
+              <f>'Data'!$B$9:$V$9</f>
             </numRef>
           </val>
         </ser>
@@ -455,12 +455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$10:$U$10</f>
+              <f>'Data'!$B$10:$V$10</f>
             </numRef>
           </val>
         </ser>
@@ -487,12 +487,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$11:$U$11</f>
+              <f>'Data'!$B$11:$V$11</f>
             </numRef>
           </val>
         </ser>
@@ -519,12 +519,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$12:$U$12</f>
+              <f>'Data'!$B$12:$V$12</f>
             </numRef>
           </val>
         </ser>
@@ -551,12 +551,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$13:$U$13</f>
+              <f>'Data'!$B$13:$V$13</f>
             </numRef>
           </val>
         </ser>
@@ -583,12 +583,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$U$1</f>
+              <f>'Data'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$14:$U$14</f>
+              <f>'Data'!$B$14:$V$14</f>
             </numRef>
           </val>
         </ser>
@@ -975,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -999,6 +999,7 @@
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="7" customWidth="1" min="20" max="20"/>
     <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1067,6 +1068,9 @@
       <c r="U1" s="1" t="n">
         <v>95</v>
       </c>
+      <c r="V1" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1134,6 +1138,9 @@
       <c r="U2" t="n">
         <v>0.129</v>
       </c>
+      <c r="V2" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1201,6 +1208,9 @@
       <c r="U3" t="n">
         <v>0.106</v>
       </c>
+      <c r="V3" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1268,6 +1278,9 @@
       <c r="U4" t="n">
         <v>0.111</v>
       </c>
+      <c r="V4" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1335,6 +1348,9 @@
       <c r="U5" t="n">
         <v>0.184</v>
       </c>
+      <c r="V5" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1402,6 +1418,9 @@
       <c r="U6" t="n">
         <v>0.015</v>
       </c>
+      <c r="V6" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1469,6 +1488,9 @@
       <c r="U7" t="n">
         <v>0.115</v>
       </c>
+      <c r="V7" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1536,6 +1558,9 @@
       <c r="U8" t="n">
         <v>0.157</v>
       </c>
+      <c r="V8" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1603,6 +1628,9 @@
       <c r="U9" t="n">
         <v>0.018</v>
       </c>
+      <c r="V9" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1670,6 +1698,9 @@
       <c r="U10" t="n">
         <v>0.017</v>
       </c>
+      <c r="V10" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1737,6 +1768,9 @@
       <c r="U11" t="n">
         <v>0.116</v>
       </c>
+      <c r="V11" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1804,6 +1838,9 @@
       <c r="U12" t="n">
         <v>0.01</v>
       </c>
+      <c r="V12" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1871,6 +1908,9 @@
       <c r="U13" t="n">
         <v>0.013</v>
       </c>
+      <c r="V13" t="n">
+        <v>0.038</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1938,6 +1978,9 @@
       <c r="U14" t="n">
         <v>0.042</v>
       </c>
+      <c r="V14" t="n">
+        <v>0.038</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -592,6 +592,70 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="13"/>
+          <order val="13"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="14"/>
+          <order val="14"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$16:$V$16</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -665,7 +729,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -975,7 +1039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1775,68 +1839,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>pca1</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.775</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.725</v>
+        <v>0.799</v>
       </c>
       <c r="E12" t="n">
-        <v>0.671</v>
+        <v>0.784</v>
       </c>
       <c r="F12" t="n">
-        <v>0.613</v>
+        <v>0.759</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.737</v>
       </c>
       <c r="H12" t="n">
-        <v>0.506</v>
+        <v>0.715</v>
       </c>
       <c r="I12" t="n">
-        <v>0.449</v>
+        <v>0.705</v>
       </c>
       <c r="J12" t="n">
-        <v>0.38</v>
+        <v>0.679</v>
       </c>
       <c r="K12" t="n">
-        <v>0.303</v>
+        <v>0.652</v>
       </c>
       <c r="L12" t="n">
-        <v>0.234</v>
+        <v>0.617</v>
       </c>
       <c r="M12" t="n">
-        <v>0.17</v>
+        <v>0.581</v>
       </c>
       <c r="N12" t="n">
-        <v>0.108</v>
+        <v>0.553</v>
       </c>
       <c r="O12" t="n">
-        <v>0.066</v>
+        <v>0.502</v>
       </c>
       <c r="P12" t="n">
-        <v>0.045</v>
+        <v>0.472</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.028</v>
+        <v>0.406</v>
       </c>
       <c r="R12" t="n">
-        <v>0.016</v>
+        <v>0.326</v>
       </c>
       <c r="S12" t="n">
-        <v>0.013</v>
+        <v>0.248</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01</v>
+        <v>0.178</v>
       </c>
       <c r="U12" t="n">
-        <v>0.01</v>
+        <v>0.093</v>
       </c>
       <c r="V12" t="n">
         <v>0.038</v>
@@ -1845,68 +1909,68 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.803</v>
+        <v>0.775</v>
       </c>
       <c r="D13" t="n">
-        <v>0.783</v>
+        <v>0.725</v>
       </c>
       <c r="E13" t="n">
-        <v>0.751</v>
+        <v>0.671</v>
       </c>
       <c r="F13" t="n">
-        <v>0.705</v>
+        <v>0.613</v>
       </c>
       <c r="G13" t="n">
-        <v>0.666</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.608</v>
+        <v>0.506</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.449</v>
       </c>
       <c r="J13" t="n">
-        <v>0.509</v>
+        <v>0.38</v>
       </c>
       <c r="K13" t="n">
-        <v>0.444</v>
+        <v>0.303</v>
       </c>
       <c r="L13" t="n">
-        <v>0.378</v>
+        <v>0.234</v>
       </c>
       <c r="M13" t="n">
-        <v>0.309</v>
+        <v>0.17</v>
       </c>
       <c r="N13" t="n">
-        <v>0.248</v>
+        <v>0.108</v>
       </c>
       <c r="O13" t="n">
-        <v>0.187</v>
+        <v>0.066</v>
       </c>
       <c r="P13" t="n">
-        <v>0.132</v>
+        <v>0.045</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.095</v>
+        <v>0.028</v>
       </c>
       <c r="R13" t="n">
-        <v>0.06</v>
+        <v>0.016</v>
       </c>
       <c r="S13" t="n">
-        <v>0.042</v>
+        <v>0.013</v>
       </c>
       <c r="T13" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="V13" t="n">
         <v>0.038</v>
@@ -1915,70 +1979,210 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sumDino</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B16" t="n">
         <v>0.829</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C16" t="n">
         <v>0.822</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D16" t="n">
         <v>0.8129999999999999</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" t="n">
         <v>0.783</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F16" t="n">
         <v>0.757</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G16" t="n">
         <v>0.732</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H16" t="n">
         <v>0.695</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I16" t="n">
         <v>0.654</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J16" t="n">
         <v>0.617</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K16" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L16" t="n">
         <v>0.506</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M16" t="n">
         <v>0.436</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N16" t="n">
         <v>0.391</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O16" t="n">
         <v>0.336</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P16" t="n">
         <v>0.286</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q16" t="n">
         <v>0.224</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R16" t="n">
         <v>0.173</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S16" t="n">
         <v>0.125</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T16" t="n">
         <v>0.066</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>0.042</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V16" t="n">
         <v>0.038</v>
       </c>
     </row>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -656,6 +656,166 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="15"/>
+          <order val="15"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$17:$V$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="16"/>
+          <order val="16"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$18:$V$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="17"/>
+          <order val="17"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$19:$V$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="18"/>
+          <order val="18"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$20:$V$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$21:$V$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -729,7 +889,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1039,7 +1199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1209,68 +1369,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.829</v>
       </c>
       <c r="C3" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.797</v>
       </c>
       <c r="E3" t="n">
-        <v>0.797</v>
+        <v>0.788</v>
       </c>
       <c r="F3" t="n">
-        <v>0.781</v>
+        <v>0.771</v>
       </c>
       <c r="G3" t="n">
-        <v>0.772</v>
+        <v>0.748</v>
       </c>
       <c r="H3" t="n">
-        <v>0.758</v>
+        <v>0.739</v>
       </c>
       <c r="I3" t="n">
-        <v>0.733</v>
+        <v>0.725</v>
       </c>
       <c r="J3" t="n">
-        <v>0.705</v>
+        <v>0.704</v>
       </c>
       <c r="K3" t="n">
-        <v>0.672</v>
+        <v>0.679</v>
       </c>
       <c r="L3" t="n">
-        <v>0.656</v>
+        <v>0.649</v>
       </c>
       <c r="M3" t="n">
-        <v>0.61</v>
+        <v>0.622</v>
       </c>
       <c r="N3" t="n">
-        <v>0.569</v>
+        <v>0.588</v>
       </c>
       <c r="O3" t="n">
         <v>0.533</v>
       </c>
       <c r="P3" t="n">
-        <v>0.478</v>
+        <v>0.476</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.417</v>
+        <v>0.426</v>
       </c>
       <c r="R3" t="n">
-        <v>0.343</v>
+        <v>0.354</v>
       </c>
       <c r="S3" t="n">
-        <v>0.262</v>
+        <v>0.243</v>
       </c>
       <c r="T3" t="n">
-        <v>0.191</v>
+        <v>0.166</v>
       </c>
       <c r="U3" t="n">
-        <v>0.106</v>
+        <v>0.078</v>
       </c>
       <c r="V3" t="n">
         <v>0.038</v>
@@ -1279,68 +1439,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.829</v>
       </c>
       <c r="C4" t="n">
-        <v>0.823</v>
+        <v>0.82</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="E4" t="n">
-        <v>0.796</v>
+        <v>0.792</v>
       </c>
       <c r="F4" t="n">
-        <v>0.775</v>
+        <v>0.779</v>
       </c>
       <c r="G4" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="H4" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="I4" t="n">
-        <v>0.707</v>
+        <v>0.728</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.699</v>
       </c>
       <c r="K4" t="n">
-        <v>0.67</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.628</v>
+        <v>0.662</v>
       </c>
       <c r="M4" t="n">
-        <v>0.598</v>
+        <v>0.63</v>
       </c>
       <c r="N4" t="n">
-        <v>0.555</v>
+        <v>0.581</v>
       </c>
       <c r="O4" t="n">
-        <v>0.51</v>
+        <v>0.549</v>
       </c>
       <c r="P4" t="n">
-        <v>0.457</v>
+        <v>0.501</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.398</v>
+        <v>0.436</v>
       </c>
       <c r="R4" t="n">
-        <v>0.329</v>
+        <v>0.369</v>
       </c>
       <c r="S4" t="n">
-        <v>0.26</v>
+        <v>0.272</v>
       </c>
       <c r="T4" t="n">
-        <v>0.179</v>
+        <v>0.19</v>
       </c>
       <c r="U4" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="V4" t="n">
         <v>0.038</v>
@@ -1349,68 +1509,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.827</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.826</v>
+        <v>0.795</v>
       </c>
       <c r="E5" t="n">
-        <v>0.831</v>
+        <v>0.78</v>
       </c>
       <c r="F5" t="n">
-        <v>0.821</v>
+        <v>0.773</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.746</v>
       </c>
       <c r="H5" t="n">
-        <v>0.806</v>
+        <v>0.731</v>
       </c>
       <c r="I5" t="n">
-        <v>0.795</v>
+        <v>0.71</v>
       </c>
       <c r="J5" t="n">
-        <v>0.778</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.768</v>
+        <v>0.673</v>
       </c>
       <c r="L5" t="n">
-        <v>0.742</v>
+        <v>0.641</v>
       </c>
       <c r="M5" t="n">
-        <v>0.727</v>
+        <v>0.608</v>
       </c>
       <c r="N5" t="n">
-        <v>0.701</v>
+        <v>0.58</v>
       </c>
       <c r="O5" t="n">
-        <v>0.668</v>
+        <v>0.53</v>
       </c>
       <c r="P5" t="n">
-        <v>0.637</v>
+        <v>0.463</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.582</v>
+        <v>0.393</v>
       </c>
       <c r="R5" t="n">
-        <v>0.533</v>
+        <v>0.314</v>
       </c>
       <c r="S5" t="n">
-        <v>0.458</v>
+        <v>0.245</v>
       </c>
       <c r="T5" t="n">
-        <v>0.337</v>
+        <v>0.156</v>
       </c>
       <c r="U5" t="n">
-        <v>0.184</v>
+        <v>0.068</v>
       </c>
       <c r="V5" t="n">
         <v>0.038</v>
@@ -1419,68 +1579,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.829</v>
       </c>
       <c r="C6" t="n">
-        <v>0.804</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.784</v>
+        <v>0.795</v>
       </c>
       <c r="E6" t="n">
-        <v>0.763</v>
+        <v>0.78</v>
       </c>
       <c r="F6" t="n">
-        <v>0.745</v>
+        <v>0.773</v>
       </c>
       <c r="G6" t="n">
-        <v>0.711</v>
+        <v>0.746</v>
       </c>
       <c r="H6" t="n">
-        <v>0.662</v>
+        <v>0.731</v>
       </c>
       <c r="I6" t="n">
-        <v>0.632</v>
+        <v>0.71</v>
       </c>
       <c r="J6" t="n">
-        <v>0.576</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K6" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.53</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.285</v>
-      </c>
       <c r="P6" t="n">
-        <v>0.215</v>
+        <v>0.463</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.152</v>
+        <v>0.393</v>
       </c>
       <c r="R6" t="n">
-        <v>0.111</v>
+        <v>0.314</v>
       </c>
       <c r="S6" t="n">
-        <v>0.066</v>
+        <v>0.245</v>
       </c>
       <c r="T6" t="n">
-        <v>0.035</v>
+        <v>0.156</v>
       </c>
       <c r="U6" t="n">
-        <v>0.015</v>
+        <v>0.068</v>
       </c>
       <c r="V6" t="n">
         <v>0.038</v>
@@ -1489,68 +1649,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.829</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.778</v>
       </c>
       <c r="E7" t="n">
-        <v>0.796</v>
+        <v>0.744</v>
       </c>
       <c r="F7" t="n">
-        <v>0.791</v>
+        <v>0.704</v>
       </c>
       <c r="G7" t="n">
-        <v>0.781</v>
+        <v>0.663</v>
       </c>
       <c r="H7" t="n">
-        <v>0.764</v>
+        <v>0.636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.754</v>
+        <v>0.578</v>
       </c>
       <c r="J7" t="n">
-        <v>0.745</v>
+        <v>0.546</v>
       </c>
       <c r="K7" t="n">
-        <v>0.728</v>
+        <v>0.509</v>
       </c>
       <c r="L7" t="n">
-        <v>0.698</v>
+        <v>0.468</v>
       </c>
       <c r="M7" t="n">
-        <v>0.667</v>
+        <v>0.42</v>
       </c>
       <c r="N7" t="n">
-        <v>0.629</v>
+        <v>0.379</v>
       </c>
       <c r="O7" t="n">
-        <v>0.593</v>
+        <v>0.322</v>
       </c>
       <c r="P7" t="n">
-        <v>0.55</v>
+        <v>0.286</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.493</v>
+        <v>0.246</v>
       </c>
       <c r="R7" t="n">
-        <v>0.425</v>
+        <v>0.222</v>
       </c>
       <c r="S7" t="n">
-        <v>0.324</v>
+        <v>0.198</v>
       </c>
       <c r="T7" t="n">
-        <v>0.221</v>
+        <v>0.132</v>
       </c>
       <c r="U7" t="n">
-        <v>0.115</v>
+        <v>0.075</v>
       </c>
       <c r="V7" t="n">
         <v>0.038</v>
@@ -1559,68 +1719,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.829</v>
       </c>
       <c r="C8" t="n">
-        <v>0.823</v>
+        <v>0.82</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.806</v>
+        <v>0.797</v>
       </c>
       <c r="F8" t="n">
-        <v>0.802</v>
+        <v>0.781</v>
       </c>
       <c r="G8" t="n">
-        <v>0.794</v>
+        <v>0.772</v>
       </c>
       <c r="H8" t="n">
-        <v>0.789</v>
+        <v>0.758</v>
       </c>
       <c r="I8" t="n">
-        <v>0.774</v>
+        <v>0.733</v>
       </c>
       <c r="J8" t="n">
-        <v>0.757</v>
+        <v>0.705</v>
       </c>
       <c r="K8" t="n">
-        <v>0.741</v>
+        <v>0.672</v>
       </c>
       <c r="L8" t="n">
-        <v>0.716</v>
+        <v>0.656</v>
       </c>
       <c r="M8" t="n">
-        <v>0.703</v>
+        <v>0.61</v>
       </c>
       <c r="N8" t="n">
-        <v>0.674</v>
+        <v>0.569</v>
       </c>
       <c r="O8" t="n">
-        <v>0.635</v>
+        <v>0.533</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6</v>
+        <v>0.478</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.552</v>
+        <v>0.417</v>
       </c>
       <c r="R8" t="n">
-        <v>0.48</v>
+        <v>0.343</v>
       </c>
       <c r="S8" t="n">
-        <v>0.403</v>
+        <v>0.262</v>
       </c>
       <c r="T8" t="n">
-        <v>0.288</v>
+        <v>0.191</v>
       </c>
       <c r="U8" t="n">
-        <v>0.157</v>
+        <v>0.106</v>
       </c>
       <c r="V8" t="n">
         <v>0.038</v>
@@ -1629,68 +1789,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>dinov2_pca_gaussian</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.829</v>
       </c>
       <c r="C9" t="n">
-        <v>0.797</v>
+        <v>0.823</v>
       </c>
       <c r="D9" t="n">
-        <v>0.787</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.753</v>
+        <v>0.796</v>
       </c>
       <c r="F9" t="n">
-        <v>0.719</v>
+        <v>0.775</v>
       </c>
       <c r="G9" t="n">
-        <v>0.68</v>
+        <v>0.761</v>
       </c>
       <c r="H9" t="n">
-        <v>0.627</v>
+        <v>0.742</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.707</v>
       </c>
       <c r="J9" t="n">
-        <v>0.498</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="P9" t="n">
         <v>0.457</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.15</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.106</v>
+        <v>0.398</v>
       </c>
       <c r="R9" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.329</v>
       </c>
       <c r="S9" t="n">
-        <v>0.042</v>
+        <v>0.26</v>
       </c>
       <c r="T9" t="n">
-        <v>0.027</v>
+        <v>0.179</v>
       </c>
       <c r="U9" t="n">
-        <v>0.018</v>
+        <v>0.111</v>
       </c>
       <c r="V9" t="n">
         <v>0.038</v>
@@ -1699,68 +1859,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.829</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8</v>
+        <v>0.827</v>
       </c>
       <c r="D10" t="n">
-        <v>0.785</v>
+        <v>0.826</v>
       </c>
       <c r="E10" t="n">
-        <v>0.759</v>
+        <v>0.831</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751</v>
+        <v>0.821</v>
       </c>
       <c r="G10" t="n">
-        <v>0.716</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.679</v>
+        <v>0.806</v>
       </c>
       <c r="I10" t="n">
-        <v>0.636</v>
+        <v>0.795</v>
       </c>
       <c r="J10" t="n">
-        <v>0.585</v>
+        <v>0.778</v>
       </c>
       <c r="K10" t="n">
-        <v>0.524</v>
+        <v>0.768</v>
       </c>
       <c r="L10" t="n">
-        <v>0.471</v>
+        <v>0.742</v>
       </c>
       <c r="M10" t="n">
-        <v>0.413</v>
+        <v>0.727</v>
       </c>
       <c r="N10" t="n">
-        <v>0.351</v>
+        <v>0.701</v>
       </c>
       <c r="O10" t="n">
-        <v>0.286</v>
+        <v>0.668</v>
       </c>
       <c r="P10" t="n">
-        <v>0.215</v>
+        <v>0.637</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.164</v>
+        <v>0.582</v>
       </c>
       <c r="R10" t="n">
-        <v>0.11</v>
+        <v>0.533</v>
       </c>
       <c r="S10" t="n">
-        <v>0.065</v>
+        <v>0.458</v>
       </c>
       <c r="T10" t="n">
-        <v>0.038</v>
+        <v>0.337</v>
       </c>
       <c r="U10" t="n">
-        <v>0.017</v>
+        <v>0.184</v>
       </c>
       <c r="V10" t="n">
         <v>0.038</v>
@@ -1769,68 +1929,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.829</v>
       </c>
       <c r="C11" t="n">
-        <v>0.822</v>
+        <v>0.804</v>
       </c>
       <c r="D11" t="n">
-        <v>0.799</v>
+        <v>0.784</v>
       </c>
       <c r="E11" t="n">
-        <v>0.773</v>
+        <v>0.763</v>
       </c>
       <c r="F11" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="G11" t="n">
-        <v>0.729</v>
+        <v>0.711</v>
       </c>
       <c r="H11" t="n">
-        <v>0.714</v>
+        <v>0.662</v>
       </c>
       <c r="I11" t="n">
-        <v>0.667</v>
+        <v>0.632</v>
       </c>
       <c r="J11" t="n">
-        <v>0.633</v>
+        <v>0.576</v>
       </c>
       <c r="K11" t="n">
-        <v>0.608</v>
+        <v>0.53</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.469</v>
       </c>
       <c r="M11" t="n">
-        <v>0.525</v>
+        <v>0.403</v>
       </c>
       <c r="N11" t="n">
-        <v>0.486</v>
+        <v>0.348</v>
       </c>
       <c r="O11" t="n">
-        <v>0.448</v>
+        <v>0.285</v>
       </c>
       <c r="P11" t="n">
-        <v>0.419</v>
+        <v>0.215</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.372</v>
+        <v>0.152</v>
       </c>
       <c r="R11" t="n">
-        <v>0.326</v>
+        <v>0.111</v>
       </c>
       <c r="S11" t="n">
-        <v>0.243</v>
+        <v>0.066</v>
       </c>
       <c r="T11" t="n">
-        <v>0.185</v>
+        <v>0.035</v>
       </c>
       <c r="U11" t="n">
-        <v>0.116</v>
+        <v>0.015</v>
       </c>
       <c r="V11" t="n">
         <v>0.038</v>
@@ -1839,68 +1999,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pca1</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.799</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.784</v>
+        <v>0.796</v>
       </c>
       <c r="F12" t="n">
-        <v>0.759</v>
+        <v>0.791</v>
       </c>
       <c r="G12" t="n">
-        <v>0.737</v>
+        <v>0.781</v>
       </c>
       <c r="H12" t="n">
-        <v>0.715</v>
+        <v>0.764</v>
       </c>
       <c r="I12" t="n">
-        <v>0.705</v>
+        <v>0.754</v>
       </c>
       <c r="J12" t="n">
-        <v>0.679</v>
+        <v>0.745</v>
       </c>
       <c r="K12" t="n">
-        <v>0.652</v>
+        <v>0.728</v>
       </c>
       <c r="L12" t="n">
-        <v>0.617</v>
+        <v>0.698</v>
       </c>
       <c r="M12" t="n">
-        <v>0.581</v>
+        <v>0.667</v>
       </c>
       <c r="N12" t="n">
-        <v>0.553</v>
+        <v>0.629</v>
       </c>
       <c r="O12" t="n">
-        <v>0.502</v>
+        <v>0.593</v>
       </c>
       <c r="P12" t="n">
-        <v>0.472</v>
+        <v>0.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.406</v>
+        <v>0.493</v>
       </c>
       <c r="R12" t="n">
-        <v>0.326</v>
+        <v>0.425</v>
       </c>
       <c r="S12" t="n">
-        <v>0.248</v>
+        <v>0.324</v>
       </c>
       <c r="T12" t="n">
-        <v>0.178</v>
+        <v>0.221</v>
       </c>
       <c r="U12" t="n">
-        <v>0.093</v>
+        <v>0.115</v>
       </c>
       <c r="V12" t="n">
         <v>0.038</v>
@@ -1909,68 +2069,68 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.775</v>
+        <v>0.823</v>
       </c>
       <c r="D13" t="n">
-        <v>0.725</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.671</v>
+        <v>0.806</v>
       </c>
       <c r="F13" t="n">
-        <v>0.613</v>
+        <v>0.802</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.794</v>
       </c>
       <c r="H13" t="n">
-        <v>0.506</v>
+        <v>0.789</v>
       </c>
       <c r="I13" t="n">
-        <v>0.449</v>
+        <v>0.774</v>
       </c>
       <c r="J13" t="n">
-        <v>0.38</v>
+        <v>0.757</v>
       </c>
       <c r="K13" t="n">
-        <v>0.303</v>
+        <v>0.741</v>
       </c>
       <c r="L13" t="n">
-        <v>0.234</v>
+        <v>0.716</v>
       </c>
       <c r="M13" t="n">
-        <v>0.17</v>
+        <v>0.703</v>
       </c>
       <c r="N13" t="n">
-        <v>0.108</v>
+        <v>0.674</v>
       </c>
       <c r="O13" t="n">
-        <v>0.066</v>
+        <v>0.635</v>
       </c>
       <c r="P13" t="n">
-        <v>0.045</v>
+        <v>0.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.028</v>
+        <v>0.552</v>
       </c>
       <c r="R13" t="n">
-        <v>0.016</v>
+        <v>0.48</v>
       </c>
       <c r="S13" t="n">
-        <v>0.013</v>
+        <v>0.403</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01</v>
+        <v>0.288</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01</v>
+        <v>0.157</v>
       </c>
       <c r="V13" t="n">
         <v>0.038</v>
@@ -1979,68 +2139,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.829</v>
       </c>
       <c r="C14" t="n">
-        <v>0.803</v>
+        <v>0.797</v>
       </c>
       <c r="D14" t="n">
-        <v>0.783</v>
+        <v>0.787</v>
       </c>
       <c r="E14" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="F14" t="n">
-        <v>0.705</v>
+        <v>0.719</v>
       </c>
       <c r="G14" t="n">
-        <v>0.666</v>
+        <v>0.68</v>
       </c>
       <c r="H14" t="n">
-        <v>0.608</v>
+        <v>0.627</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.509</v>
+        <v>0.498</v>
       </c>
       <c r="K14" t="n">
-        <v>0.444</v>
+        <v>0.457</v>
       </c>
       <c r="L14" t="n">
-        <v>0.378</v>
+        <v>0.404</v>
       </c>
       <c r="M14" t="n">
-        <v>0.309</v>
+        <v>0.343</v>
       </c>
       <c r="N14" t="n">
-        <v>0.248</v>
+        <v>0.263</v>
       </c>
       <c r="O14" t="n">
-        <v>0.187</v>
+        <v>0.209</v>
       </c>
       <c r="P14" t="n">
-        <v>0.132</v>
+        <v>0.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.095</v>
+        <v>0.106</v>
       </c>
       <c r="R14" t="n">
-        <v>0.06</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="S14" t="n">
         <v>0.042</v>
       </c>
       <c r="T14" t="n">
-        <v>0.024</v>
+        <v>0.027</v>
       </c>
       <c r="U14" t="n">
-        <v>0.013</v>
+        <v>0.018</v>
       </c>
       <c r="V14" t="n">
         <v>0.038</v>
@@ -2049,68 +2209,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.829</v>
       </c>
       <c r="C15" t="n">
-        <v>0.821</v>
+        <v>0.8</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.785</v>
       </c>
       <c r="E15" t="n">
-        <v>0.799</v>
+        <v>0.759</v>
       </c>
       <c r="F15" t="n">
-        <v>0.788</v>
+        <v>0.751</v>
       </c>
       <c r="G15" t="n">
-        <v>0.772</v>
+        <v>0.716</v>
       </c>
       <c r="H15" t="n">
-        <v>0.771</v>
+        <v>0.679</v>
       </c>
       <c r="I15" t="n">
-        <v>0.74</v>
+        <v>0.636</v>
       </c>
       <c r="J15" t="n">
-        <v>0.726</v>
+        <v>0.585</v>
       </c>
       <c r="K15" t="n">
-        <v>0.697</v>
+        <v>0.524</v>
       </c>
       <c r="L15" t="n">
-        <v>0.67</v>
+        <v>0.471</v>
       </c>
       <c r="M15" t="n">
-        <v>0.637</v>
+        <v>0.413</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>0.351</v>
       </c>
       <c r="O15" t="n">
-        <v>0.547</v>
+        <v>0.286</v>
       </c>
       <c r="P15" t="n">
-        <v>0.496</v>
+        <v>0.215</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.423</v>
+        <v>0.164</v>
       </c>
       <c r="R15" t="n">
-        <v>0.359</v>
+        <v>0.11</v>
       </c>
       <c r="S15" t="n">
-        <v>0.292</v>
+        <v>0.065</v>
       </c>
       <c r="T15" t="n">
-        <v>0.194</v>
+        <v>0.038</v>
       </c>
       <c r="U15" t="n">
-        <v>0.111</v>
+        <v>0.017</v>
       </c>
       <c r="V15" t="n">
         <v>0.038</v>
@@ -2119,70 +2279,420 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>occlusion</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.486</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pca1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>random_baseline</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sumDino</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B21" t="n">
         <v>0.829</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C21" t="n">
         <v>0.822</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D21" t="n">
         <v>0.8129999999999999</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E21" t="n">
         <v>0.783</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F21" t="n">
         <v>0.757</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G21" t="n">
         <v>0.732</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H21" t="n">
         <v>0.695</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I21" t="n">
         <v>0.654</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J21" t="n">
         <v>0.617</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K21" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L21" t="n">
         <v>0.506</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M21" t="n">
         <v>0.436</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N21" t="n">
         <v>0.391</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O21" t="n">
         <v>0.336</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P21" t="n">
         <v>0.286</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q21" t="n">
         <v>0.224</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R21" t="n">
         <v>0.173</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S21" t="n">
         <v>0.125</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T21" t="n">
         <v>0.066</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U21" t="n">
         <v>0.042</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V21" t="n">
         <v>0.038</v>
       </c>
     </row>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -784,38 +784,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="19"/>
-          <order val="19"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$21:$V$21</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -889,7 +857,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1199,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2349,68 +2317,68 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pca1</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.829</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.775</v>
       </c>
       <c r="D17" t="n">
-        <v>0.799</v>
+        <v>0.725</v>
       </c>
       <c r="E17" t="n">
-        <v>0.784</v>
+        <v>0.671</v>
       </c>
       <c r="F17" t="n">
-        <v>0.759</v>
+        <v>0.613</v>
       </c>
       <c r="G17" t="n">
-        <v>0.737</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.715</v>
+        <v>0.506</v>
       </c>
       <c r="I17" t="n">
-        <v>0.705</v>
+        <v>0.449</v>
       </c>
       <c r="J17" t="n">
-        <v>0.679</v>
+        <v>0.38</v>
       </c>
       <c r="K17" t="n">
-        <v>0.652</v>
+        <v>0.303</v>
       </c>
       <c r="L17" t="n">
-        <v>0.617</v>
+        <v>0.234</v>
       </c>
       <c r="M17" t="n">
-        <v>0.581</v>
+        <v>0.17</v>
       </c>
       <c r="N17" t="n">
-        <v>0.553</v>
+        <v>0.108</v>
       </c>
       <c r="O17" t="n">
-        <v>0.502</v>
+        <v>0.066</v>
       </c>
       <c r="P17" t="n">
-        <v>0.472</v>
+        <v>0.045</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.406</v>
+        <v>0.028</v>
       </c>
       <c r="R17" t="n">
-        <v>0.326</v>
+        <v>0.016</v>
       </c>
       <c r="S17" t="n">
-        <v>0.248</v>
+        <v>0.013</v>
       </c>
       <c r="T17" t="n">
-        <v>0.178</v>
+        <v>0.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0.093</v>
+        <v>0.01</v>
       </c>
       <c r="V17" t="n">
         <v>0.038</v>
@@ -2419,68 +2387,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.829</v>
       </c>
       <c r="C18" t="n">
-        <v>0.775</v>
+        <v>0.803</v>
       </c>
       <c r="D18" t="n">
-        <v>0.725</v>
+        <v>0.783</v>
       </c>
       <c r="E18" t="n">
-        <v>0.671</v>
+        <v>0.751</v>
       </c>
       <c r="F18" t="n">
-        <v>0.613</v>
+        <v>0.705</v>
       </c>
       <c r="G18" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.449</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.38</v>
+        <v>0.509</v>
       </c>
       <c r="K18" t="n">
-        <v>0.303</v>
+        <v>0.444</v>
       </c>
       <c r="L18" t="n">
-        <v>0.234</v>
+        <v>0.378</v>
       </c>
       <c r="M18" t="n">
-        <v>0.17</v>
+        <v>0.309</v>
       </c>
       <c r="N18" t="n">
-        <v>0.108</v>
+        <v>0.248</v>
       </c>
       <c r="O18" t="n">
-        <v>0.066</v>
+        <v>0.187</v>
       </c>
       <c r="P18" t="n">
-        <v>0.045</v>
+        <v>0.132</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.028</v>
+        <v>0.095</v>
       </c>
       <c r="R18" t="n">
-        <v>0.016</v>
+        <v>0.06</v>
       </c>
       <c r="S18" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U18" t="n">
         <v>0.013</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.01</v>
       </c>
       <c r="V18" t="n">
         <v>0.038</v>
@@ -2489,68 +2457,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>sumDino</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.803</v>
+        <v>0.82</v>
       </c>
       <c r="D19" t="n">
-        <v>0.783</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.751</v>
+        <v>0.799</v>
       </c>
       <c r="F19" t="n">
-        <v>0.705</v>
+        <v>0.789</v>
       </c>
       <c r="G19" t="n">
-        <v>0.666</v>
+        <v>0.775</v>
       </c>
       <c r="H19" t="n">
-        <v>0.608</v>
+        <v>0.743</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="J19" t="n">
-        <v>0.509</v>
+        <v>0.699</v>
       </c>
       <c r="K19" t="n">
-        <v>0.444</v>
+        <v>0.662</v>
       </c>
       <c r="L19" t="n">
-        <v>0.378</v>
+        <v>0.607</v>
       </c>
       <c r="M19" t="n">
-        <v>0.309</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.248</v>
+        <v>0.526</v>
       </c>
       <c r="O19" t="n">
-        <v>0.187</v>
+        <v>0.492</v>
       </c>
       <c r="P19" t="n">
-        <v>0.132</v>
+        <v>0.453</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.095</v>
+        <v>0.409</v>
       </c>
       <c r="R19" t="n">
-        <v>0.06</v>
+        <v>0.344</v>
       </c>
       <c r="S19" t="n">
-        <v>0.042</v>
+        <v>0.27</v>
       </c>
       <c r="T19" t="n">
-        <v>0.024</v>
+        <v>0.194</v>
       </c>
       <c r="U19" t="n">
-        <v>0.013</v>
+        <v>0.092</v>
       </c>
       <c r="V19" t="n">
         <v>0.038</v>
@@ -2559,140 +2527,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0.829</v>
       </c>
       <c r="C20" t="n">
-        <v>0.82</v>
+        <v>0.822</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.799</v>
+        <v>0.783</v>
       </c>
       <c r="F20" t="n">
-        <v>0.789</v>
+        <v>0.757</v>
       </c>
       <c r="G20" t="n">
-        <v>0.775</v>
+        <v>0.732</v>
       </c>
       <c r="H20" t="n">
-        <v>0.743</v>
+        <v>0.695</v>
       </c>
       <c r="I20" t="n">
-        <v>0.715</v>
+        <v>0.654</v>
       </c>
       <c r="J20" t="n">
-        <v>0.699</v>
+        <v>0.617</v>
       </c>
       <c r="K20" t="n">
-        <v>0.662</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.607</v>
+        <v>0.506</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.436</v>
       </c>
       <c r="N20" t="n">
-        <v>0.526</v>
+        <v>0.391</v>
       </c>
       <c r="O20" t="n">
-        <v>0.492</v>
+        <v>0.336</v>
       </c>
       <c r="P20" t="n">
-        <v>0.453</v>
+        <v>0.286</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.409</v>
+        <v>0.224</v>
       </c>
       <c r="R20" t="n">
-        <v>0.344</v>
+        <v>0.173</v>
       </c>
       <c r="S20" t="n">
-        <v>0.27</v>
+        <v>0.125</v>
       </c>
       <c r="T20" t="n">
-        <v>0.194</v>
+        <v>0.066</v>
       </c>
       <c r="U20" t="n">
-        <v>0.092</v>
+        <v>0.042</v>
       </c>
       <c r="V20" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="V21" t="n">
         <v>0.038</v>
       </c>
     </row>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -784,6 +784,38 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$21:$V$21</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -857,7 +889,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1167,10 +1199,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
@@ -1337,68 +1369,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.829</v>
       </c>
       <c r="C3" t="n">
-        <v>0.827</v>
+        <v>0.821</v>
       </c>
       <c r="D3" t="n">
-        <v>0.797</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.788</v>
+        <v>0.794</v>
       </c>
       <c r="F3" t="n">
-        <v>0.771</v>
+        <v>0.789</v>
       </c>
       <c r="G3" t="n">
-        <v>0.748</v>
+        <v>0.776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.739</v>
+        <v>0.762</v>
       </c>
       <c r="I3" t="n">
-        <v>0.725</v>
+        <v>0.744</v>
       </c>
       <c r="J3" t="n">
-        <v>0.704</v>
+        <v>0.72</v>
       </c>
       <c r="K3" t="n">
-        <v>0.679</v>
+        <v>0.703</v>
       </c>
       <c r="L3" t="n">
-        <v>0.649</v>
+        <v>0.678</v>
       </c>
       <c r="M3" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.622</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.588</v>
-      </c>
       <c r="O3" t="n">
-        <v>0.533</v>
+        <v>0.596</v>
       </c>
       <c r="P3" t="n">
-        <v>0.476</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.426</v>
+        <v>0.516</v>
       </c>
       <c r="R3" t="n">
-        <v>0.354</v>
+        <v>0.44</v>
       </c>
       <c r="S3" t="n">
-        <v>0.243</v>
+        <v>0.359</v>
       </c>
       <c r="T3" t="n">
-        <v>0.166</v>
+        <v>0.271</v>
       </c>
       <c r="U3" t="n">
-        <v>0.078</v>
+        <v>0.152</v>
       </c>
       <c r="V3" t="n">
         <v>0.038</v>
@@ -1407,68 +1439,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.829</v>
       </c>
       <c r="C4" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.806</v>
+        <v>0.797</v>
       </c>
       <c r="E4" t="n">
-        <v>0.792</v>
+        <v>0.788</v>
       </c>
       <c r="F4" t="n">
-        <v>0.779</v>
+        <v>0.771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.763</v>
+        <v>0.748</v>
       </c>
       <c r="H4" t="n">
-        <v>0.752</v>
+        <v>0.739</v>
       </c>
       <c r="I4" t="n">
-        <v>0.728</v>
+        <v>0.725</v>
       </c>
       <c r="J4" t="n">
-        <v>0.699</v>
+        <v>0.704</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="L4" t="n">
-        <v>0.662</v>
+        <v>0.649</v>
       </c>
       <c r="M4" t="n">
-        <v>0.63</v>
+        <v>0.622</v>
       </c>
       <c r="N4" t="n">
-        <v>0.581</v>
+        <v>0.588</v>
       </c>
       <c r="O4" t="n">
-        <v>0.549</v>
+        <v>0.533</v>
       </c>
       <c r="P4" t="n">
-        <v>0.501</v>
+        <v>0.476</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.436</v>
+        <v>0.426</v>
       </c>
       <c r="R4" t="n">
-        <v>0.369</v>
+        <v>0.354</v>
       </c>
       <c r="S4" t="n">
-        <v>0.272</v>
+        <v>0.243</v>
       </c>
       <c r="T4" t="n">
-        <v>0.19</v>
+        <v>0.166</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1</v>
+        <v>0.078</v>
       </c>
       <c r="V4" t="n">
         <v>0.038</v>
@@ -1477,68 +1509,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="D5" t="n">
-        <v>0.795</v>
+        <v>0.806</v>
       </c>
       <c r="E5" t="n">
-        <v>0.78</v>
+        <v>0.792</v>
       </c>
       <c r="F5" t="n">
-        <v>0.773</v>
+        <v>0.779</v>
       </c>
       <c r="G5" t="n">
-        <v>0.746</v>
+        <v>0.763</v>
       </c>
       <c r="H5" t="n">
-        <v>0.731</v>
+        <v>0.752</v>
       </c>
       <c r="I5" t="n">
-        <v>0.71</v>
+        <v>0.728</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="K5" t="n">
-        <v>0.673</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.641</v>
+        <v>0.662</v>
       </c>
       <c r="M5" t="n">
-        <v>0.608</v>
+        <v>0.63</v>
       </c>
       <c r="N5" t="n">
-        <v>0.58</v>
+        <v>0.581</v>
       </c>
       <c r="O5" t="n">
-        <v>0.53</v>
+        <v>0.549</v>
       </c>
       <c r="P5" t="n">
-        <v>0.463</v>
+        <v>0.501</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.393</v>
+        <v>0.436</v>
       </c>
       <c r="R5" t="n">
-        <v>0.314</v>
+        <v>0.369</v>
       </c>
       <c r="S5" t="n">
-        <v>0.245</v>
+        <v>0.272</v>
       </c>
       <c r="T5" t="n">
-        <v>0.156</v>
+        <v>0.19</v>
       </c>
       <c r="U5" t="n">
-        <v>0.068</v>
+        <v>0.1</v>
       </c>
       <c r="V5" t="n">
         <v>0.038</v>
@@ -1547,7 +1579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1617,68 +1649,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.829</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.778</v>
+        <v>0.795</v>
       </c>
       <c r="E7" t="n">
-        <v>0.744</v>
+        <v>0.78</v>
       </c>
       <c r="F7" t="n">
-        <v>0.704</v>
+        <v>0.773</v>
       </c>
       <c r="G7" t="n">
-        <v>0.663</v>
+        <v>0.746</v>
       </c>
       <c r="H7" t="n">
-        <v>0.636</v>
+        <v>0.731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.578</v>
+        <v>0.71</v>
       </c>
       <c r="J7" t="n">
-        <v>0.546</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.509</v>
+        <v>0.673</v>
       </c>
       <c r="L7" t="n">
-        <v>0.468</v>
+        <v>0.641</v>
       </c>
       <c r="M7" t="n">
-        <v>0.42</v>
+        <v>0.608</v>
       </c>
       <c r="N7" t="n">
-        <v>0.379</v>
+        <v>0.58</v>
       </c>
       <c r="O7" t="n">
-        <v>0.322</v>
+        <v>0.53</v>
       </c>
       <c r="P7" t="n">
-        <v>0.286</v>
+        <v>0.463</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.246</v>
+        <v>0.393</v>
       </c>
       <c r="R7" t="n">
-        <v>0.222</v>
+        <v>0.314</v>
       </c>
       <c r="S7" t="n">
-        <v>0.198</v>
+        <v>0.245</v>
       </c>
       <c r="T7" t="n">
-        <v>0.132</v>
+        <v>0.156</v>
       </c>
       <c r="U7" t="n">
-        <v>0.075</v>
+        <v>0.068</v>
       </c>
       <c r="V7" t="n">
         <v>0.038</v>
@@ -1687,68 +1719,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.829</v>
       </c>
       <c r="C8" t="n">
-        <v>0.82</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.778</v>
       </c>
       <c r="E8" t="n">
-        <v>0.797</v>
+        <v>0.744</v>
       </c>
       <c r="F8" t="n">
-        <v>0.781</v>
+        <v>0.704</v>
       </c>
       <c r="G8" t="n">
-        <v>0.772</v>
+        <v>0.663</v>
       </c>
       <c r="H8" t="n">
-        <v>0.758</v>
+        <v>0.636</v>
       </c>
       <c r="I8" t="n">
-        <v>0.733</v>
+        <v>0.578</v>
       </c>
       <c r="J8" t="n">
-        <v>0.705</v>
+        <v>0.546</v>
       </c>
       <c r="K8" t="n">
-        <v>0.672</v>
+        <v>0.509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.656</v>
+        <v>0.468</v>
       </c>
       <c r="M8" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="N8" t="n">
-        <v>0.569</v>
+        <v>0.379</v>
       </c>
       <c r="O8" t="n">
-        <v>0.533</v>
+        <v>0.322</v>
       </c>
       <c r="P8" t="n">
-        <v>0.478</v>
+        <v>0.286</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.417</v>
+        <v>0.246</v>
       </c>
       <c r="R8" t="n">
-        <v>0.343</v>
+        <v>0.222</v>
       </c>
       <c r="S8" t="n">
-        <v>0.262</v>
+        <v>0.198</v>
       </c>
       <c r="T8" t="n">
-        <v>0.191</v>
+        <v>0.132</v>
       </c>
       <c r="U8" t="n">
-        <v>0.106</v>
+        <v>0.075</v>
       </c>
       <c r="V8" t="n">
         <v>0.038</v>
@@ -1757,68 +1789,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.829</v>
       </c>
       <c r="C9" t="n">
-        <v>0.823</v>
+        <v>0.82</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.796</v>
+        <v>0.797</v>
       </c>
       <c r="F9" t="n">
-        <v>0.775</v>
+        <v>0.781</v>
       </c>
       <c r="G9" t="n">
-        <v>0.761</v>
+        <v>0.772</v>
       </c>
       <c r="H9" t="n">
-        <v>0.742</v>
+        <v>0.758</v>
       </c>
       <c r="I9" t="n">
-        <v>0.707</v>
+        <v>0.733</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.705</v>
       </c>
       <c r="K9" t="n">
-        <v>0.67</v>
+        <v>0.672</v>
       </c>
       <c r="L9" t="n">
-        <v>0.628</v>
+        <v>0.656</v>
       </c>
       <c r="M9" t="n">
-        <v>0.598</v>
+        <v>0.61</v>
       </c>
       <c r="N9" t="n">
-        <v>0.555</v>
+        <v>0.569</v>
       </c>
       <c r="O9" t="n">
-        <v>0.51</v>
+        <v>0.533</v>
       </c>
       <c r="P9" t="n">
-        <v>0.457</v>
+        <v>0.478</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.398</v>
+        <v>0.417</v>
       </c>
       <c r="R9" t="n">
-        <v>0.329</v>
+        <v>0.343</v>
       </c>
       <c r="S9" t="n">
-        <v>0.26</v>
+        <v>0.262</v>
       </c>
       <c r="T9" t="n">
-        <v>0.179</v>
+        <v>0.191</v>
       </c>
       <c r="U9" t="n">
-        <v>0.111</v>
+        <v>0.106</v>
       </c>
       <c r="V9" t="n">
         <v>0.038</v>
@@ -1827,68 +1859,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_pca_gaussian</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.829</v>
       </c>
       <c r="C10" t="n">
-        <v>0.827</v>
+        <v>0.823</v>
       </c>
       <c r="D10" t="n">
-        <v>0.826</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.831</v>
+        <v>0.796</v>
       </c>
       <c r="F10" t="n">
-        <v>0.821</v>
+        <v>0.775</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.761</v>
       </c>
       <c r="H10" t="n">
-        <v>0.806</v>
+        <v>0.742</v>
       </c>
       <c r="I10" t="n">
-        <v>0.795</v>
+        <v>0.707</v>
       </c>
       <c r="J10" t="n">
-        <v>0.778</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.768</v>
+        <v>0.67</v>
       </c>
       <c r="L10" t="n">
-        <v>0.742</v>
+        <v>0.628</v>
       </c>
       <c r="M10" t="n">
-        <v>0.727</v>
+        <v>0.598</v>
       </c>
       <c r="N10" t="n">
-        <v>0.701</v>
+        <v>0.555</v>
       </c>
       <c r="O10" t="n">
-        <v>0.668</v>
+        <v>0.51</v>
       </c>
       <c r="P10" t="n">
-        <v>0.637</v>
+        <v>0.457</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.582</v>
+        <v>0.398</v>
       </c>
       <c r="R10" t="n">
-        <v>0.533</v>
+        <v>0.329</v>
       </c>
       <c r="S10" t="n">
-        <v>0.458</v>
+        <v>0.26</v>
       </c>
       <c r="T10" t="n">
-        <v>0.337</v>
+        <v>0.179</v>
       </c>
       <c r="U10" t="n">
-        <v>0.184</v>
+        <v>0.111</v>
       </c>
       <c r="V10" t="n">
         <v>0.038</v>
@@ -1897,68 +1929,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.829</v>
       </c>
       <c r="C11" t="n">
-        <v>0.804</v>
+        <v>0.827</v>
       </c>
       <c r="D11" t="n">
-        <v>0.784</v>
+        <v>0.826</v>
       </c>
       <c r="E11" t="n">
-        <v>0.763</v>
+        <v>0.831</v>
       </c>
       <c r="F11" t="n">
-        <v>0.745</v>
+        <v>0.821</v>
       </c>
       <c r="G11" t="n">
-        <v>0.711</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.662</v>
+        <v>0.806</v>
       </c>
       <c r="I11" t="n">
-        <v>0.632</v>
+        <v>0.795</v>
       </c>
       <c r="J11" t="n">
-        <v>0.576</v>
+        <v>0.778</v>
       </c>
       <c r="K11" t="n">
-        <v>0.53</v>
+        <v>0.768</v>
       </c>
       <c r="L11" t="n">
-        <v>0.469</v>
+        <v>0.742</v>
       </c>
       <c r="M11" t="n">
-        <v>0.403</v>
+        <v>0.727</v>
       </c>
       <c r="N11" t="n">
-        <v>0.348</v>
+        <v>0.701</v>
       </c>
       <c r="O11" t="n">
-        <v>0.285</v>
+        <v>0.668</v>
       </c>
       <c r="P11" t="n">
-        <v>0.215</v>
+        <v>0.637</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.152</v>
+        <v>0.582</v>
       </c>
       <c r="R11" t="n">
-        <v>0.111</v>
+        <v>0.533</v>
       </c>
       <c r="S11" t="n">
-        <v>0.066</v>
+        <v>0.458</v>
       </c>
       <c r="T11" t="n">
-        <v>0.035</v>
+        <v>0.337</v>
       </c>
       <c r="U11" t="n">
-        <v>0.015</v>
+        <v>0.184</v>
       </c>
       <c r="V11" t="n">
         <v>0.038</v>
@@ -1967,68 +1999,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.804</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="E12" t="n">
-        <v>0.796</v>
+        <v>0.763</v>
       </c>
       <c r="F12" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G12" t="n">
-        <v>0.781</v>
+        <v>0.711</v>
       </c>
       <c r="H12" t="n">
-        <v>0.764</v>
+        <v>0.662</v>
       </c>
       <c r="I12" t="n">
-        <v>0.754</v>
+        <v>0.632</v>
       </c>
       <c r="J12" t="n">
-        <v>0.745</v>
+        <v>0.576</v>
       </c>
       <c r="K12" t="n">
-        <v>0.728</v>
+        <v>0.53</v>
       </c>
       <c r="L12" t="n">
-        <v>0.698</v>
+        <v>0.469</v>
       </c>
       <c r="M12" t="n">
-        <v>0.667</v>
+        <v>0.403</v>
       </c>
       <c r="N12" t="n">
-        <v>0.629</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>0.593</v>
+        <v>0.285</v>
       </c>
       <c r="P12" t="n">
-        <v>0.55</v>
+        <v>0.215</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.493</v>
+        <v>0.152</v>
       </c>
       <c r="R12" t="n">
-        <v>0.425</v>
+        <v>0.111</v>
       </c>
       <c r="S12" t="n">
-        <v>0.324</v>
+        <v>0.066</v>
       </c>
       <c r="T12" t="n">
-        <v>0.221</v>
+        <v>0.035</v>
       </c>
       <c r="U12" t="n">
-        <v>0.115</v>
+        <v>0.015</v>
       </c>
       <c r="V12" t="n">
         <v>0.038</v>
@@ -2037,68 +2069,68 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.823</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.806</v>
+        <v>0.796</v>
       </c>
       <c r="F13" t="n">
-        <v>0.802</v>
+        <v>0.791</v>
       </c>
       <c r="G13" t="n">
-        <v>0.794</v>
+        <v>0.781</v>
       </c>
       <c r="H13" t="n">
-        <v>0.789</v>
+        <v>0.764</v>
       </c>
       <c r="I13" t="n">
-        <v>0.774</v>
+        <v>0.754</v>
       </c>
       <c r="J13" t="n">
-        <v>0.757</v>
+        <v>0.745</v>
       </c>
       <c r="K13" t="n">
-        <v>0.741</v>
+        <v>0.728</v>
       </c>
       <c r="L13" t="n">
-        <v>0.716</v>
+        <v>0.698</v>
       </c>
       <c r="M13" t="n">
-        <v>0.703</v>
+        <v>0.667</v>
       </c>
       <c r="N13" t="n">
-        <v>0.674</v>
+        <v>0.629</v>
       </c>
       <c r="O13" t="n">
-        <v>0.635</v>
+        <v>0.593</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.552</v>
+        <v>0.493</v>
       </c>
       <c r="R13" t="n">
-        <v>0.48</v>
+        <v>0.425</v>
       </c>
       <c r="S13" t="n">
-        <v>0.403</v>
+        <v>0.324</v>
       </c>
       <c r="T13" t="n">
-        <v>0.288</v>
+        <v>0.221</v>
       </c>
       <c r="U13" t="n">
-        <v>0.157</v>
+        <v>0.115</v>
       </c>
       <c r="V13" t="n">
         <v>0.038</v>
@@ -2107,68 +2139,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.829</v>
       </c>
       <c r="C14" t="n">
-        <v>0.797</v>
+        <v>0.823</v>
       </c>
       <c r="D14" t="n">
-        <v>0.787</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.753</v>
+        <v>0.806</v>
       </c>
       <c r="F14" t="n">
-        <v>0.719</v>
+        <v>0.802</v>
       </c>
       <c r="G14" t="n">
-        <v>0.68</v>
+        <v>0.794</v>
       </c>
       <c r="H14" t="n">
-        <v>0.627</v>
+        <v>0.789</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="J14" t="n">
-        <v>0.498</v>
+        <v>0.757</v>
       </c>
       <c r="K14" t="n">
-        <v>0.457</v>
+        <v>0.741</v>
       </c>
       <c r="L14" t="n">
-        <v>0.404</v>
+        <v>0.716</v>
       </c>
       <c r="M14" t="n">
-        <v>0.343</v>
+        <v>0.703</v>
       </c>
       <c r="N14" t="n">
-        <v>0.263</v>
+        <v>0.674</v>
       </c>
       <c r="O14" t="n">
-        <v>0.209</v>
+        <v>0.635</v>
       </c>
       <c r="P14" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.106</v>
+        <v>0.552</v>
       </c>
       <c r="R14" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="S14" t="n">
-        <v>0.042</v>
+        <v>0.403</v>
       </c>
       <c r="T14" t="n">
-        <v>0.027</v>
+        <v>0.288</v>
       </c>
       <c r="U14" t="n">
-        <v>0.018</v>
+        <v>0.157</v>
       </c>
       <c r="V14" t="n">
         <v>0.038</v>
@@ -2177,68 +2209,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.829</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="D15" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="E15" t="n">
-        <v>0.759</v>
+        <v>0.753</v>
       </c>
       <c r="F15" t="n">
-        <v>0.751</v>
+        <v>0.719</v>
       </c>
       <c r="G15" t="n">
-        <v>0.716</v>
+        <v>0.68</v>
       </c>
       <c r="H15" t="n">
-        <v>0.679</v>
+        <v>0.627</v>
       </c>
       <c r="I15" t="n">
-        <v>0.636</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.585</v>
+        <v>0.498</v>
       </c>
       <c r="K15" t="n">
-        <v>0.524</v>
+        <v>0.457</v>
       </c>
       <c r="L15" t="n">
-        <v>0.471</v>
+        <v>0.404</v>
       </c>
       <c r="M15" t="n">
-        <v>0.413</v>
+        <v>0.343</v>
       </c>
       <c r="N15" t="n">
-        <v>0.351</v>
+        <v>0.263</v>
       </c>
       <c r="O15" t="n">
-        <v>0.286</v>
+        <v>0.209</v>
       </c>
       <c r="P15" t="n">
-        <v>0.215</v>
+        <v>0.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.164</v>
+        <v>0.106</v>
       </c>
       <c r="R15" t="n">
-        <v>0.11</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.065</v>
+        <v>0.042</v>
       </c>
       <c r="T15" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="U15" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="V15" t="n">
         <v>0.038</v>
@@ -2247,68 +2279,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.822</v>
+        <v>0.8</v>
       </c>
       <c r="D16" t="n">
-        <v>0.799</v>
+        <v>0.785</v>
       </c>
       <c r="E16" t="n">
-        <v>0.773</v>
+        <v>0.759</v>
       </c>
       <c r="F16" t="n">
-        <v>0.744</v>
+        <v>0.751</v>
       </c>
       <c r="G16" t="n">
-        <v>0.729</v>
+        <v>0.716</v>
       </c>
       <c r="H16" t="n">
-        <v>0.714</v>
+        <v>0.679</v>
       </c>
       <c r="I16" t="n">
-        <v>0.667</v>
+        <v>0.636</v>
       </c>
       <c r="J16" t="n">
-        <v>0.633</v>
+        <v>0.585</v>
       </c>
       <c r="K16" t="n">
-        <v>0.608</v>
+        <v>0.524</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.471</v>
       </c>
       <c r="M16" t="n">
-        <v>0.525</v>
+        <v>0.413</v>
       </c>
       <c r="N16" t="n">
-        <v>0.486</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
-        <v>0.448</v>
+        <v>0.286</v>
       </c>
       <c r="P16" t="n">
-        <v>0.419</v>
+        <v>0.215</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.372</v>
+        <v>0.164</v>
       </c>
       <c r="R16" t="n">
-        <v>0.326</v>
+        <v>0.11</v>
       </c>
       <c r="S16" t="n">
-        <v>0.243</v>
+        <v>0.065</v>
       </c>
       <c r="T16" t="n">
-        <v>0.185</v>
+        <v>0.038</v>
       </c>
       <c r="U16" t="n">
-        <v>0.116</v>
+        <v>0.017</v>
       </c>
       <c r="V16" t="n">
         <v>0.038</v>
@@ -2317,68 +2349,68 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.829</v>
       </c>
       <c r="C17" t="n">
-        <v>0.775</v>
+        <v>0.822</v>
       </c>
       <c r="D17" t="n">
-        <v>0.725</v>
+        <v>0.799</v>
       </c>
       <c r="E17" t="n">
-        <v>0.671</v>
+        <v>0.773</v>
       </c>
       <c r="F17" t="n">
-        <v>0.613</v>
+        <v>0.744</v>
       </c>
       <c r="G17" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="L17" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.234</v>
-      </c>
       <c r="M17" t="n">
-        <v>0.17</v>
+        <v>0.525</v>
       </c>
       <c r="N17" t="n">
-        <v>0.108</v>
+        <v>0.486</v>
       </c>
       <c r="O17" t="n">
-        <v>0.066</v>
+        <v>0.448</v>
       </c>
       <c r="P17" t="n">
-        <v>0.045</v>
+        <v>0.419</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.028</v>
+        <v>0.372</v>
       </c>
       <c r="R17" t="n">
-        <v>0.016</v>
+        <v>0.326</v>
       </c>
       <c r="S17" t="n">
-        <v>0.013</v>
+        <v>0.243</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01</v>
+        <v>0.185</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01</v>
+        <v>0.116</v>
       </c>
       <c r="V17" t="n">
         <v>0.038</v>
@@ -2387,68 +2419,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.829</v>
       </c>
       <c r="C18" t="n">
-        <v>0.803</v>
+        <v>0.775</v>
       </c>
       <c r="D18" t="n">
-        <v>0.783</v>
+        <v>0.725</v>
       </c>
       <c r="E18" t="n">
-        <v>0.751</v>
+        <v>0.671</v>
       </c>
       <c r="F18" t="n">
-        <v>0.705</v>
+        <v>0.613</v>
       </c>
       <c r="G18" t="n">
-        <v>0.666</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.608</v>
+        <v>0.506</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.449</v>
       </c>
       <c r="J18" t="n">
-        <v>0.509</v>
+        <v>0.38</v>
       </c>
       <c r="K18" t="n">
-        <v>0.444</v>
+        <v>0.303</v>
       </c>
       <c r="L18" t="n">
-        <v>0.378</v>
+        <v>0.234</v>
       </c>
       <c r="M18" t="n">
-        <v>0.309</v>
+        <v>0.17</v>
       </c>
       <c r="N18" t="n">
-        <v>0.248</v>
+        <v>0.108</v>
       </c>
       <c r="O18" t="n">
-        <v>0.187</v>
+        <v>0.066</v>
       </c>
       <c r="P18" t="n">
-        <v>0.132</v>
+        <v>0.045</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.095</v>
+        <v>0.028</v>
       </c>
       <c r="R18" t="n">
-        <v>0.06</v>
+        <v>0.016</v>
       </c>
       <c r="S18" t="n">
-        <v>0.042</v>
+        <v>0.013</v>
       </c>
       <c r="T18" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="V18" t="n">
         <v>0.038</v>
@@ -2457,68 +2489,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.82</v>
+        <v>0.803</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.783</v>
       </c>
       <c r="E19" t="n">
-        <v>0.799</v>
+        <v>0.751</v>
       </c>
       <c r="F19" t="n">
-        <v>0.789</v>
+        <v>0.705</v>
       </c>
       <c r="G19" t="n">
-        <v>0.775</v>
+        <v>0.666</v>
       </c>
       <c r="H19" t="n">
-        <v>0.743</v>
+        <v>0.608</v>
       </c>
       <c r="I19" t="n">
-        <v>0.715</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.699</v>
+        <v>0.509</v>
       </c>
       <c r="K19" t="n">
-        <v>0.662</v>
+        <v>0.444</v>
       </c>
       <c r="L19" t="n">
-        <v>0.607</v>
+        <v>0.378</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.309</v>
       </c>
       <c r="N19" t="n">
-        <v>0.526</v>
+        <v>0.248</v>
       </c>
       <c r="O19" t="n">
-        <v>0.492</v>
+        <v>0.187</v>
       </c>
       <c r="P19" t="n">
-        <v>0.453</v>
+        <v>0.132</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.409</v>
+        <v>0.095</v>
       </c>
       <c r="R19" t="n">
-        <v>0.344</v>
+        <v>0.06</v>
       </c>
       <c r="S19" t="n">
-        <v>0.27</v>
+        <v>0.042</v>
       </c>
       <c r="T19" t="n">
-        <v>0.194</v>
+        <v>0.024</v>
       </c>
       <c r="U19" t="n">
-        <v>0.092</v>
+        <v>0.013</v>
       </c>
       <c r="V19" t="n">
         <v>0.038</v>
@@ -2527,70 +2559,140 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>sumDino</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B21" t="n">
         <v>0.829</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>0.822</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>0.8129999999999999</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>0.783</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>0.757</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>0.732</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>0.695</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>0.654</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>0.617</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>0.506</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>0.436</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>0.391</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>0.336</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P21" t="n">
         <v>0.286</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q21" t="n">
         <v>0.224</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>0.173</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>0.125</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>0.066</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>0.042</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V21" t="n">
         <v>0.038</v>
       </c>
     </row>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -784,38 +784,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="19"/>
-          <order val="19"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$21:$V$21</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -889,7 +857,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1199,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1376,61 +1344,61 @@
         <v>0.829</v>
       </c>
       <c r="C3" t="n">
-        <v>0.821</v>
+        <v>0.827</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.794</v>
+        <v>0.795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.789</v>
+        <v>0.792</v>
       </c>
       <c r="G3" t="n">
-        <v>0.776</v>
+        <v>0.782</v>
       </c>
       <c r="H3" t="n">
-        <v>0.762</v>
+        <v>0.772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.744</v>
+        <v>0.748</v>
       </c>
       <c r="J3" t="n">
-        <v>0.72</v>
+        <v>0.725</v>
       </c>
       <c r="K3" t="n">
-        <v>0.703</v>
+        <v>0.707</v>
       </c>
       <c r="L3" t="n">
-        <v>0.678</v>
+        <v>0.697</v>
       </c>
       <c r="M3" t="n">
-        <v>0.658</v>
+        <v>0.659</v>
       </c>
       <c r="N3" t="n">
-        <v>0.622</v>
+        <v>0.642</v>
       </c>
       <c r="O3" t="n">
-        <v>0.596</v>
+        <v>0.602</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.573</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.516</v>
+        <v>0.521</v>
       </c>
       <c r="R3" t="n">
-        <v>0.44</v>
+        <v>0.451</v>
       </c>
       <c r="S3" t="n">
-        <v>0.359</v>
+        <v>0.374</v>
       </c>
       <c r="T3" t="n">
-        <v>0.271</v>
+        <v>0.285</v>
       </c>
       <c r="U3" t="n">
-        <v>0.152</v>
+        <v>0.166</v>
       </c>
       <c r="V3" t="n">
         <v>0.038</v>
@@ -1859,68 +1827,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dinov2_pca_gaussian</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.829</v>
       </c>
       <c r="C10" t="n">
-        <v>0.823</v>
+        <v>0.827</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="E10" t="n">
-        <v>0.796</v>
+        <v>0.831</v>
       </c>
       <c r="F10" t="n">
-        <v>0.775</v>
+        <v>0.821</v>
       </c>
       <c r="G10" t="n">
-        <v>0.761</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H10" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="L10" t="n">
         <v>0.742</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.628</v>
-      </c>
       <c r="M10" t="n">
-        <v>0.598</v>
+        <v>0.727</v>
       </c>
       <c r="N10" t="n">
-        <v>0.555</v>
+        <v>0.701</v>
       </c>
       <c r="O10" t="n">
-        <v>0.51</v>
+        <v>0.668</v>
       </c>
       <c r="P10" t="n">
-        <v>0.457</v>
+        <v>0.637</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.398</v>
+        <v>0.582</v>
       </c>
       <c r="R10" t="n">
-        <v>0.329</v>
+        <v>0.533</v>
       </c>
       <c r="S10" t="n">
-        <v>0.26</v>
+        <v>0.458</v>
       </c>
       <c r="T10" t="n">
-        <v>0.179</v>
+        <v>0.337</v>
       </c>
       <c r="U10" t="n">
-        <v>0.111</v>
+        <v>0.184</v>
       </c>
       <c r="V10" t="n">
         <v>0.038</v>
@@ -1929,68 +1897,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.829</v>
       </c>
       <c r="C11" t="n">
-        <v>0.827</v>
+        <v>0.804</v>
       </c>
       <c r="D11" t="n">
-        <v>0.826</v>
+        <v>0.784</v>
       </c>
       <c r="E11" t="n">
-        <v>0.831</v>
+        <v>0.763</v>
       </c>
       <c r="F11" t="n">
-        <v>0.821</v>
+        <v>0.745</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.711</v>
       </c>
       <c r="H11" t="n">
-        <v>0.806</v>
+        <v>0.662</v>
       </c>
       <c r="I11" t="n">
-        <v>0.795</v>
+        <v>0.632</v>
       </c>
       <c r="J11" t="n">
-        <v>0.778</v>
+        <v>0.576</v>
       </c>
       <c r="K11" t="n">
-        <v>0.768</v>
+        <v>0.53</v>
       </c>
       <c r="L11" t="n">
-        <v>0.742</v>
+        <v>0.469</v>
       </c>
       <c r="M11" t="n">
-        <v>0.727</v>
+        <v>0.403</v>
       </c>
       <c r="N11" t="n">
-        <v>0.701</v>
+        <v>0.348</v>
       </c>
       <c r="O11" t="n">
-        <v>0.668</v>
+        <v>0.285</v>
       </c>
       <c r="P11" t="n">
-        <v>0.637</v>
+        <v>0.215</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.582</v>
+        <v>0.152</v>
       </c>
       <c r="R11" t="n">
-        <v>0.533</v>
+        <v>0.111</v>
       </c>
       <c r="S11" t="n">
-        <v>0.458</v>
+        <v>0.066</v>
       </c>
       <c r="T11" t="n">
-        <v>0.337</v>
+        <v>0.035</v>
       </c>
       <c r="U11" t="n">
-        <v>0.184</v>
+        <v>0.015</v>
       </c>
       <c r="V11" t="n">
         <v>0.038</v>
@@ -1999,68 +1967,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.804</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.784</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.763</v>
+        <v>0.796</v>
       </c>
       <c r="F12" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.745</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.576</v>
-      </c>
       <c r="K12" t="n">
-        <v>0.53</v>
+        <v>0.728</v>
       </c>
       <c r="L12" t="n">
-        <v>0.469</v>
+        <v>0.698</v>
       </c>
       <c r="M12" t="n">
-        <v>0.403</v>
+        <v>0.667</v>
       </c>
       <c r="N12" t="n">
-        <v>0.348</v>
+        <v>0.629</v>
       </c>
       <c r="O12" t="n">
-        <v>0.285</v>
+        <v>0.593</v>
       </c>
       <c r="P12" t="n">
-        <v>0.215</v>
+        <v>0.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.152</v>
+        <v>0.493</v>
       </c>
       <c r="R12" t="n">
-        <v>0.111</v>
+        <v>0.425</v>
       </c>
       <c r="S12" t="n">
-        <v>0.066</v>
+        <v>0.324</v>
       </c>
       <c r="T12" t="n">
-        <v>0.035</v>
+        <v>0.221</v>
       </c>
       <c r="U12" t="n">
-        <v>0.015</v>
+        <v>0.115</v>
       </c>
       <c r="V12" t="n">
         <v>0.038</v>
@@ -2069,68 +2037,68 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.823</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.796</v>
+        <v>0.806</v>
       </c>
       <c r="F13" t="n">
-        <v>0.791</v>
+        <v>0.802</v>
       </c>
       <c r="G13" t="n">
-        <v>0.781</v>
+        <v>0.794</v>
       </c>
       <c r="H13" t="n">
-        <v>0.764</v>
+        <v>0.789</v>
       </c>
       <c r="I13" t="n">
-        <v>0.754</v>
+        <v>0.774</v>
       </c>
       <c r="J13" t="n">
-        <v>0.745</v>
+        <v>0.757</v>
       </c>
       <c r="K13" t="n">
-        <v>0.728</v>
+        <v>0.741</v>
       </c>
       <c r="L13" t="n">
-        <v>0.698</v>
+        <v>0.716</v>
       </c>
       <c r="M13" t="n">
-        <v>0.667</v>
+        <v>0.703</v>
       </c>
       <c r="N13" t="n">
-        <v>0.629</v>
+        <v>0.674</v>
       </c>
       <c r="O13" t="n">
-        <v>0.593</v>
+        <v>0.635</v>
       </c>
       <c r="P13" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.493</v>
+        <v>0.552</v>
       </c>
       <c r="R13" t="n">
-        <v>0.425</v>
+        <v>0.48</v>
       </c>
       <c r="S13" t="n">
-        <v>0.324</v>
+        <v>0.403</v>
       </c>
       <c r="T13" t="n">
-        <v>0.221</v>
+        <v>0.288</v>
       </c>
       <c r="U13" t="n">
-        <v>0.115</v>
+        <v>0.157</v>
       </c>
       <c r="V13" t="n">
         <v>0.038</v>
@@ -2139,68 +2107,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.829</v>
       </c>
       <c r="C14" t="n">
-        <v>0.823</v>
+        <v>0.797</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="E14" t="n">
-        <v>0.806</v>
+        <v>0.753</v>
       </c>
       <c r="F14" t="n">
-        <v>0.802</v>
+        <v>0.719</v>
       </c>
       <c r="G14" t="n">
-        <v>0.794</v>
+        <v>0.68</v>
       </c>
       <c r="H14" t="n">
-        <v>0.789</v>
+        <v>0.627</v>
       </c>
       <c r="I14" t="n">
-        <v>0.774</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.757</v>
+        <v>0.498</v>
       </c>
       <c r="K14" t="n">
-        <v>0.741</v>
+        <v>0.457</v>
       </c>
       <c r="L14" t="n">
-        <v>0.716</v>
+        <v>0.404</v>
       </c>
       <c r="M14" t="n">
-        <v>0.703</v>
+        <v>0.343</v>
       </c>
       <c r="N14" t="n">
-        <v>0.674</v>
+        <v>0.263</v>
       </c>
       <c r="O14" t="n">
-        <v>0.635</v>
+        <v>0.209</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.552</v>
+        <v>0.106</v>
       </c>
       <c r="R14" t="n">
-        <v>0.48</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.403</v>
+        <v>0.042</v>
       </c>
       <c r="T14" t="n">
-        <v>0.288</v>
+        <v>0.027</v>
       </c>
       <c r="U14" t="n">
-        <v>0.157</v>
+        <v>0.018</v>
       </c>
       <c r="V14" t="n">
         <v>0.038</v>
@@ -2209,68 +2177,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.829</v>
       </c>
       <c r="C15" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="D15" t="n">
-        <v>0.787</v>
+        <v>0.785</v>
       </c>
       <c r="E15" t="n">
-        <v>0.753</v>
+        <v>0.759</v>
       </c>
       <c r="F15" t="n">
-        <v>0.719</v>
+        <v>0.751</v>
       </c>
       <c r="G15" t="n">
-        <v>0.68</v>
+        <v>0.716</v>
       </c>
       <c r="H15" t="n">
-        <v>0.627</v>
+        <v>0.679</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="J15" t="n">
-        <v>0.498</v>
+        <v>0.585</v>
       </c>
       <c r="K15" t="n">
-        <v>0.457</v>
+        <v>0.524</v>
       </c>
       <c r="L15" t="n">
-        <v>0.404</v>
+        <v>0.471</v>
       </c>
       <c r="M15" t="n">
-        <v>0.343</v>
+        <v>0.413</v>
       </c>
       <c r="N15" t="n">
-        <v>0.263</v>
+        <v>0.351</v>
       </c>
       <c r="O15" t="n">
-        <v>0.209</v>
+        <v>0.286</v>
       </c>
       <c r="P15" t="n">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.106</v>
+        <v>0.164</v>
       </c>
       <c r="R15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="S15" t="n">
-        <v>0.042</v>
+        <v>0.065</v>
       </c>
       <c r="T15" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="U15" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="V15" t="n">
         <v>0.038</v>
@@ -2279,68 +2247,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8</v>
+        <v>0.822</v>
       </c>
       <c r="D16" t="n">
-        <v>0.785</v>
+        <v>0.799</v>
       </c>
       <c r="E16" t="n">
-        <v>0.759</v>
+        <v>0.773</v>
       </c>
       <c r="F16" t="n">
-        <v>0.751</v>
+        <v>0.744</v>
       </c>
       <c r="G16" t="n">
-        <v>0.716</v>
+        <v>0.729</v>
       </c>
       <c r="H16" t="n">
-        <v>0.679</v>
+        <v>0.714</v>
       </c>
       <c r="I16" t="n">
-        <v>0.636</v>
+        <v>0.667</v>
       </c>
       <c r="J16" t="n">
-        <v>0.585</v>
+        <v>0.633</v>
       </c>
       <c r="K16" t="n">
-        <v>0.524</v>
+        <v>0.608</v>
       </c>
       <c r="L16" t="n">
-        <v>0.471</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.413</v>
+        <v>0.525</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.486</v>
       </c>
       <c r="O16" t="n">
-        <v>0.286</v>
+        <v>0.448</v>
       </c>
       <c r="P16" t="n">
-        <v>0.215</v>
+        <v>0.419</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.164</v>
+        <v>0.372</v>
       </c>
       <c r="R16" t="n">
-        <v>0.11</v>
+        <v>0.326</v>
       </c>
       <c r="S16" t="n">
-        <v>0.065</v>
+        <v>0.243</v>
       </c>
       <c r="T16" t="n">
-        <v>0.038</v>
+        <v>0.185</v>
       </c>
       <c r="U16" t="n">
-        <v>0.017</v>
+        <v>0.116</v>
       </c>
       <c r="V16" t="n">
         <v>0.038</v>
@@ -2349,68 +2317,68 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.829</v>
       </c>
       <c r="C17" t="n">
-        <v>0.822</v>
+        <v>0.775</v>
       </c>
       <c r="D17" t="n">
-        <v>0.799</v>
+        <v>0.725</v>
       </c>
       <c r="E17" t="n">
-        <v>0.773</v>
+        <v>0.671</v>
       </c>
       <c r="F17" t="n">
-        <v>0.744</v>
+        <v>0.613</v>
       </c>
       <c r="G17" t="n">
-        <v>0.729</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.714</v>
+        <v>0.506</v>
       </c>
       <c r="I17" t="n">
-        <v>0.667</v>
+        <v>0.449</v>
       </c>
       <c r="J17" t="n">
-        <v>0.633</v>
+        <v>0.38</v>
       </c>
       <c r="K17" t="n">
-        <v>0.608</v>
+        <v>0.303</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.234</v>
       </c>
       <c r="M17" t="n">
-        <v>0.525</v>
+        <v>0.17</v>
       </c>
       <c r="N17" t="n">
-        <v>0.486</v>
+        <v>0.108</v>
       </c>
       <c r="O17" t="n">
-        <v>0.448</v>
+        <v>0.066</v>
       </c>
       <c r="P17" t="n">
-        <v>0.419</v>
+        <v>0.045</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.372</v>
+        <v>0.028</v>
       </c>
       <c r="R17" t="n">
-        <v>0.326</v>
+        <v>0.016</v>
       </c>
       <c r="S17" t="n">
-        <v>0.243</v>
+        <v>0.013</v>
       </c>
       <c r="T17" t="n">
-        <v>0.185</v>
+        <v>0.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0.116</v>
+        <v>0.01</v>
       </c>
       <c r="V17" t="n">
         <v>0.038</v>
@@ -2419,68 +2387,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.829</v>
       </c>
       <c r="C18" t="n">
-        <v>0.775</v>
+        <v>0.803</v>
       </c>
       <c r="D18" t="n">
-        <v>0.725</v>
+        <v>0.783</v>
       </c>
       <c r="E18" t="n">
-        <v>0.671</v>
+        <v>0.751</v>
       </c>
       <c r="F18" t="n">
-        <v>0.613</v>
+        <v>0.705</v>
       </c>
       <c r="G18" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.449</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.38</v>
+        <v>0.509</v>
       </c>
       <c r="K18" t="n">
-        <v>0.303</v>
+        <v>0.444</v>
       </c>
       <c r="L18" t="n">
-        <v>0.234</v>
+        <v>0.378</v>
       </c>
       <c r="M18" t="n">
-        <v>0.17</v>
+        <v>0.309</v>
       </c>
       <c r="N18" t="n">
-        <v>0.108</v>
+        <v>0.248</v>
       </c>
       <c r="O18" t="n">
-        <v>0.066</v>
+        <v>0.187</v>
       </c>
       <c r="P18" t="n">
-        <v>0.045</v>
+        <v>0.132</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.028</v>
+        <v>0.095</v>
       </c>
       <c r="R18" t="n">
-        <v>0.016</v>
+        <v>0.06</v>
       </c>
       <c r="S18" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U18" t="n">
         <v>0.013</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.01</v>
       </c>
       <c r="V18" t="n">
         <v>0.038</v>
@@ -2489,68 +2457,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>sumDino</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.803</v>
+        <v>0.82</v>
       </c>
       <c r="D19" t="n">
-        <v>0.783</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.751</v>
+        <v>0.799</v>
       </c>
       <c r="F19" t="n">
-        <v>0.705</v>
+        <v>0.789</v>
       </c>
       <c r="G19" t="n">
-        <v>0.666</v>
+        <v>0.775</v>
       </c>
       <c r="H19" t="n">
-        <v>0.608</v>
+        <v>0.743</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.715</v>
       </c>
       <c r="J19" t="n">
-        <v>0.509</v>
+        <v>0.699</v>
       </c>
       <c r="K19" t="n">
-        <v>0.444</v>
+        <v>0.662</v>
       </c>
       <c r="L19" t="n">
-        <v>0.378</v>
+        <v>0.607</v>
       </c>
       <c r="M19" t="n">
-        <v>0.309</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.248</v>
+        <v>0.526</v>
       </c>
       <c r="O19" t="n">
-        <v>0.187</v>
+        <v>0.492</v>
       </c>
       <c r="P19" t="n">
-        <v>0.132</v>
+        <v>0.453</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.095</v>
+        <v>0.409</v>
       </c>
       <c r="R19" t="n">
-        <v>0.06</v>
+        <v>0.344</v>
       </c>
       <c r="S19" t="n">
-        <v>0.042</v>
+        <v>0.27</v>
       </c>
       <c r="T19" t="n">
-        <v>0.024</v>
+        <v>0.194</v>
       </c>
       <c r="U19" t="n">
-        <v>0.013</v>
+        <v>0.092</v>
       </c>
       <c r="V19" t="n">
         <v>0.038</v>
@@ -2559,140 +2527,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0.829</v>
       </c>
       <c r="C20" t="n">
-        <v>0.82</v>
+        <v>0.822</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.799</v>
+        <v>0.783</v>
       </c>
       <c r="F20" t="n">
-        <v>0.789</v>
+        <v>0.757</v>
       </c>
       <c r="G20" t="n">
-        <v>0.775</v>
+        <v>0.732</v>
       </c>
       <c r="H20" t="n">
-        <v>0.743</v>
+        <v>0.695</v>
       </c>
       <c r="I20" t="n">
-        <v>0.715</v>
+        <v>0.654</v>
       </c>
       <c r="J20" t="n">
-        <v>0.699</v>
+        <v>0.617</v>
       </c>
       <c r="K20" t="n">
-        <v>0.662</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.607</v>
+        <v>0.506</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.436</v>
       </c>
       <c r="N20" t="n">
-        <v>0.526</v>
+        <v>0.391</v>
       </c>
       <c r="O20" t="n">
-        <v>0.492</v>
+        <v>0.336</v>
       </c>
       <c r="P20" t="n">
-        <v>0.453</v>
+        <v>0.286</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.409</v>
+        <v>0.224</v>
       </c>
       <c r="R20" t="n">
-        <v>0.344</v>
+        <v>0.173</v>
       </c>
       <c r="S20" t="n">
-        <v>0.27</v>
+        <v>0.125</v>
       </c>
       <c r="T20" t="n">
-        <v>0.194</v>
+        <v>0.066</v>
       </c>
       <c r="U20" t="n">
-        <v>0.092</v>
+        <v>0.042</v>
       </c>
       <c r="V20" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="V21" t="n">
         <v>0.038</v>
       </c>
     </row>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -1347,58 +1347,58 @@
         <v>0.827</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.795</v>
+        <v>0.801</v>
       </c>
       <c r="F3" t="n">
-        <v>0.792</v>
+        <v>0.789</v>
       </c>
       <c r="G3" t="n">
         <v>0.782</v>
       </c>
       <c r="H3" t="n">
-        <v>0.772</v>
+        <v>0.775</v>
       </c>
       <c r="I3" t="n">
-        <v>0.748</v>
+        <v>0.753</v>
       </c>
       <c r="J3" t="n">
-        <v>0.725</v>
+        <v>0.733</v>
       </c>
       <c r="K3" t="n">
-        <v>0.707</v>
+        <v>0.718</v>
       </c>
       <c r="L3" t="n">
-        <v>0.697</v>
+        <v>0.698</v>
       </c>
       <c r="M3" t="n">
-        <v>0.659</v>
+        <v>0.67</v>
       </c>
       <c r="N3" t="n">
-        <v>0.642</v>
+        <v>0.643</v>
       </c>
       <c r="O3" t="n">
-        <v>0.602</v>
+        <v>0.615</v>
       </c>
       <c r="P3" t="n">
-        <v>0.573</v>
+        <v>0.575</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.521</v>
+        <v>0.53</v>
       </c>
       <c r="R3" t="n">
-        <v>0.451</v>
+        <v>0.468</v>
       </c>
       <c r="S3" t="n">
-        <v>0.374</v>
+        <v>0.381</v>
       </c>
       <c r="T3" t="n">
-        <v>0.285</v>
+        <v>0.288</v>
       </c>
       <c r="U3" t="n">
-        <v>0.166</v>
+        <v>0.173</v>
       </c>
       <c r="V3" t="n">
         <v>0.038</v>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -1344,61 +1344,61 @@
         <v>0.829</v>
       </c>
       <c r="C3" t="n">
-        <v>0.827</v>
+        <v>0.826</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.801</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.789</v>
+        <v>0.796</v>
       </c>
       <c r="G3" t="n">
-        <v>0.782</v>
+        <v>0.787</v>
       </c>
       <c r="H3" t="n">
-        <v>0.775</v>
+        <v>0.781</v>
       </c>
       <c r="I3" t="n">
-        <v>0.753</v>
+        <v>0.755</v>
       </c>
       <c r="J3" t="n">
-        <v>0.733</v>
+        <v>0.74</v>
       </c>
       <c r="K3" t="n">
-        <v>0.718</v>
+        <v>0.716</v>
       </c>
       <c r="L3" t="n">
-        <v>0.698</v>
+        <v>0.707</v>
       </c>
       <c r="M3" t="n">
-        <v>0.67</v>
+        <v>0.681</v>
       </c>
       <c r="N3" t="n">
-        <v>0.643</v>
+        <v>0.661</v>
       </c>
       <c r="O3" t="n">
-        <v>0.615</v>
+        <v>0.617</v>
       </c>
       <c r="P3" t="n">
-        <v>0.575</v>
+        <v>0.57</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.53</v>
+        <v>0.525</v>
       </c>
       <c r="R3" t="n">
-        <v>0.468</v>
+        <v>0.48</v>
       </c>
       <c r="S3" t="n">
-        <v>0.381</v>
+        <v>0.392</v>
       </c>
       <c r="T3" t="n">
-        <v>0.288</v>
+        <v>0.297</v>
       </c>
       <c r="U3" t="n">
-        <v>0.173</v>
+        <v>0.174</v>
       </c>
       <c r="V3" t="n">
         <v>0.038</v>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -784,6 +784,134 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$21:$V$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="20"/>
+          <order val="20"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$22:$V$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="21"/>
+          <order val="21"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A23</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$23:$V$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="22"/>
+          <order val="22"/>
+          <tx>
+            <strRef>
+              <f>'Data'!A24</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$B$24:$V$24</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -857,7 +985,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1167,10 +1295,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
@@ -1267,68 +1395,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>c3f</t>
+          <t>U2Net-Saliency</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.829</v>
       </c>
       <c r="C2" t="n">
-        <v>0.824</v>
+        <v>0.826</v>
       </c>
       <c r="D2" t="n">
-        <v>0.825</v>
+        <v>0.826</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.802</v>
       </c>
       <c r="G2" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="H2" t="n">
-        <v>0.772</v>
+        <v>0.778</v>
       </c>
       <c r="I2" t="n">
-        <v>0.757</v>
+        <v>0.767</v>
       </c>
       <c r="J2" t="n">
-        <v>0.737</v>
+        <v>0.733</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.706</v>
       </c>
       <c r="L2" t="n">
-        <v>0.604</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.669</v>
       </c>
       <c r="N2" t="n">
-        <v>0.54</v>
+        <v>0.636</v>
       </c>
       <c r="O2" t="n">
-        <v>0.527</v>
+        <v>0.582</v>
       </c>
       <c r="P2" t="n">
-        <v>0.493</v>
+        <v>0.546</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.441</v>
+        <v>0.489</v>
       </c>
       <c r="R2" t="n">
-        <v>0.39</v>
+        <v>0.417</v>
       </c>
       <c r="S2" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="T2" t="n">
-        <v>0.261</v>
+        <v>0.23</v>
       </c>
       <c r="U2" t="n">
-        <v>0.129</v>
+        <v>0.117</v>
       </c>
       <c r="V2" t="n">
         <v>0.038</v>
@@ -1337,68 +1465,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_ENT_SMOOTH</t>
+          <t>c3f</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.829</v>
       </c>
       <c r="C3" t="n">
-        <v>0.826</v>
+        <v>0.824</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="E3" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.8070000000000001</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.796</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.787</v>
+        <v>0.797</v>
       </c>
       <c r="H3" t="n">
-        <v>0.781</v>
+        <v>0.772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="J3" t="n">
-        <v>0.74</v>
+        <v>0.737</v>
       </c>
       <c r="K3" t="n">
-        <v>0.716</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0.707</v>
+        <v>0.604</v>
       </c>
       <c r="M3" t="n">
-        <v>0.681</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.661</v>
+        <v>0.54</v>
       </c>
       <c r="O3" t="n">
-        <v>0.617</v>
+        <v>0.527</v>
       </c>
       <c r="P3" t="n">
-        <v>0.57</v>
+        <v>0.493</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.525</v>
+        <v>0.441</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="S3" t="n">
-        <v>0.392</v>
+        <v>0.338</v>
       </c>
       <c r="T3" t="n">
-        <v>0.297</v>
+        <v>0.261</v>
       </c>
       <c r="U3" t="n">
-        <v>0.174</v>
+        <v>0.129</v>
       </c>
       <c r="V3" t="n">
         <v>0.038</v>
@@ -1407,68 +1535,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.829</v>
       </c>
       <c r="C4" t="n">
-        <v>0.827</v>
+        <v>0.823</v>
       </c>
       <c r="D4" t="n">
-        <v>0.797</v>
+        <v>0.82</v>
       </c>
       <c r="E4" t="n">
-        <v>0.788</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.771</v>
+        <v>0.806</v>
       </c>
       <c r="G4" t="n">
-        <v>0.748</v>
+        <v>0.8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.739</v>
+        <v>0.779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.725</v>
+        <v>0.758</v>
       </c>
       <c r="J4" t="n">
-        <v>0.704</v>
+        <v>0.737</v>
       </c>
       <c r="K4" t="n">
-        <v>0.679</v>
+        <v>0.723</v>
       </c>
       <c r="L4" t="n">
-        <v>0.649</v>
+        <v>0.709</v>
       </c>
       <c r="M4" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.622</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.533</v>
-      </c>
       <c r="P4" t="n">
-        <v>0.476</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.426</v>
+        <v>0.528</v>
       </c>
       <c r="R4" t="n">
-        <v>0.354</v>
+        <v>0.472</v>
       </c>
       <c r="S4" t="n">
-        <v>0.243</v>
+        <v>0.379</v>
       </c>
       <c r="T4" t="n">
-        <v>0.166</v>
+        <v>0.291</v>
       </c>
       <c r="U4" t="n">
-        <v>0.078</v>
+        <v>0.177</v>
       </c>
       <c r="V4" t="n">
         <v>0.038</v>
@@ -1477,68 +1605,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.82</v>
+        <v>0.827</v>
       </c>
       <c r="D5" t="n">
-        <v>0.806</v>
+        <v>0.797</v>
       </c>
       <c r="E5" t="n">
-        <v>0.792</v>
+        <v>0.788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.779</v>
+        <v>0.771</v>
       </c>
       <c r="G5" t="n">
-        <v>0.763</v>
+        <v>0.748</v>
       </c>
       <c r="H5" t="n">
-        <v>0.752</v>
+        <v>0.739</v>
       </c>
       <c r="I5" t="n">
-        <v>0.728</v>
+        <v>0.725</v>
       </c>
       <c r="J5" t="n">
-        <v>0.699</v>
+        <v>0.704</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="L5" t="n">
-        <v>0.662</v>
+        <v>0.649</v>
       </c>
       <c r="M5" t="n">
-        <v>0.63</v>
+        <v>0.622</v>
       </c>
       <c r="N5" t="n">
-        <v>0.581</v>
+        <v>0.588</v>
       </c>
       <c r="O5" t="n">
-        <v>0.549</v>
+        <v>0.533</v>
       </c>
       <c r="P5" t="n">
-        <v>0.501</v>
+        <v>0.476</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.436</v>
+        <v>0.426</v>
       </c>
       <c r="R5" t="n">
-        <v>0.369</v>
+        <v>0.354</v>
       </c>
       <c r="S5" t="n">
-        <v>0.272</v>
+        <v>0.243</v>
       </c>
       <c r="T5" t="n">
-        <v>0.19</v>
+        <v>0.166</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1</v>
+        <v>0.078</v>
       </c>
       <c r="V5" t="n">
         <v>0.038</v>
@@ -1547,68 +1675,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>dinov2_ENT</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.829</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="D6" t="n">
-        <v>0.795</v>
+        <v>0.806</v>
       </c>
       <c r="E6" t="n">
-        <v>0.78</v>
+        <v>0.792</v>
       </c>
       <c r="F6" t="n">
-        <v>0.773</v>
+        <v>0.779</v>
       </c>
       <c r="G6" t="n">
-        <v>0.746</v>
+        <v>0.763</v>
       </c>
       <c r="H6" t="n">
-        <v>0.731</v>
+        <v>0.752</v>
       </c>
       <c r="I6" t="n">
-        <v>0.71</v>
+        <v>0.728</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="K6" t="n">
-        <v>0.673</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.641</v>
+        <v>0.662</v>
       </c>
       <c r="M6" t="n">
-        <v>0.608</v>
+        <v>0.63</v>
       </c>
       <c r="N6" t="n">
-        <v>0.58</v>
+        <v>0.581</v>
       </c>
       <c r="O6" t="n">
-        <v>0.53</v>
+        <v>0.549</v>
       </c>
       <c r="P6" t="n">
-        <v>0.463</v>
+        <v>0.501</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.393</v>
+        <v>0.436</v>
       </c>
       <c r="R6" t="n">
-        <v>0.314</v>
+        <v>0.369</v>
       </c>
       <c r="S6" t="n">
-        <v>0.245</v>
+        <v>0.272</v>
       </c>
       <c r="T6" t="n">
-        <v>0.156</v>
+        <v>0.19</v>
       </c>
       <c r="U6" t="n">
-        <v>0.068</v>
+        <v>0.1</v>
       </c>
       <c r="V6" t="n">
         <v>0.038</v>
@@ -1617,7 +1745,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1687,68 +1815,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>dinov2_PC_EV</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.829</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.778</v>
+        <v>0.795</v>
       </c>
       <c r="E8" t="n">
-        <v>0.744</v>
+        <v>0.78</v>
       </c>
       <c r="F8" t="n">
-        <v>0.704</v>
+        <v>0.773</v>
       </c>
       <c r="G8" t="n">
-        <v>0.663</v>
+        <v>0.746</v>
       </c>
       <c r="H8" t="n">
-        <v>0.636</v>
+        <v>0.731</v>
       </c>
       <c r="I8" t="n">
-        <v>0.578</v>
+        <v>0.71</v>
       </c>
       <c r="J8" t="n">
-        <v>0.546</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.509</v>
+        <v>0.673</v>
       </c>
       <c r="L8" t="n">
-        <v>0.468</v>
+        <v>0.641</v>
       </c>
       <c r="M8" t="n">
-        <v>0.42</v>
+        <v>0.608</v>
       </c>
       <c r="N8" t="n">
-        <v>0.379</v>
+        <v>0.58</v>
       </c>
       <c r="O8" t="n">
-        <v>0.322</v>
+        <v>0.53</v>
       </c>
       <c r="P8" t="n">
-        <v>0.286</v>
+        <v>0.463</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.246</v>
+        <v>0.393</v>
       </c>
       <c r="R8" t="n">
-        <v>0.222</v>
+        <v>0.314</v>
       </c>
       <c r="S8" t="n">
-        <v>0.198</v>
+        <v>0.245</v>
       </c>
       <c r="T8" t="n">
-        <v>0.132</v>
+        <v>0.156</v>
       </c>
       <c r="U8" t="n">
-        <v>0.075</v>
+        <v>0.068</v>
       </c>
       <c r="V8" t="n">
         <v>0.038</v>
@@ -1757,68 +1885,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_PC_L2</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.829</v>
       </c>
       <c r="C9" t="n">
-        <v>0.82</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.778</v>
       </c>
       <c r="E9" t="n">
-        <v>0.797</v>
+        <v>0.744</v>
       </c>
       <c r="F9" t="n">
-        <v>0.781</v>
+        <v>0.704</v>
       </c>
       <c r="G9" t="n">
-        <v>0.772</v>
+        <v>0.663</v>
       </c>
       <c r="H9" t="n">
-        <v>0.758</v>
+        <v>0.636</v>
       </c>
       <c r="I9" t="n">
-        <v>0.733</v>
+        <v>0.578</v>
       </c>
       <c r="J9" t="n">
-        <v>0.705</v>
+        <v>0.546</v>
       </c>
       <c r="K9" t="n">
-        <v>0.672</v>
+        <v>0.509</v>
       </c>
       <c r="L9" t="n">
-        <v>0.656</v>
+        <v>0.468</v>
       </c>
       <c r="M9" t="n">
-        <v>0.61</v>
+        <v>0.42</v>
       </c>
       <c r="N9" t="n">
-        <v>0.569</v>
+        <v>0.379</v>
       </c>
       <c r="O9" t="n">
-        <v>0.533</v>
+        <v>0.322</v>
       </c>
       <c r="P9" t="n">
-        <v>0.478</v>
+        <v>0.286</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.417</v>
+        <v>0.246</v>
       </c>
       <c r="R9" t="n">
-        <v>0.343</v>
+        <v>0.222</v>
       </c>
       <c r="S9" t="n">
-        <v>0.262</v>
+        <v>0.198</v>
       </c>
       <c r="T9" t="n">
-        <v>0.191</v>
+        <v>0.132</v>
       </c>
       <c r="U9" t="n">
-        <v>0.106</v>
+        <v>0.075</v>
       </c>
       <c r="V9" t="n">
         <v>0.038</v>
@@ -1827,68 +1955,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.829</v>
       </c>
       <c r="C10" t="n">
-        <v>0.827</v>
+        <v>0.82</v>
       </c>
       <c r="D10" t="n">
-        <v>0.826</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.831</v>
+        <v>0.797</v>
       </c>
       <c r="F10" t="n">
-        <v>0.821</v>
+        <v>0.781</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="H10" t="n">
-        <v>0.806</v>
+        <v>0.758</v>
       </c>
       <c r="I10" t="n">
-        <v>0.795</v>
+        <v>0.733</v>
       </c>
       <c r="J10" t="n">
-        <v>0.778</v>
+        <v>0.705</v>
       </c>
       <c r="K10" t="n">
-        <v>0.768</v>
+        <v>0.672</v>
       </c>
       <c r="L10" t="n">
-        <v>0.742</v>
+        <v>0.656</v>
       </c>
       <c r="M10" t="n">
-        <v>0.727</v>
+        <v>0.61</v>
       </c>
       <c r="N10" t="n">
-        <v>0.701</v>
+        <v>0.569</v>
       </c>
       <c r="O10" t="n">
-        <v>0.668</v>
+        <v>0.533</v>
       </c>
       <c r="P10" t="n">
-        <v>0.637</v>
+        <v>0.478</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.582</v>
+        <v>0.417</v>
       </c>
       <c r="R10" t="n">
-        <v>0.533</v>
+        <v>0.343</v>
       </c>
       <c r="S10" t="n">
-        <v>0.458</v>
+        <v>0.262</v>
       </c>
       <c r="T10" t="n">
-        <v>0.337</v>
+        <v>0.191</v>
       </c>
       <c r="U10" t="n">
-        <v>0.184</v>
+        <v>0.106</v>
       </c>
       <c r="V10" t="n">
         <v>0.038</v>
@@ -1897,68 +2025,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.829</v>
       </c>
       <c r="C11" t="n">
-        <v>0.804</v>
+        <v>0.827</v>
       </c>
       <c r="D11" t="n">
-        <v>0.784</v>
+        <v>0.826</v>
       </c>
       <c r="E11" t="n">
-        <v>0.763</v>
+        <v>0.831</v>
       </c>
       <c r="F11" t="n">
-        <v>0.745</v>
+        <v>0.821</v>
       </c>
       <c r="G11" t="n">
-        <v>0.711</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.662</v>
+        <v>0.806</v>
       </c>
       <c r="I11" t="n">
-        <v>0.632</v>
+        <v>0.795</v>
       </c>
       <c r="J11" t="n">
-        <v>0.576</v>
+        <v>0.778</v>
       </c>
       <c r="K11" t="n">
-        <v>0.53</v>
+        <v>0.768</v>
       </c>
       <c r="L11" t="n">
-        <v>0.469</v>
+        <v>0.742</v>
       </c>
       <c r="M11" t="n">
-        <v>0.403</v>
+        <v>0.727</v>
       </c>
       <c r="N11" t="n">
-        <v>0.348</v>
+        <v>0.701</v>
       </c>
       <c r="O11" t="n">
-        <v>0.285</v>
+        <v>0.668</v>
       </c>
       <c r="P11" t="n">
-        <v>0.215</v>
+        <v>0.637</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.152</v>
+        <v>0.582</v>
       </c>
       <c r="R11" t="n">
-        <v>0.111</v>
+        <v>0.533</v>
       </c>
       <c r="S11" t="n">
-        <v>0.066</v>
+        <v>0.458</v>
       </c>
       <c r="T11" t="n">
-        <v>0.035</v>
+        <v>0.337</v>
       </c>
       <c r="U11" t="n">
-        <v>0.015</v>
+        <v>0.184</v>
       </c>
       <c r="V11" t="n">
         <v>0.038</v>
@@ -1967,68 +2095,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.804</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="E12" t="n">
-        <v>0.796</v>
+        <v>0.763</v>
       </c>
       <c r="F12" t="n">
-        <v>0.791</v>
+        <v>0.745</v>
       </c>
       <c r="G12" t="n">
-        <v>0.781</v>
+        <v>0.711</v>
       </c>
       <c r="H12" t="n">
-        <v>0.764</v>
+        <v>0.662</v>
       </c>
       <c r="I12" t="n">
-        <v>0.754</v>
+        <v>0.632</v>
       </c>
       <c r="J12" t="n">
-        <v>0.745</v>
+        <v>0.576</v>
       </c>
       <c r="K12" t="n">
-        <v>0.728</v>
+        <v>0.53</v>
       </c>
       <c r="L12" t="n">
-        <v>0.698</v>
+        <v>0.469</v>
       </c>
       <c r="M12" t="n">
-        <v>0.667</v>
+        <v>0.403</v>
       </c>
       <c r="N12" t="n">
-        <v>0.629</v>
+        <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>0.593</v>
+        <v>0.285</v>
       </c>
       <c r="P12" t="n">
-        <v>0.55</v>
+        <v>0.215</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.493</v>
+        <v>0.152</v>
       </c>
       <c r="R12" t="n">
-        <v>0.425</v>
+        <v>0.111</v>
       </c>
       <c r="S12" t="n">
-        <v>0.324</v>
+        <v>0.066</v>
       </c>
       <c r="T12" t="n">
-        <v>0.221</v>
+        <v>0.035</v>
       </c>
       <c r="U12" t="n">
-        <v>0.115</v>
+        <v>0.015</v>
       </c>
       <c r="V12" t="n">
         <v>0.038</v>
@@ -2037,68 +2165,68 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.823</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.806</v>
+        <v>0.796</v>
       </c>
       <c r="F13" t="n">
-        <v>0.802</v>
+        <v>0.791</v>
       </c>
       <c r="G13" t="n">
-        <v>0.794</v>
+        <v>0.781</v>
       </c>
       <c r="H13" t="n">
-        <v>0.789</v>
+        <v>0.764</v>
       </c>
       <c r="I13" t="n">
-        <v>0.774</v>
+        <v>0.754</v>
       </c>
       <c r="J13" t="n">
-        <v>0.757</v>
+        <v>0.745</v>
       </c>
       <c r="K13" t="n">
-        <v>0.741</v>
+        <v>0.728</v>
       </c>
       <c r="L13" t="n">
-        <v>0.716</v>
+        <v>0.698</v>
       </c>
       <c r="M13" t="n">
-        <v>0.703</v>
+        <v>0.667</v>
       </c>
       <c r="N13" t="n">
-        <v>0.674</v>
+        <v>0.629</v>
       </c>
       <c r="O13" t="n">
-        <v>0.635</v>
+        <v>0.593</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.552</v>
+        <v>0.493</v>
       </c>
       <c r="R13" t="n">
-        <v>0.48</v>
+        <v>0.425</v>
       </c>
       <c r="S13" t="n">
-        <v>0.403</v>
+        <v>0.324</v>
       </c>
       <c r="T13" t="n">
-        <v>0.288</v>
+        <v>0.221</v>
       </c>
       <c r="U13" t="n">
-        <v>0.157</v>
+        <v>0.115</v>
       </c>
       <c r="V13" t="n">
         <v>0.038</v>
@@ -2107,68 +2235,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.829</v>
       </c>
       <c r="C14" t="n">
-        <v>0.797</v>
+        <v>0.823</v>
       </c>
       <c r="D14" t="n">
-        <v>0.787</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.753</v>
+        <v>0.806</v>
       </c>
       <c r="F14" t="n">
-        <v>0.719</v>
+        <v>0.802</v>
       </c>
       <c r="G14" t="n">
-        <v>0.68</v>
+        <v>0.794</v>
       </c>
       <c r="H14" t="n">
-        <v>0.627</v>
+        <v>0.789</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.774</v>
       </c>
       <c r="J14" t="n">
-        <v>0.498</v>
+        <v>0.757</v>
       </c>
       <c r="K14" t="n">
-        <v>0.457</v>
+        <v>0.741</v>
       </c>
       <c r="L14" t="n">
-        <v>0.404</v>
+        <v>0.716</v>
       </c>
       <c r="M14" t="n">
-        <v>0.343</v>
+        <v>0.703</v>
       </c>
       <c r="N14" t="n">
-        <v>0.263</v>
+        <v>0.674</v>
       </c>
       <c r="O14" t="n">
-        <v>0.209</v>
+        <v>0.635</v>
       </c>
       <c r="P14" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.106</v>
+        <v>0.552</v>
       </c>
       <c r="R14" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="S14" t="n">
-        <v>0.042</v>
+        <v>0.403</v>
       </c>
       <c r="T14" t="n">
-        <v>0.027</v>
+        <v>0.288</v>
       </c>
       <c r="U14" t="n">
-        <v>0.018</v>
+        <v>0.157</v>
       </c>
       <c r="V14" t="n">
         <v>0.038</v>
@@ -2177,68 +2305,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.829</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="D15" t="n">
-        <v>0.785</v>
+        <v>0.787</v>
       </c>
       <c r="E15" t="n">
-        <v>0.759</v>
+        <v>0.753</v>
       </c>
       <c r="F15" t="n">
-        <v>0.751</v>
+        <v>0.719</v>
       </c>
       <c r="G15" t="n">
-        <v>0.716</v>
+        <v>0.68</v>
       </c>
       <c r="H15" t="n">
-        <v>0.679</v>
+        <v>0.627</v>
       </c>
       <c r="I15" t="n">
-        <v>0.636</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.585</v>
+        <v>0.498</v>
       </c>
       <c r="K15" t="n">
-        <v>0.524</v>
+        <v>0.457</v>
       </c>
       <c r="L15" t="n">
-        <v>0.471</v>
+        <v>0.404</v>
       </c>
       <c r="M15" t="n">
-        <v>0.413</v>
+        <v>0.343</v>
       </c>
       <c r="N15" t="n">
-        <v>0.351</v>
+        <v>0.263</v>
       </c>
       <c r="O15" t="n">
-        <v>0.286</v>
+        <v>0.209</v>
       </c>
       <c r="P15" t="n">
-        <v>0.215</v>
+        <v>0.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.164</v>
+        <v>0.106</v>
       </c>
       <c r="R15" t="n">
-        <v>0.11</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.065</v>
+        <v>0.042</v>
       </c>
       <c r="T15" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="U15" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="V15" t="n">
         <v>0.038</v>
@@ -2247,68 +2375,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>inputxgradient_continuous</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0.829</v>
       </c>
       <c r="C16" t="n">
-        <v>0.822</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>0.799</v>
       </c>
       <c r="E16" t="n">
-        <v>0.773</v>
+        <v>0.768</v>
       </c>
       <c r="F16" t="n">
-        <v>0.744</v>
+        <v>0.73</v>
       </c>
       <c r="G16" t="n">
-        <v>0.729</v>
+        <v>0.697</v>
       </c>
       <c r="H16" t="n">
-        <v>0.714</v>
+        <v>0.644</v>
       </c>
       <c r="I16" t="n">
-        <v>0.667</v>
+        <v>0.594</v>
       </c>
       <c r="J16" t="n">
-        <v>0.633</v>
+        <v>0.542</v>
       </c>
       <c r="K16" t="n">
-        <v>0.608</v>
+        <v>0.473</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.432</v>
       </c>
       <c r="M16" t="n">
-        <v>0.525</v>
+        <v>0.377</v>
       </c>
       <c r="N16" t="n">
-        <v>0.486</v>
+        <v>0.324</v>
       </c>
       <c r="O16" t="n">
-        <v>0.448</v>
+        <v>0.276</v>
       </c>
       <c r="P16" t="n">
-        <v>0.419</v>
+        <v>0.211</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.372</v>
+        <v>0.174</v>
       </c>
       <c r="R16" t="n">
-        <v>0.326</v>
+        <v>0.144</v>
       </c>
       <c r="S16" t="n">
-        <v>0.243</v>
+        <v>0.098</v>
       </c>
       <c r="T16" t="n">
-        <v>0.185</v>
+        <v>0.076</v>
       </c>
       <c r="U16" t="n">
-        <v>0.116</v>
+        <v>0.045</v>
       </c>
       <c r="V16" t="n">
         <v>0.038</v>
@@ -2317,68 +2445,68 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>inputxgradient_u2net_fill</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.829</v>
       </c>
       <c r="C17" t="n">
-        <v>0.775</v>
+        <v>0.822</v>
       </c>
       <c r="D17" t="n">
-        <v>0.725</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.671</v>
+        <v>0.804</v>
       </c>
       <c r="F17" t="n">
-        <v>0.613</v>
+        <v>0.781</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.761</v>
       </c>
       <c r="H17" t="n">
-        <v>0.506</v>
+        <v>0.742</v>
       </c>
       <c r="I17" t="n">
-        <v>0.449</v>
+        <v>0.714</v>
       </c>
       <c r="J17" t="n">
-        <v>0.38</v>
+        <v>0.677</v>
       </c>
       <c r="K17" t="n">
-        <v>0.303</v>
+        <v>0.645</v>
       </c>
       <c r="L17" t="n">
-        <v>0.234</v>
+        <v>0.629</v>
       </c>
       <c r="M17" t="n">
-        <v>0.17</v>
+        <v>0.594</v>
       </c>
       <c r="N17" t="n">
-        <v>0.108</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.066</v>
+        <v>0.515</v>
       </c>
       <c r="P17" t="n">
-        <v>0.045</v>
+        <v>0.482</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.028</v>
+        <v>0.441</v>
       </c>
       <c r="R17" t="n">
-        <v>0.016</v>
+        <v>0.384</v>
       </c>
       <c r="S17" t="n">
-        <v>0.013</v>
+        <v>0.305</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01</v>
+        <v>0.213</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01</v>
+        <v>0.109</v>
       </c>
       <c r="V17" t="n">
         <v>0.038</v>
@@ -2387,68 +2515,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.829</v>
       </c>
       <c r="C18" t="n">
-        <v>0.803</v>
+        <v>0.8</v>
       </c>
       <c r="D18" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="E18" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.751</v>
       </c>
-      <c r="F18" t="n">
-        <v>0.705</v>
-      </c>
       <c r="G18" t="n">
-        <v>0.666</v>
+        <v>0.716</v>
       </c>
       <c r="H18" t="n">
-        <v>0.608</v>
+        <v>0.679</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="J18" t="n">
-        <v>0.509</v>
+        <v>0.585</v>
       </c>
       <c r="K18" t="n">
-        <v>0.444</v>
+        <v>0.524</v>
       </c>
       <c r="L18" t="n">
-        <v>0.378</v>
+        <v>0.471</v>
       </c>
       <c r="M18" t="n">
-        <v>0.309</v>
+        <v>0.413</v>
       </c>
       <c r="N18" t="n">
-        <v>0.248</v>
+        <v>0.351</v>
       </c>
       <c r="O18" t="n">
-        <v>0.187</v>
+        <v>0.286</v>
       </c>
       <c r="P18" t="n">
-        <v>0.132</v>
+        <v>0.215</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.095</v>
+        <v>0.164</v>
       </c>
       <c r="R18" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="S18" t="n">
-        <v>0.042</v>
+        <v>0.065</v>
       </c>
       <c r="T18" t="n">
-        <v>0.024</v>
+        <v>0.038</v>
       </c>
       <c r="U18" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="V18" t="n">
         <v>0.038</v>
@@ -2457,68 +2585,68 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sumDino</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.82</v>
+        <v>0.822</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.799</v>
       </c>
       <c r="E19" t="n">
-        <v>0.799</v>
+        <v>0.773</v>
       </c>
       <c r="F19" t="n">
-        <v>0.789</v>
+        <v>0.744</v>
       </c>
       <c r="G19" t="n">
-        <v>0.775</v>
+        <v>0.729</v>
       </c>
       <c r="H19" t="n">
-        <v>0.743</v>
+        <v>0.714</v>
       </c>
       <c r="I19" t="n">
-        <v>0.715</v>
+        <v>0.667</v>
       </c>
       <c r="J19" t="n">
-        <v>0.699</v>
+        <v>0.633</v>
       </c>
       <c r="K19" t="n">
-        <v>0.662</v>
+        <v>0.608</v>
       </c>
       <c r="L19" t="n">
-        <v>0.607</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="N19" t="n">
-        <v>0.526</v>
+        <v>0.486</v>
       </c>
       <c r="O19" t="n">
-        <v>0.492</v>
+        <v>0.448</v>
       </c>
       <c r="P19" t="n">
-        <v>0.453</v>
+        <v>0.419</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.409</v>
+        <v>0.372</v>
       </c>
       <c r="R19" t="n">
-        <v>0.344</v>
+        <v>0.326</v>
       </c>
       <c r="S19" t="n">
-        <v>0.27</v>
+        <v>0.243</v>
       </c>
       <c r="T19" t="n">
-        <v>0.194</v>
+        <v>0.185</v>
       </c>
       <c r="U19" t="n">
-        <v>0.092</v>
+        <v>0.116</v>
       </c>
       <c r="V19" t="n">
         <v>0.038</v>
@@ -2527,70 +2655,350 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>random_baseline</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sumDino</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.799</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>u2net_dino_fusion</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.748</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.038</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>xrai</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B24" t="n">
         <v>0.829</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C24" t="n">
         <v>0.822</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D24" t="n">
         <v>0.8129999999999999</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E24" t="n">
         <v>0.783</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F24" t="n">
         <v>0.757</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G24" t="n">
         <v>0.732</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H24" t="n">
         <v>0.695</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I24" t="n">
         <v>0.654</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J24" t="n">
         <v>0.617</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K24" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L24" t="n">
         <v>0.506</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M24" t="n">
         <v>0.436</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N24" t="n">
         <v>0.391</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O24" t="n">
         <v>0.336</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P24" t="n">
         <v>0.286</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q24" t="n">
         <v>0.224</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R24" t="n">
         <v>0.173</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S24" t="n">
         <v>0.125</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T24" t="n">
         <v>0.066</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U24" t="n">
         <v>0.042</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V24" t="n">
         <v>0.038</v>
       </c>
     </row>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -752,166 +752,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="18"/>
-          <order val="18"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A20</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$20:$V$20</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="19"/>
-          <order val="19"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A21</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$21:$V$21</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="20"/>
-          <order val="20"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A22</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$22:$V$22</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="21"/>
-          <order val="21"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$23:$V$23</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="22"/>
-          <order val="22"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A24</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$24:$V$24</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -985,7 +825,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1295,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1395,68 +1235,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U2Net-Saliency</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.829</v>
       </c>
       <c r="C2" t="n">
-        <v>0.826</v>
+        <v>0.775</v>
       </c>
       <c r="D2" t="n">
-        <v>0.826</v>
+        <v>0.725</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.671</v>
       </c>
       <c r="F2" t="n">
-        <v>0.802</v>
+        <v>0.613</v>
       </c>
       <c r="G2" t="n">
-        <v>0.796</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.778</v>
+        <v>0.506</v>
       </c>
       <c r="I2" t="n">
-        <v>0.767</v>
+        <v>0.449</v>
       </c>
       <c r="J2" t="n">
-        <v>0.733</v>
+        <v>0.38</v>
       </c>
       <c r="K2" t="n">
-        <v>0.706</v>
+        <v>0.303</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.234</v>
       </c>
       <c r="M2" t="n">
-        <v>0.669</v>
+        <v>0.17</v>
       </c>
       <c r="N2" t="n">
-        <v>0.636</v>
+        <v>0.108</v>
       </c>
       <c r="O2" t="n">
-        <v>0.582</v>
+        <v>0.066</v>
       </c>
       <c r="P2" t="n">
-        <v>0.546</v>
+        <v>0.045</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.489</v>
+        <v>0.028</v>
       </c>
       <c r="R2" t="n">
-        <v>0.417</v>
+        <v>0.016</v>
       </c>
       <c r="S2" t="n">
-        <v>0.341</v>
+        <v>0.013</v>
       </c>
       <c r="T2" t="n">
-        <v>0.23</v>
+        <v>0.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0.117</v>
+        <v>0.01</v>
       </c>
       <c r="V2" t="n">
         <v>0.038</v>
@@ -1465,68 +1305,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>c3f</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.829</v>
       </c>
       <c r="C3" t="n">
-        <v>0.824</v>
+        <v>0.803</v>
       </c>
       <c r="D3" t="n">
-        <v>0.825</v>
+        <v>0.783</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.751</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.797</v>
+        <v>0.666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.772</v>
+        <v>0.608</v>
       </c>
       <c r="I3" t="n">
-        <v>0.757</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.737</v>
+        <v>0.509</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.444</v>
       </c>
       <c r="L3" t="n">
-        <v>0.604</v>
+        <v>0.378</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.309</v>
       </c>
       <c r="N3" t="n">
-        <v>0.54</v>
+        <v>0.248</v>
       </c>
       <c r="O3" t="n">
-        <v>0.527</v>
+        <v>0.187</v>
       </c>
       <c r="P3" t="n">
-        <v>0.493</v>
+        <v>0.132</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.441</v>
+        <v>0.095</v>
       </c>
       <c r="R3" t="n">
-        <v>0.39</v>
+        <v>0.06</v>
       </c>
       <c r="S3" t="n">
-        <v>0.338</v>
+        <v>0.042</v>
       </c>
       <c r="T3" t="n">
-        <v>0.261</v>
+        <v>0.024</v>
       </c>
       <c r="U3" t="n">
-        <v>0.129</v>
+        <v>0.013</v>
       </c>
       <c r="V3" t="n">
         <v>0.038</v>
@@ -1535,68 +1375,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_ENT_SMOOTH</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.829</v>
       </c>
       <c r="C4" t="n">
-        <v>0.823</v>
+        <v>0.797</v>
       </c>
       <c r="D4" t="n">
-        <v>0.82</v>
+        <v>0.787</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="F4" t="n">
-        <v>0.806</v>
+        <v>0.719</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
-        <v>0.779</v>
+        <v>0.627</v>
       </c>
       <c r="I4" t="n">
-        <v>0.758</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.737</v>
+        <v>0.498</v>
       </c>
       <c r="K4" t="n">
-        <v>0.723</v>
+        <v>0.457</v>
       </c>
       <c r="L4" t="n">
-        <v>0.709</v>
+        <v>0.404</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.343</v>
       </c>
       <c r="N4" t="n">
-        <v>0.654</v>
+        <v>0.263</v>
       </c>
       <c r="O4" t="n">
-        <v>0.622</v>
+        <v>0.209</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.528</v>
+        <v>0.106</v>
       </c>
       <c r="R4" t="n">
-        <v>0.472</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.379</v>
+        <v>0.042</v>
       </c>
       <c r="T4" t="n">
-        <v>0.291</v>
+        <v>0.027</v>
       </c>
       <c r="U4" t="n">
-        <v>0.177</v>
+        <v>0.018</v>
       </c>
       <c r="V4" t="n">
         <v>0.038</v>
@@ -1605,68 +1445,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.827</v>
+        <v>0.804</v>
       </c>
       <c r="D5" t="n">
-        <v>0.797</v>
+        <v>0.784</v>
       </c>
       <c r="E5" t="n">
-        <v>0.788</v>
+        <v>0.763</v>
       </c>
       <c r="F5" t="n">
-        <v>0.771</v>
+        <v>0.745</v>
       </c>
       <c r="G5" t="n">
-        <v>0.748</v>
+        <v>0.711</v>
       </c>
       <c r="H5" t="n">
-        <v>0.739</v>
+        <v>0.662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.725</v>
+        <v>0.632</v>
       </c>
       <c r="J5" t="n">
-        <v>0.704</v>
+        <v>0.576</v>
       </c>
       <c r="K5" t="n">
-        <v>0.679</v>
+        <v>0.53</v>
       </c>
       <c r="L5" t="n">
-        <v>0.649</v>
+        <v>0.469</v>
       </c>
       <c r="M5" t="n">
-        <v>0.622</v>
+        <v>0.403</v>
       </c>
       <c r="N5" t="n">
-        <v>0.588</v>
+        <v>0.348</v>
       </c>
       <c r="O5" t="n">
-        <v>0.533</v>
+        <v>0.285</v>
       </c>
       <c r="P5" t="n">
-        <v>0.476</v>
+        <v>0.215</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.426</v>
+        <v>0.152</v>
       </c>
       <c r="R5" t="n">
-        <v>0.354</v>
+        <v>0.111</v>
       </c>
       <c r="S5" t="n">
-        <v>0.243</v>
+        <v>0.066</v>
       </c>
       <c r="T5" t="n">
-        <v>0.166</v>
+        <v>0.035</v>
       </c>
       <c r="U5" t="n">
-        <v>0.078</v>
+        <v>0.015</v>
       </c>
       <c r="V5" t="n">
         <v>0.038</v>
@@ -1675,68 +1515,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dinov2_ENT</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.829</v>
       </c>
       <c r="C6" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.806</v>
+        <v>0.785</v>
       </c>
       <c r="E6" t="n">
-        <v>0.792</v>
+        <v>0.759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.779</v>
+        <v>0.751</v>
       </c>
       <c r="G6" t="n">
-        <v>0.763</v>
+        <v>0.716</v>
       </c>
       <c r="H6" t="n">
-        <v>0.752</v>
+        <v>0.679</v>
       </c>
       <c r="I6" t="n">
-        <v>0.728</v>
+        <v>0.636</v>
       </c>
       <c r="J6" t="n">
-        <v>0.699</v>
+        <v>0.585</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.524</v>
       </c>
       <c r="L6" t="n">
-        <v>0.662</v>
+        <v>0.471</v>
       </c>
       <c r="M6" t="n">
-        <v>0.63</v>
+        <v>0.413</v>
       </c>
       <c r="N6" t="n">
-        <v>0.581</v>
+        <v>0.351</v>
       </c>
       <c r="O6" t="n">
-        <v>0.549</v>
+        <v>0.286</v>
       </c>
       <c r="P6" t="n">
-        <v>0.501</v>
+        <v>0.215</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.436</v>
+        <v>0.164</v>
       </c>
       <c r="R6" t="n">
-        <v>0.369</v>
+        <v>0.11</v>
       </c>
       <c r="S6" t="n">
-        <v>0.272</v>
+        <v>0.065</v>
       </c>
       <c r="T6" t="n">
-        <v>0.19</v>
+        <v>0.038</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1</v>
+        <v>0.017</v>
       </c>
       <c r="V6" t="n">
         <v>0.038</v>
@@ -1745,7 +1585,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>inputxgradient_continuous</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1755,58 +1595,58 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.795</v>
+        <v>0.799</v>
       </c>
       <c r="E7" t="n">
-        <v>0.78</v>
+        <v>0.768</v>
       </c>
       <c r="F7" t="n">
-        <v>0.773</v>
+        <v>0.73</v>
       </c>
       <c r="G7" t="n">
-        <v>0.746</v>
+        <v>0.697</v>
       </c>
       <c r="H7" t="n">
-        <v>0.731</v>
+        <v>0.644</v>
       </c>
       <c r="I7" t="n">
-        <v>0.71</v>
+        <v>0.594</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="K7" t="n">
-        <v>0.673</v>
+        <v>0.473</v>
       </c>
       <c r="L7" t="n">
-        <v>0.641</v>
+        <v>0.432</v>
       </c>
       <c r="M7" t="n">
-        <v>0.608</v>
+        <v>0.377</v>
       </c>
       <c r="N7" t="n">
-        <v>0.58</v>
+        <v>0.324</v>
       </c>
       <c r="O7" t="n">
-        <v>0.53</v>
+        <v>0.276</v>
       </c>
       <c r="P7" t="n">
-        <v>0.463</v>
+        <v>0.211</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.393</v>
+        <v>0.174</v>
       </c>
       <c r="R7" t="n">
-        <v>0.314</v>
+        <v>0.144</v>
       </c>
       <c r="S7" t="n">
-        <v>0.245</v>
+        <v>0.098</v>
       </c>
       <c r="T7" t="n">
-        <v>0.156</v>
+        <v>0.076</v>
       </c>
       <c r="U7" t="n">
-        <v>0.068</v>
+        <v>0.045</v>
       </c>
       <c r="V7" t="n">
         <v>0.038</v>
@@ -1815,68 +1655,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_PC_EV</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.829</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.822</v>
       </c>
       <c r="D8" t="n">
-        <v>0.795</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="F8" t="n">
-        <v>0.773</v>
+        <v>0.757</v>
       </c>
       <c r="G8" t="n">
-        <v>0.746</v>
+        <v>0.732</v>
       </c>
       <c r="H8" t="n">
-        <v>0.731</v>
+        <v>0.695</v>
       </c>
       <c r="I8" t="n">
-        <v>0.71</v>
+        <v>0.654</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.617</v>
       </c>
       <c r="K8" t="n">
-        <v>0.673</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.641</v>
+        <v>0.506</v>
       </c>
       <c r="M8" t="n">
-        <v>0.608</v>
+        <v>0.436</v>
       </c>
       <c r="N8" t="n">
-        <v>0.58</v>
+        <v>0.391</v>
       </c>
       <c r="O8" t="n">
-        <v>0.53</v>
+        <v>0.336</v>
       </c>
       <c r="P8" t="n">
-        <v>0.463</v>
+        <v>0.286</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.393</v>
+        <v>0.224</v>
       </c>
       <c r="R8" t="n">
-        <v>0.314</v>
+        <v>0.173</v>
       </c>
       <c r="S8" t="n">
-        <v>0.245</v>
+        <v>0.125</v>
       </c>
       <c r="T8" t="n">
-        <v>0.156</v>
+        <v>0.066</v>
       </c>
       <c r="U8" t="n">
-        <v>0.068</v>
+        <v>0.042</v>
       </c>
       <c r="V8" t="n">
         <v>0.038</v>
@@ -1885,68 +1725,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_PC_L2</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.829</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.822</v>
       </c>
       <c r="D9" t="n">
-        <v>0.778</v>
+        <v>0.799</v>
       </c>
       <c r="E9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.744</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.704</v>
-      </c>
       <c r="G9" t="n">
-        <v>0.663</v>
+        <v>0.729</v>
       </c>
       <c r="H9" t="n">
-        <v>0.636</v>
+        <v>0.714</v>
       </c>
       <c r="I9" t="n">
-        <v>0.578</v>
+        <v>0.667</v>
       </c>
       <c r="J9" t="n">
-        <v>0.546</v>
+        <v>0.633</v>
       </c>
       <c r="K9" t="n">
-        <v>0.509</v>
+        <v>0.608</v>
       </c>
       <c r="L9" t="n">
-        <v>0.468</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.42</v>
+        <v>0.525</v>
       </c>
       <c r="N9" t="n">
-        <v>0.379</v>
+        <v>0.486</v>
       </c>
       <c r="O9" t="n">
-        <v>0.322</v>
+        <v>0.448</v>
       </c>
       <c r="P9" t="n">
-        <v>0.286</v>
+        <v>0.419</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.246</v>
+        <v>0.372</v>
       </c>
       <c r="R9" t="n">
-        <v>0.222</v>
+        <v>0.326</v>
       </c>
       <c r="S9" t="n">
-        <v>0.198</v>
+        <v>0.243</v>
       </c>
       <c r="T9" t="n">
-        <v>0.132</v>
+        <v>0.185</v>
       </c>
       <c r="U9" t="n">
-        <v>0.075</v>
+        <v>0.116</v>
       </c>
       <c r="V9" t="n">
         <v>0.038</v>
@@ -1955,68 +1795,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.829</v>
       </c>
       <c r="C10" t="n">
-        <v>0.82</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.795</v>
       </c>
       <c r="E10" t="n">
-        <v>0.797</v>
+        <v>0.78</v>
       </c>
       <c r="F10" t="n">
-        <v>0.781</v>
+        <v>0.773</v>
       </c>
       <c r="G10" t="n">
-        <v>0.772</v>
+        <v>0.746</v>
       </c>
       <c r="H10" t="n">
-        <v>0.758</v>
+        <v>0.731</v>
       </c>
       <c r="I10" t="n">
-        <v>0.733</v>
+        <v>0.71</v>
       </c>
       <c r="J10" t="n">
-        <v>0.705</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.672</v>
+        <v>0.673</v>
       </c>
       <c r="L10" t="n">
-        <v>0.656</v>
+        <v>0.641</v>
       </c>
       <c r="M10" t="n">
-        <v>0.61</v>
+        <v>0.608</v>
       </c>
       <c r="N10" t="n">
-        <v>0.569</v>
+        <v>0.58</v>
       </c>
       <c r="O10" t="n">
-        <v>0.533</v>
+        <v>0.53</v>
       </c>
       <c r="P10" t="n">
-        <v>0.478</v>
+        <v>0.463</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.417</v>
+        <v>0.393</v>
       </c>
       <c r="R10" t="n">
-        <v>0.343</v>
+        <v>0.314</v>
       </c>
       <c r="S10" t="n">
-        <v>0.262</v>
+        <v>0.245</v>
       </c>
       <c r="T10" t="n">
-        <v>0.191</v>
+        <v>0.156</v>
       </c>
       <c r="U10" t="n">
-        <v>0.106</v>
+        <v>0.068</v>
       </c>
       <c r="V10" t="n">
         <v>0.038</v>
@@ -2025,68 +1865,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>grad_cam</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.829</v>
       </c>
       <c r="C11" t="n">
-        <v>0.827</v>
+        <v>0.82</v>
       </c>
       <c r="D11" t="n">
-        <v>0.826</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.831</v>
+        <v>0.797</v>
       </c>
       <c r="F11" t="n">
-        <v>0.821</v>
+        <v>0.781</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="H11" t="n">
-        <v>0.806</v>
+        <v>0.758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.795</v>
+        <v>0.733</v>
       </c>
       <c r="J11" t="n">
-        <v>0.778</v>
+        <v>0.705</v>
       </c>
       <c r="K11" t="n">
-        <v>0.768</v>
+        <v>0.672</v>
       </c>
       <c r="L11" t="n">
-        <v>0.742</v>
+        <v>0.656</v>
       </c>
       <c r="M11" t="n">
-        <v>0.727</v>
+        <v>0.61</v>
       </c>
       <c r="N11" t="n">
-        <v>0.701</v>
+        <v>0.569</v>
       </c>
       <c r="O11" t="n">
-        <v>0.668</v>
+        <v>0.533</v>
       </c>
       <c r="P11" t="n">
-        <v>0.637</v>
+        <v>0.478</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.582</v>
+        <v>0.417</v>
       </c>
       <c r="R11" t="n">
-        <v>0.533</v>
+        <v>0.343</v>
       </c>
       <c r="S11" t="n">
-        <v>0.458</v>
+        <v>0.262</v>
       </c>
       <c r="T11" t="n">
-        <v>0.337</v>
+        <v>0.191</v>
       </c>
       <c r="U11" t="n">
-        <v>0.184</v>
+        <v>0.106</v>
       </c>
       <c r="V11" t="n">
         <v>0.038</v>
@@ -2095,68 +1935,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.804</v>
+        <v>0.827</v>
       </c>
       <c r="D12" t="n">
-        <v>0.784</v>
+        <v>0.797</v>
       </c>
       <c r="E12" t="n">
-        <v>0.763</v>
+        <v>0.788</v>
       </c>
       <c r="F12" t="n">
-        <v>0.745</v>
+        <v>0.771</v>
       </c>
       <c r="G12" t="n">
-        <v>0.711</v>
+        <v>0.748</v>
       </c>
       <c r="H12" t="n">
-        <v>0.662</v>
+        <v>0.739</v>
       </c>
       <c r="I12" t="n">
-        <v>0.632</v>
+        <v>0.725</v>
       </c>
       <c r="J12" t="n">
-        <v>0.576</v>
+        <v>0.704</v>
       </c>
       <c r="K12" t="n">
-        <v>0.53</v>
+        <v>0.679</v>
       </c>
       <c r="L12" t="n">
-        <v>0.469</v>
+        <v>0.649</v>
       </c>
       <c r="M12" t="n">
-        <v>0.403</v>
+        <v>0.622</v>
       </c>
       <c r="N12" t="n">
-        <v>0.348</v>
+        <v>0.588</v>
       </c>
       <c r="O12" t="n">
-        <v>0.285</v>
+        <v>0.533</v>
       </c>
       <c r="P12" t="n">
-        <v>0.215</v>
+        <v>0.476</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.152</v>
+        <v>0.426</v>
       </c>
       <c r="R12" t="n">
-        <v>0.111</v>
+        <v>0.354</v>
       </c>
       <c r="S12" t="n">
-        <v>0.066</v>
+        <v>0.243</v>
       </c>
       <c r="T12" t="n">
-        <v>0.035</v>
+        <v>0.166</v>
       </c>
       <c r="U12" t="n">
-        <v>0.015</v>
+        <v>0.078</v>
       </c>
       <c r="V12" t="n">
         <v>0.038</v>
@@ -2165,68 +2005,68 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>guided_backprop</t>
+          <t>inputxgradient_u2net_fill</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.822</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.796</v>
+        <v>0.804</v>
       </c>
       <c r="F13" t="n">
-        <v>0.791</v>
+        <v>0.781</v>
       </c>
       <c r="G13" t="n">
-        <v>0.781</v>
+        <v>0.761</v>
       </c>
       <c r="H13" t="n">
-        <v>0.764</v>
+        <v>0.742</v>
       </c>
       <c r="I13" t="n">
-        <v>0.754</v>
+        <v>0.714</v>
       </c>
       <c r="J13" t="n">
-        <v>0.745</v>
+        <v>0.677</v>
       </c>
       <c r="K13" t="n">
-        <v>0.728</v>
+        <v>0.645</v>
       </c>
       <c r="L13" t="n">
-        <v>0.698</v>
+        <v>0.629</v>
       </c>
       <c r="M13" t="n">
-        <v>0.667</v>
+        <v>0.594</v>
       </c>
       <c r="N13" t="n">
-        <v>0.629</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>0.593</v>
+        <v>0.515</v>
       </c>
       <c r="P13" t="n">
-        <v>0.55</v>
+        <v>0.482</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.493</v>
+        <v>0.441</v>
       </c>
       <c r="R13" t="n">
-        <v>0.425</v>
+        <v>0.384</v>
       </c>
       <c r="S13" t="n">
-        <v>0.324</v>
+        <v>0.305</v>
       </c>
       <c r="T13" t="n">
-        <v>0.221</v>
+        <v>0.213</v>
       </c>
       <c r="U13" t="n">
-        <v>0.115</v>
+        <v>0.109</v>
       </c>
       <c r="V13" t="n">
         <v>0.038</v>
@@ -2235,68 +2075,68 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>guided_gradcam</t>
+          <t>u2net_dino_fusion</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0.829</v>
       </c>
       <c r="C14" t="n">
-        <v>0.823</v>
+        <v>0.82</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.806</v>
+        <v>0.803</v>
       </c>
       <c r="F14" t="n">
-        <v>0.802</v>
+        <v>0.787</v>
       </c>
       <c r="G14" t="n">
-        <v>0.794</v>
+        <v>0.776</v>
       </c>
       <c r="H14" t="n">
-        <v>0.789</v>
+        <v>0.756</v>
       </c>
       <c r="I14" t="n">
-        <v>0.774</v>
+        <v>0.743</v>
       </c>
       <c r="J14" t="n">
-        <v>0.757</v>
+        <v>0.727</v>
       </c>
       <c r="K14" t="n">
-        <v>0.741</v>
+        <v>0.696</v>
       </c>
       <c r="L14" t="n">
-        <v>0.716</v>
+        <v>0.679</v>
       </c>
       <c r="M14" t="n">
-        <v>0.703</v>
+        <v>0.631</v>
       </c>
       <c r="N14" t="n">
-        <v>0.674</v>
+        <v>0.602</v>
       </c>
       <c r="O14" t="n">
-        <v>0.635</v>
+        <v>0.549</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6</v>
+        <v>0.481</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.552</v>
+        <v>0.448</v>
       </c>
       <c r="R14" t="n">
-        <v>0.48</v>
+        <v>0.377</v>
       </c>
       <c r="S14" t="n">
-        <v>0.403</v>
+        <v>0.289</v>
       </c>
       <c r="T14" t="n">
-        <v>0.288</v>
+        <v>0.186</v>
       </c>
       <c r="U14" t="n">
-        <v>0.157</v>
+        <v>0.106</v>
       </c>
       <c r="V14" t="n">
         <v>0.038</v>
@@ -2305,68 +2145,68 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>U2Net-Saliency</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0.829</v>
       </c>
       <c r="C15" t="n">
-        <v>0.797</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="D15" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.787</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.719</v>
-      </c>
       <c r="G15" t="n">
-        <v>0.68</v>
+        <v>0.775</v>
       </c>
       <c r="H15" t="n">
-        <v>0.627</v>
+        <v>0.76</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.749</v>
       </c>
       <c r="J15" t="n">
-        <v>0.498</v>
+        <v>0.716</v>
       </c>
       <c r="K15" t="n">
-        <v>0.457</v>
+        <v>0.696</v>
       </c>
       <c r="L15" t="n">
-        <v>0.404</v>
+        <v>0.678</v>
       </c>
       <c r="M15" t="n">
-        <v>0.343</v>
+        <v>0.649</v>
       </c>
       <c r="N15" t="n">
-        <v>0.263</v>
+        <v>0.626</v>
       </c>
       <c r="O15" t="n">
-        <v>0.209</v>
+        <v>0.574</v>
       </c>
       <c r="P15" t="n">
-        <v>0.15</v>
+        <v>0.534</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.106</v>
+        <v>0.476</v>
       </c>
       <c r="R15" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.399</v>
       </c>
       <c r="S15" t="n">
-        <v>0.042</v>
+        <v>0.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0.027</v>
+        <v>0.202</v>
       </c>
       <c r="U15" t="n">
-        <v>0.018</v>
+        <v>0.112</v>
       </c>
       <c r="V15" t="n">
         <v>0.038</v>
@@ -2375,7 +2215,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inputxgradient_continuous</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2385,58 +2225,58 @@
         <v>0.8179999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>0.799</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.768</v>
+        <v>0.796</v>
       </c>
       <c r="F16" t="n">
-        <v>0.73</v>
+        <v>0.791</v>
       </c>
       <c r="G16" t="n">
-        <v>0.697</v>
+        <v>0.781</v>
       </c>
       <c r="H16" t="n">
-        <v>0.644</v>
+        <v>0.764</v>
       </c>
       <c r="I16" t="n">
-        <v>0.594</v>
+        <v>0.754</v>
       </c>
       <c r="J16" t="n">
-        <v>0.542</v>
+        <v>0.745</v>
       </c>
       <c r="K16" t="n">
-        <v>0.473</v>
+        <v>0.728</v>
       </c>
       <c r="L16" t="n">
-        <v>0.432</v>
+        <v>0.698</v>
       </c>
       <c r="M16" t="n">
-        <v>0.377</v>
+        <v>0.667</v>
       </c>
       <c r="N16" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="S16" t="n">
         <v>0.324</v>
       </c>
-      <c r="O16" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.098</v>
-      </c>
       <c r="T16" t="n">
-        <v>0.076</v>
+        <v>0.221</v>
       </c>
       <c r="U16" t="n">
-        <v>0.045</v>
+        <v>0.115</v>
       </c>
       <c r="V16" t="n">
         <v>0.038</v>
@@ -2445,68 +2285,68 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inputxgradient_u2net_fill</t>
+          <t>dinov2_COMBO_ENT_SMOOTH</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0.829</v>
       </c>
       <c r="C17" t="n">
-        <v>0.822</v>
+        <v>0.823</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="E17" t="n">
-        <v>0.804</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.781</v>
+        <v>0.806</v>
       </c>
       <c r="G17" t="n">
-        <v>0.761</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0.742</v>
+        <v>0.779</v>
       </c>
       <c r="I17" t="n">
-        <v>0.714</v>
+        <v>0.758</v>
       </c>
       <c r="J17" t="n">
-        <v>0.677</v>
+        <v>0.737</v>
       </c>
       <c r="K17" t="n">
-        <v>0.645</v>
+        <v>0.723</v>
       </c>
       <c r="L17" t="n">
-        <v>0.629</v>
+        <v>0.709</v>
       </c>
       <c r="M17" t="n">
-        <v>0.594</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.654</v>
       </c>
       <c r="O17" t="n">
-        <v>0.515</v>
+        <v>0.622</v>
       </c>
       <c r="P17" t="n">
-        <v>0.482</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.441</v>
+        <v>0.528</v>
       </c>
       <c r="R17" t="n">
-        <v>0.384</v>
+        <v>0.472</v>
       </c>
       <c r="S17" t="n">
-        <v>0.305</v>
+        <v>0.379</v>
       </c>
       <c r="T17" t="n">
-        <v>0.213</v>
+        <v>0.291</v>
       </c>
       <c r="U17" t="n">
-        <v>0.109</v>
+        <v>0.177</v>
       </c>
       <c r="V17" t="n">
         <v>0.038</v>
@@ -2515,68 +2355,68 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0.829</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8</v>
+        <v>0.823</v>
       </c>
       <c r="D18" t="n">
-        <v>0.785</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.759</v>
+        <v>0.806</v>
       </c>
       <c r="F18" t="n">
-        <v>0.751</v>
+        <v>0.802</v>
       </c>
       <c r="G18" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.716</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.471</v>
-      </c>
       <c r="M18" t="n">
-        <v>0.413</v>
+        <v>0.703</v>
       </c>
       <c r="N18" t="n">
-        <v>0.351</v>
+        <v>0.674</v>
       </c>
       <c r="O18" t="n">
-        <v>0.286</v>
+        <v>0.635</v>
       </c>
       <c r="P18" t="n">
-        <v>0.215</v>
+        <v>0.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.164</v>
+        <v>0.552</v>
       </c>
       <c r="R18" t="n">
-        <v>0.11</v>
+        <v>0.48</v>
       </c>
       <c r="S18" t="n">
-        <v>0.065</v>
+        <v>0.403</v>
       </c>
       <c r="T18" t="n">
-        <v>0.038</v>
+        <v>0.288</v>
       </c>
       <c r="U18" t="n">
-        <v>0.017</v>
+        <v>0.157</v>
       </c>
       <c r="V18" t="n">
         <v>0.038</v>
@@ -2585,424 +2425,86 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0.829</v>
       </c>
       <c r="C19" t="n">
-        <v>0.822</v>
+        <v>0.827</v>
       </c>
       <c r="D19" t="n">
-        <v>0.799</v>
+        <v>0.826</v>
       </c>
       <c r="E19" t="n">
-        <v>0.773</v>
+        <v>0.831</v>
       </c>
       <c r="F19" t="n">
-        <v>0.744</v>
+        <v>0.821</v>
       </c>
       <c r="G19" t="n">
-        <v>0.729</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.714</v>
+        <v>0.806</v>
       </c>
       <c r="I19" t="n">
-        <v>0.667</v>
+        <v>0.795</v>
       </c>
       <c r="J19" t="n">
-        <v>0.633</v>
+        <v>0.778</v>
       </c>
       <c r="K19" t="n">
-        <v>0.608</v>
+        <v>0.768</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.742</v>
       </c>
       <c r="M19" t="n">
-        <v>0.525</v>
+        <v>0.727</v>
       </c>
       <c r="N19" t="n">
-        <v>0.486</v>
+        <v>0.701</v>
       </c>
       <c r="O19" t="n">
-        <v>0.448</v>
+        <v>0.668</v>
       </c>
       <c r="P19" t="n">
-        <v>0.419</v>
+        <v>0.637</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.372</v>
+        <v>0.582</v>
       </c>
       <c r="R19" t="n">
-        <v>0.326</v>
+        <v>0.533</v>
       </c>
       <c r="S19" t="n">
-        <v>0.243</v>
+        <v>0.458</v>
       </c>
       <c r="T19" t="n">
-        <v>0.185</v>
+        <v>0.337</v>
       </c>
       <c r="U19" t="n">
-        <v>0.116</v>
+        <v>0.184</v>
       </c>
       <c r="V19" t="n">
         <v>0.038</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>random_baseline</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>saliency</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.803</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.666</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sumDino</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.799</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>u2net_dino_fusion</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.748</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.204</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.8129999999999999</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.783</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.436</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.224</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:V19">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -560,198 +560,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="12"/>
-          <order val="12"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$14:$V$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="13"/>
-          <order val="13"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$15:$V$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="14"/>
-          <order val="14"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A16</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$16:$V$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="15"/>
-          <order val="15"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A17</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$17:$V$17</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="16"/>
-          <order val="16"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A18</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$18:$V$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="17"/>
-          <order val="17"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A19</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$19:$V$19</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -825,7 +633,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>21</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1135,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1235,68 +1043,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>0.829</v>
       </c>
       <c r="C2" t="n">
-        <v>0.775</v>
+        <v>0.797</v>
       </c>
       <c r="D2" t="n">
-        <v>0.725</v>
+        <v>0.787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.671</v>
+        <v>0.753</v>
       </c>
       <c r="F2" t="n">
-        <v>0.613</v>
+        <v>0.719</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H2" t="n">
-        <v>0.506</v>
+        <v>0.627</v>
       </c>
       <c r="I2" t="n">
-        <v>0.449</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38</v>
+        <v>0.498</v>
       </c>
       <c r="K2" t="n">
-        <v>0.303</v>
+        <v>0.457</v>
       </c>
       <c r="L2" t="n">
-        <v>0.234</v>
+        <v>0.404</v>
       </c>
       <c r="M2" t="n">
-        <v>0.17</v>
+        <v>0.343</v>
       </c>
       <c r="N2" t="n">
-        <v>0.108</v>
+        <v>0.263</v>
       </c>
       <c r="O2" t="n">
-        <v>0.066</v>
+        <v>0.209</v>
       </c>
       <c r="P2" t="n">
-        <v>0.045</v>
+        <v>0.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.028</v>
+        <v>0.106</v>
       </c>
       <c r="R2" t="n">
-        <v>0.016</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>0.013</v>
+        <v>0.042</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="V2" t="n">
         <v>0.038</v>
@@ -1305,68 +1113,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0.829</v>
       </c>
       <c r="C3" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
       <c r="D3" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="E3" t="n">
-        <v>0.751</v>
+        <v>0.763</v>
       </c>
       <c r="F3" t="n">
-        <v>0.705</v>
+        <v>0.745</v>
       </c>
       <c r="G3" t="n">
-        <v>0.666</v>
+        <v>0.711</v>
       </c>
       <c r="H3" t="n">
-        <v>0.608</v>
+        <v>0.662</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="J3" t="n">
-        <v>0.509</v>
+        <v>0.576</v>
       </c>
       <c r="K3" t="n">
-        <v>0.444</v>
+        <v>0.53</v>
       </c>
       <c r="L3" t="n">
-        <v>0.378</v>
+        <v>0.469</v>
       </c>
       <c r="M3" t="n">
-        <v>0.309</v>
+        <v>0.403</v>
       </c>
       <c r="N3" t="n">
-        <v>0.248</v>
+        <v>0.348</v>
       </c>
       <c r="O3" t="n">
-        <v>0.187</v>
+        <v>0.285</v>
       </c>
       <c r="P3" t="n">
-        <v>0.132</v>
+        <v>0.215</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.095</v>
+        <v>0.152</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06</v>
+        <v>0.111</v>
       </c>
       <c r="S3" t="n">
-        <v>0.042</v>
+        <v>0.066</v>
       </c>
       <c r="T3" t="n">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="U3" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="V3" t="n">
         <v>0.038</v>
@@ -1375,68 +1183,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0.829</v>
       </c>
       <c r="C4" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="n">
-        <v>0.787</v>
+        <v>0.785</v>
       </c>
       <c r="E4" t="n">
-        <v>0.753</v>
+        <v>0.759</v>
       </c>
       <c r="F4" t="n">
-        <v>0.719</v>
+        <v>0.751</v>
       </c>
       <c r="G4" t="n">
-        <v>0.68</v>
+        <v>0.716</v>
       </c>
       <c r="H4" t="n">
-        <v>0.627</v>
+        <v>0.679</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="J4" t="n">
-        <v>0.498</v>
+        <v>0.585</v>
       </c>
       <c r="K4" t="n">
-        <v>0.457</v>
+        <v>0.524</v>
       </c>
       <c r="L4" t="n">
-        <v>0.404</v>
+        <v>0.471</v>
       </c>
       <c r="M4" t="n">
-        <v>0.343</v>
+        <v>0.413</v>
       </c>
       <c r="N4" t="n">
-        <v>0.263</v>
+        <v>0.351</v>
       </c>
       <c r="O4" t="n">
-        <v>0.209</v>
+        <v>0.286</v>
       </c>
       <c r="P4" t="n">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.106</v>
+        <v>0.164</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="S4" t="n">
-        <v>0.042</v>
+        <v>0.065</v>
       </c>
       <c r="T4" t="n">
-        <v>0.027</v>
+        <v>0.038</v>
       </c>
       <c r="U4" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="V4" t="n">
         <v>0.038</v>
@@ -1445,68 +1253,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>inputxgradient_continuous</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0.829</v>
       </c>
       <c r="C5" t="n">
-        <v>0.804</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.784</v>
+        <v>0.799</v>
       </c>
       <c r="E5" t="n">
-        <v>0.763</v>
+        <v>0.768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745</v>
+        <v>0.73</v>
       </c>
       <c r="G5" t="n">
-        <v>0.711</v>
+        <v>0.697</v>
       </c>
       <c r="H5" t="n">
-        <v>0.662</v>
+        <v>0.644</v>
       </c>
       <c r="I5" t="n">
-        <v>0.632</v>
+        <v>0.594</v>
       </c>
       <c r="J5" t="n">
-        <v>0.576</v>
+        <v>0.542</v>
       </c>
       <c r="K5" t="n">
-        <v>0.53</v>
+        <v>0.473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.469</v>
+        <v>0.432</v>
       </c>
       <c r="M5" t="n">
-        <v>0.403</v>
+        <v>0.377</v>
       </c>
       <c r="N5" t="n">
-        <v>0.348</v>
+        <v>0.324</v>
       </c>
       <c r="O5" t="n">
-        <v>0.285</v>
+        <v>0.276</v>
       </c>
       <c r="P5" t="n">
-        <v>0.215</v>
+        <v>0.211</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.152</v>
+        <v>0.174</v>
       </c>
       <c r="R5" t="n">
-        <v>0.111</v>
+        <v>0.144</v>
       </c>
       <c r="S5" t="n">
-        <v>0.066</v>
+        <v>0.098</v>
       </c>
       <c r="T5" t="n">
-        <v>0.035</v>
+        <v>0.076</v>
       </c>
       <c r="U5" t="n">
-        <v>0.015</v>
+        <v>0.045</v>
       </c>
       <c r="V5" t="n">
         <v>0.038</v>
@@ -1515,68 +1323,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0.829</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8</v>
+        <v>0.822</v>
       </c>
       <c r="D6" t="n">
-        <v>0.785</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.759</v>
+        <v>0.783</v>
       </c>
       <c r="F6" t="n">
-        <v>0.751</v>
+        <v>0.757</v>
       </c>
       <c r="G6" t="n">
-        <v>0.716</v>
+        <v>0.732</v>
       </c>
       <c r="H6" t="n">
-        <v>0.679</v>
+        <v>0.695</v>
       </c>
       <c r="I6" t="n">
-        <v>0.636</v>
+        <v>0.654</v>
       </c>
       <c r="J6" t="n">
-        <v>0.585</v>
+        <v>0.617</v>
       </c>
       <c r="K6" t="n">
-        <v>0.524</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.471</v>
+        <v>0.506</v>
       </c>
       <c r="M6" t="n">
-        <v>0.413</v>
+        <v>0.436</v>
       </c>
       <c r="N6" t="n">
-        <v>0.351</v>
+        <v>0.391</v>
       </c>
       <c r="O6" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="P6" t="n">
         <v>0.286</v>
       </c>
-      <c r="P6" t="n">
-        <v>0.215</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.164</v>
+        <v>0.224</v>
       </c>
       <c r="R6" t="n">
-        <v>0.11</v>
+        <v>0.173</v>
       </c>
       <c r="S6" t="n">
-        <v>0.065</v>
+        <v>0.125</v>
       </c>
       <c r="T6" t="n">
-        <v>0.038</v>
+        <v>0.066</v>
       </c>
       <c r="U6" t="n">
-        <v>0.017</v>
+        <v>0.042</v>
       </c>
       <c r="V6" t="n">
         <v>0.038</v>
@@ -1585,68 +1393,68 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inputxgradient_continuous</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.829</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.822</v>
       </c>
       <c r="D7" t="n">
         <v>0.799</v>
       </c>
       <c r="E7" t="n">
-        <v>0.768</v>
+        <v>0.773</v>
       </c>
       <c r="F7" t="n">
-        <v>0.73</v>
+        <v>0.744</v>
       </c>
       <c r="G7" t="n">
-        <v>0.697</v>
+        <v>0.729</v>
       </c>
       <c r="H7" t="n">
-        <v>0.644</v>
+        <v>0.714</v>
       </c>
       <c r="I7" t="n">
-        <v>0.594</v>
+        <v>0.667</v>
       </c>
       <c r="J7" t="n">
-        <v>0.542</v>
+        <v>0.633</v>
       </c>
       <c r="K7" t="n">
-        <v>0.473</v>
+        <v>0.608</v>
       </c>
       <c r="L7" t="n">
-        <v>0.432</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.377</v>
+        <v>0.525</v>
       </c>
       <c r="N7" t="n">
-        <v>0.324</v>
+        <v>0.486</v>
       </c>
       <c r="O7" t="n">
-        <v>0.276</v>
+        <v>0.448</v>
       </c>
       <c r="P7" t="n">
-        <v>0.211</v>
+        <v>0.419</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.174</v>
+        <v>0.372</v>
       </c>
       <c r="R7" t="n">
-        <v>0.144</v>
+        <v>0.326</v>
       </c>
       <c r="S7" t="n">
-        <v>0.098</v>
+        <v>0.243</v>
       </c>
       <c r="T7" t="n">
-        <v>0.076</v>
+        <v>0.185</v>
       </c>
       <c r="U7" t="n">
-        <v>0.045</v>
+        <v>0.116</v>
       </c>
       <c r="V7" t="n">
         <v>0.038</v>
@@ -1655,68 +1463,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>xrai</t>
+          <t>dinov2_PC1</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0.829</v>
       </c>
       <c r="C8" t="n">
-        <v>0.822</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.795</v>
       </c>
       <c r="E8" t="n">
-        <v>0.783</v>
+        <v>0.78</v>
       </c>
       <c r="F8" t="n">
-        <v>0.757</v>
+        <v>0.773</v>
       </c>
       <c r="G8" t="n">
-        <v>0.732</v>
+        <v>0.746</v>
       </c>
       <c r="H8" t="n">
-        <v>0.695</v>
+        <v>0.731</v>
       </c>
       <c r="I8" t="n">
-        <v>0.654</v>
+        <v>0.71</v>
       </c>
       <c r="J8" t="n">
-        <v>0.617</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.673</v>
       </c>
       <c r="L8" t="n">
-        <v>0.506</v>
+        <v>0.641</v>
       </c>
       <c r="M8" t="n">
-        <v>0.436</v>
+        <v>0.608</v>
       </c>
       <c r="N8" t="n">
-        <v>0.391</v>
+        <v>0.58</v>
       </c>
       <c r="O8" t="n">
-        <v>0.336</v>
+        <v>0.53</v>
       </c>
       <c r="P8" t="n">
-        <v>0.286</v>
+        <v>0.463</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.224</v>
+        <v>0.393</v>
       </c>
       <c r="R8" t="n">
-        <v>0.173</v>
+        <v>0.314</v>
       </c>
       <c r="S8" t="n">
-        <v>0.125</v>
+        <v>0.245</v>
       </c>
       <c r="T8" t="n">
-        <v>0.066</v>
+        <v>0.156</v>
       </c>
       <c r="U8" t="n">
-        <v>0.042</v>
+        <v>0.068</v>
       </c>
       <c r="V8" t="n">
         <v>0.038</v>
@@ -1725,68 +1533,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>dinov2_attention</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0.829</v>
       </c>
       <c r="C9" t="n">
-        <v>0.822</v>
+        <v>0.82</v>
       </c>
       <c r="D9" t="n">
-        <v>0.799</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.773</v>
+        <v>0.797</v>
       </c>
       <c r="F9" t="n">
-        <v>0.744</v>
+        <v>0.781</v>
       </c>
       <c r="G9" t="n">
-        <v>0.729</v>
+        <v>0.772</v>
       </c>
       <c r="H9" t="n">
-        <v>0.714</v>
+        <v>0.758</v>
       </c>
       <c r="I9" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="J9" t="n">
-        <v>0.633</v>
+        <v>0.705</v>
       </c>
       <c r="K9" t="n">
-        <v>0.608</v>
+        <v>0.672</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.656</v>
       </c>
       <c r="M9" t="n">
-        <v>0.525</v>
+        <v>0.61</v>
       </c>
       <c r="N9" t="n">
-        <v>0.486</v>
+        <v>0.569</v>
       </c>
       <c r="O9" t="n">
-        <v>0.448</v>
+        <v>0.533</v>
       </c>
       <c r="P9" t="n">
-        <v>0.419</v>
+        <v>0.478</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.372</v>
+        <v>0.417</v>
       </c>
       <c r="R9" t="n">
-        <v>0.326</v>
+        <v>0.343</v>
       </c>
       <c r="S9" t="n">
-        <v>0.243</v>
+        <v>0.262</v>
       </c>
       <c r="T9" t="n">
-        <v>0.185</v>
+        <v>0.191</v>
       </c>
       <c r="U9" t="n">
-        <v>0.116</v>
+        <v>0.106</v>
       </c>
       <c r="V9" t="n">
         <v>0.038</v>
@@ -1795,68 +1603,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>dinov2_COMBO_FIXED</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0.829</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.827</v>
       </c>
       <c r="D10" t="n">
-        <v>0.795</v>
+        <v>0.797</v>
       </c>
       <c r="E10" t="n">
-        <v>0.78</v>
+        <v>0.788</v>
       </c>
       <c r="F10" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="G10" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="H10" t="n">
-        <v>0.731</v>
+        <v>0.739</v>
       </c>
       <c r="I10" t="n">
-        <v>0.71</v>
+        <v>0.725</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="K10" t="n">
-        <v>0.673</v>
+        <v>0.679</v>
       </c>
       <c r="L10" t="n">
-        <v>0.641</v>
+        <v>0.649</v>
       </c>
       <c r="M10" t="n">
-        <v>0.608</v>
+        <v>0.622</v>
       </c>
       <c r="N10" t="n">
-        <v>0.58</v>
+        <v>0.588</v>
       </c>
       <c r="O10" t="n">
-        <v>0.53</v>
+        <v>0.533</v>
       </c>
       <c r="P10" t="n">
-        <v>0.463</v>
+        <v>0.476</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.393</v>
+        <v>0.426</v>
       </c>
       <c r="R10" t="n">
-        <v>0.314</v>
+        <v>0.354</v>
       </c>
       <c r="S10" t="n">
-        <v>0.245</v>
+        <v>0.243</v>
       </c>
       <c r="T10" t="n">
-        <v>0.156</v>
+        <v>0.166</v>
       </c>
       <c r="U10" t="n">
-        <v>0.068</v>
+        <v>0.078</v>
       </c>
       <c r="V10" t="n">
         <v>0.038</v>
@@ -1865,68 +1673,68 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>inputxgradient_u2net_fill</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0.829</v>
       </c>
       <c r="C11" t="n">
-        <v>0.82</v>
+        <v>0.822</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.797</v>
+        <v>0.804</v>
       </c>
       <c r="F11" t="n">
         <v>0.781</v>
       </c>
       <c r="G11" t="n">
-        <v>0.772</v>
+        <v>0.761</v>
       </c>
       <c r="H11" t="n">
-        <v>0.758</v>
+        <v>0.742</v>
       </c>
       <c r="I11" t="n">
-        <v>0.733</v>
+        <v>0.714</v>
       </c>
       <c r="J11" t="n">
-        <v>0.705</v>
+        <v>0.677</v>
       </c>
       <c r="K11" t="n">
-        <v>0.672</v>
+        <v>0.645</v>
       </c>
       <c r="L11" t="n">
-        <v>0.656</v>
+        <v>0.629</v>
       </c>
       <c r="M11" t="n">
-        <v>0.61</v>
+        <v>0.594</v>
       </c>
       <c r="N11" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.533</v>
+        <v>0.515</v>
       </c>
       <c r="P11" t="n">
-        <v>0.478</v>
+        <v>0.482</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.417</v>
+        <v>0.441</v>
       </c>
       <c r="R11" t="n">
-        <v>0.343</v>
+        <v>0.384</v>
       </c>
       <c r="S11" t="n">
-        <v>0.262</v>
+        <v>0.305</v>
       </c>
       <c r="T11" t="n">
-        <v>0.191</v>
+        <v>0.213</v>
       </c>
       <c r="U11" t="n">
-        <v>0.106</v>
+        <v>0.109</v>
       </c>
       <c r="V11" t="n">
         <v>0.038</v>
@@ -1935,68 +1743,68 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0.829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.827</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.797</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.788</v>
+        <v>0.796</v>
       </c>
       <c r="F12" t="n">
-        <v>0.771</v>
+        <v>0.791</v>
       </c>
       <c r="G12" t="n">
-        <v>0.748</v>
+        <v>0.781</v>
       </c>
       <c r="H12" t="n">
-        <v>0.739</v>
+        <v>0.764</v>
       </c>
       <c r="I12" t="n">
-        <v>0.725</v>
+        <v>0.754</v>
       </c>
       <c r="J12" t="n">
-        <v>0.704</v>
+        <v>0.745</v>
       </c>
       <c r="K12" t="n">
-        <v>0.679</v>
+        <v>0.728</v>
       </c>
       <c r="L12" t="n">
-        <v>0.649</v>
+        <v>0.698</v>
       </c>
       <c r="M12" t="n">
-        <v>0.622</v>
+        <v>0.667</v>
       </c>
       <c r="N12" t="n">
-        <v>0.588</v>
+        <v>0.629</v>
       </c>
       <c r="O12" t="n">
-        <v>0.533</v>
+        <v>0.593</v>
       </c>
       <c r="P12" t="n">
-        <v>0.476</v>
+        <v>0.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.426</v>
+        <v>0.493</v>
       </c>
       <c r="R12" t="n">
-        <v>0.354</v>
+        <v>0.425</v>
       </c>
       <c r="S12" t="n">
-        <v>0.243</v>
+        <v>0.324</v>
       </c>
       <c r="T12" t="n">
-        <v>0.166</v>
+        <v>0.221</v>
       </c>
       <c r="U12" t="n">
-        <v>0.078</v>
+        <v>0.115</v>
       </c>
       <c r="V12" t="n">
         <v>0.038</v>
@@ -2005,495 +1813,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inputxgradient_u2net_fill</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0.829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.822</v>
+        <v>0.823</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.804</v>
+        <v>0.806</v>
       </c>
       <c r="F13" t="n">
-        <v>0.781</v>
+        <v>0.802</v>
       </c>
       <c r="G13" t="n">
-        <v>0.761</v>
+        <v>0.794</v>
       </c>
       <c r="H13" t="n">
-        <v>0.742</v>
+        <v>0.789</v>
       </c>
       <c r="I13" t="n">
-        <v>0.714</v>
+        <v>0.774</v>
       </c>
       <c r="J13" t="n">
-        <v>0.677</v>
+        <v>0.757</v>
       </c>
       <c r="K13" t="n">
-        <v>0.645</v>
+        <v>0.741</v>
       </c>
       <c r="L13" t="n">
-        <v>0.629</v>
+        <v>0.716</v>
       </c>
       <c r="M13" t="n">
-        <v>0.594</v>
+        <v>0.703</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.674</v>
       </c>
       <c r="O13" t="n">
-        <v>0.515</v>
+        <v>0.635</v>
       </c>
       <c r="P13" t="n">
-        <v>0.482</v>
+        <v>0.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.441</v>
+        <v>0.552</v>
       </c>
       <c r="R13" t="n">
-        <v>0.384</v>
+        <v>0.48</v>
       </c>
       <c r="S13" t="n">
-        <v>0.305</v>
+        <v>0.403</v>
       </c>
       <c r="T13" t="n">
-        <v>0.213</v>
+        <v>0.288</v>
       </c>
       <c r="U13" t="n">
-        <v>0.109</v>
+        <v>0.157</v>
       </c>
       <c r="V13" t="n">
         <v>0.038</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>u2net_dino_fusion</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.803</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.743</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.631</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>U2Net-Saliency</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.8169999999999999</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.626</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.534</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>guided_backprop</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.796</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dinov2_COMBO_ENT_SMOOTH</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.737</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.723</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.709</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>guided_gradcam</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>grad_cam</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.821</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.637</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.184</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V19">
+  <conditionalFormatting sqref="B2:V13">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Top-1 Accuracy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Top-5 Accuracy" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -159,7 +160,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Accuracy Degradation</a:t>
+              <a:t>Top-1 Accuracy Degradation</a:t>
             </a:r>
           </a:p>
           <a:p>
@@ -181,7 +182,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Data'!A2</f>
+              <f>'Top-1 Accuracy'!A2</f>
             </strRef>
           </tx>
           <spPr>
@@ -199,12 +200,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$2:$V$2</f>
+              <f>'Top-1 Accuracy'!$B$2:$V$2</f>
             </numRef>
           </val>
         </ser>
@@ -213,7 +214,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Data'!A3</f>
+              <f>'Top-1 Accuracy'!A3</f>
             </strRef>
           </tx>
           <spPr>
@@ -231,12 +232,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$3:$V$3</f>
+              <f>'Top-1 Accuracy'!$B$3:$V$3</f>
             </numRef>
           </val>
         </ser>
@@ -245,7 +246,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Data'!A4</f>
+              <f>'Top-1 Accuracy'!A4</f>
             </strRef>
           </tx>
           <spPr>
@@ -263,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$4:$V$4</f>
+              <f>'Top-1 Accuracy'!$B$4:$V$4</f>
             </numRef>
           </val>
         </ser>
@@ -277,7 +278,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Data'!A5</f>
+              <f>'Top-1 Accuracy'!A5</f>
             </strRef>
           </tx>
           <spPr>
@@ -295,12 +296,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$5:$V$5</f>
+              <f>'Top-1 Accuracy'!$B$5:$V$5</f>
             </numRef>
           </val>
         </ser>
@@ -309,7 +310,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Data'!A6</f>
+              <f>'Top-1 Accuracy'!A6</f>
             </strRef>
           </tx>
           <spPr>
@@ -327,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$6:$V$6</f>
+              <f>'Top-1 Accuracy'!$B$6:$V$6</f>
             </numRef>
           </val>
         </ser>
@@ -341,7 +342,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Data'!A7</f>
+              <f>'Top-1 Accuracy'!A7</f>
             </strRef>
           </tx>
           <spPr>
@@ -359,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$7:$V$7</f>
+              <f>'Top-1 Accuracy'!$B$7:$V$7</f>
             </numRef>
           </val>
         </ser>
@@ -373,7 +374,7 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'Data'!A8</f>
+              <f>'Top-1 Accuracy'!A8</f>
             </strRef>
           </tx>
           <spPr>
@@ -391,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$8:$V$8</f>
+              <f>'Top-1 Accuracy'!$B$8:$V$8</f>
             </numRef>
           </val>
         </ser>
@@ -405,7 +406,7 @@
           <order val="7"/>
           <tx>
             <strRef>
-              <f>'Data'!A9</f>
+              <f>'Top-1 Accuracy'!A9</f>
             </strRef>
           </tx>
           <spPr>
@@ -423,12 +424,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$9:$V$9</f>
+              <f>'Top-1 Accuracy'!$B$9:$V$9</f>
             </numRef>
           </val>
         </ser>
@@ -437,7 +438,7 @@
           <order val="8"/>
           <tx>
             <strRef>
-              <f>'Data'!A10</f>
+              <f>'Top-1 Accuracy'!A10</f>
             </strRef>
           </tx>
           <spPr>
@@ -455,12 +456,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$10:$V$10</f>
+              <f>'Top-1 Accuracy'!$B$10:$V$10</f>
             </numRef>
           </val>
         </ser>
@@ -469,7 +470,7 @@
           <order val="9"/>
           <tx>
             <strRef>
-              <f>'Data'!A11</f>
+              <f>'Top-1 Accuracy'!A11</f>
             </strRef>
           </tx>
           <spPr>
@@ -487,76 +488,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Data'!$B$1:$V$1</f>
+              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data'!$B$11:$V$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="10"/>
-          <order val="10"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$12:$V$12</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="11"/>
-          <order val="11"/>
-          <tx>
-            <strRef>
-              <f>'Data'!A13</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Data'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Data'!$B$13:$V$13</f>
+              <f>'Top-1 Accuracy'!$B$11:$V$11</f>
             </numRef>
           </val>
         </ser>
@@ -627,13 +564,457 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Top-5 Accuracy Degradation</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Generator: resnet50 | Judge: vgg16 | Fill: blur</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$2:$V$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$3:$V$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$4:$V$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$5:$V$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$6:$V$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$7:$V$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$8:$V$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$9:$V$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$10:$V$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Top-5 Accuracy'!A11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Top-5 Accuracy'!$B$11:$V$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Occlusion Level (%)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.05"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Top-5 Accuracy</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="tr"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9000000" cy="5400000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -943,11 +1324,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1043,845 +1424,1526 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inputxgradient</t>
+          <t>random_baseline</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.9199199199199199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.829</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.787</v>
-      </c>
       <c r="E2" t="n">
-        <v>0.753</v>
+        <v>0.784</v>
       </c>
       <c r="F2" t="n">
-        <v>0.719</v>
+        <v>0.74</v>
       </c>
       <c r="G2" t="n">
-        <v>0.68</v>
+        <v>0.698</v>
       </c>
       <c r="H2" t="n">
-        <v>0.627</v>
+        <v>0.634</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="J2" t="n">
-        <v>0.498</v>
+        <v>0.479</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.399</v>
       </c>
       <c r="L2" t="n">
-        <v>0.404</v>
+        <v>0.328</v>
       </c>
       <c r="M2" t="n">
-        <v>0.343</v>
+        <v>0.256</v>
       </c>
       <c r="N2" t="n">
-        <v>0.263</v>
+        <v>0.181</v>
       </c>
       <c r="O2" t="n">
-        <v>0.209</v>
+        <v>0.129</v>
       </c>
       <c r="P2" t="n">
-        <v>0.15</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.106</v>
+        <v>0.061</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.042</v>
       </c>
       <c r="S2" t="n">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="T2" t="n">
         <v>0.027</v>
       </c>
       <c r="U2" t="n">
-        <v>0.018</v>
+        <v>0.021</v>
       </c>
       <c r="V2" t="n">
-        <v>0.038</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>inputxgradient</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0.9199199199199199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.829</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.711</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.662</v>
+        <v>0.798</v>
       </c>
       <c r="I3" t="n">
-        <v>0.632</v>
+        <v>0.75</v>
       </c>
       <c r="J3" t="n">
-        <v>0.576</v>
+        <v>0.734</v>
       </c>
       <c r="K3" t="n">
-        <v>0.53</v>
+        <v>0.681</v>
       </c>
       <c r="L3" t="n">
-        <v>0.469</v>
+        <v>0.637</v>
       </c>
       <c r="M3" t="n">
-        <v>0.403</v>
+        <v>0.578</v>
       </c>
       <c r="N3" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.348</v>
       </c>
-      <c r="O3" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.152</v>
-      </c>
       <c r="R3" t="n">
-        <v>0.111</v>
+        <v>0.291</v>
       </c>
       <c r="S3" t="n">
-        <v>0.066</v>
+        <v>0.243</v>
       </c>
       <c r="T3" t="n">
-        <v>0.035</v>
+        <v>0.174</v>
       </c>
       <c r="U3" t="n">
-        <v>0.015</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0.038</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.9199199199199199</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="G4" t="n">
         <v>0.829</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.759</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.716</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.679</v>
+        <v>0.799</v>
       </c>
       <c r="I4" t="n">
-        <v>0.636</v>
+        <v>0.765</v>
       </c>
       <c r="J4" t="n">
-        <v>0.585</v>
+        <v>0.73</v>
       </c>
       <c r="K4" t="n">
-        <v>0.524</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.471</v>
+        <v>0.652</v>
       </c>
       <c r="M4" t="n">
-        <v>0.413</v>
+        <v>0.612</v>
       </c>
       <c r="N4" t="n">
-        <v>0.351</v>
+        <v>0.556</v>
       </c>
       <c r="O4" t="n">
-        <v>0.286</v>
+        <v>0.507</v>
       </c>
       <c r="P4" t="n">
-        <v>0.215</v>
+        <v>0.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.164</v>
+        <v>0.401</v>
       </c>
       <c r="R4" t="n">
-        <v>0.11</v>
+        <v>0.336</v>
       </c>
       <c r="S4" t="n">
-        <v>0.065</v>
+        <v>0.276</v>
       </c>
       <c r="T4" t="n">
-        <v>0.038</v>
+        <v>0.244</v>
       </c>
       <c r="U4" t="n">
-        <v>0.017</v>
+        <v>0.191</v>
       </c>
       <c r="V4" t="n">
-        <v>0.038</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>inputxgradient_continuous</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.829</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.907</v>
       </c>
       <c r="D5" t="n">
-        <v>0.799</v>
+        <v>0.898</v>
       </c>
       <c r="E5" t="n">
-        <v>0.768</v>
+        <v>0.883</v>
       </c>
       <c r="F5" t="n">
-        <v>0.73</v>
+        <v>0.862</v>
       </c>
       <c r="G5" t="n">
-        <v>0.697</v>
+        <v>0.85</v>
       </c>
       <c r="H5" t="n">
-        <v>0.644</v>
+        <v>0.834</v>
       </c>
       <c r="I5" t="n">
-        <v>0.594</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.542</v>
+        <v>0.775</v>
       </c>
       <c r="K5" t="n">
-        <v>0.473</v>
+        <v>0.741</v>
       </c>
       <c r="L5" t="n">
-        <v>0.432</v>
+        <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.377</v>
+        <v>0.663</v>
       </c>
       <c r="N5" t="n">
-        <v>0.324</v>
+        <v>0.603</v>
       </c>
       <c r="O5" t="n">
-        <v>0.276</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.211</v>
+        <v>0.493</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.174</v>
+        <v>0.433</v>
       </c>
       <c r="R5" t="n">
-        <v>0.144</v>
+        <v>0.356</v>
       </c>
       <c r="S5" t="n">
-        <v>0.098</v>
+        <v>0.287</v>
       </c>
       <c r="T5" t="n">
-        <v>0.076</v>
+        <v>0.217</v>
       </c>
       <c r="U5" t="n">
-        <v>0.045</v>
+        <v>0.148</v>
       </c>
       <c r="V5" t="n">
-        <v>0.038</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xrai</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.829</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C6" t="n">
-        <v>0.822</v>
+        <v>0.909</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.891</v>
       </c>
       <c r="E6" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.861</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.783</v>
       </c>
-      <c r="F6" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.654</v>
       </c>
-      <c r="J6" t="n">
-        <v>0.617</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.436</v>
-      </c>
       <c r="N6" t="n">
-        <v>0.391</v>
+        <v>0.605</v>
       </c>
       <c r="O6" t="n">
-        <v>0.336</v>
+        <v>0.553</v>
       </c>
       <c r="P6" t="n">
-        <v>0.286</v>
+        <v>0.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.224</v>
+        <v>0.439</v>
       </c>
       <c r="R6" t="n">
-        <v>0.173</v>
+        <v>0.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0.125</v>
+        <v>0.287</v>
       </c>
       <c r="T6" t="n">
-        <v>0.066</v>
+        <v>0.216</v>
       </c>
       <c r="U6" t="n">
-        <v>0.042</v>
+        <v>0.128</v>
       </c>
       <c r="V6" t="n">
-        <v>0.038</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>occlusion</t>
+          <t>grad_cam</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.829</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C7" t="n">
-        <v>0.822</v>
+        <v>0.904</v>
       </c>
       <c r="D7" t="n">
-        <v>0.799</v>
+        <v>0.889</v>
       </c>
       <c r="E7" t="n">
-        <v>0.773</v>
+        <v>0.874</v>
       </c>
       <c r="F7" t="n">
-        <v>0.744</v>
+        <v>0.853</v>
       </c>
       <c r="G7" t="n">
-        <v>0.729</v>
+        <v>0.849</v>
       </c>
       <c r="H7" t="n">
-        <v>0.714</v>
+        <v>0.84</v>
       </c>
       <c r="I7" t="n">
-        <v>0.667</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.633</v>
+        <v>0.786</v>
       </c>
       <c r="K7" t="n">
-        <v>0.608</v>
+        <v>0.768</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="M7" t="n">
-        <v>0.525</v>
+        <v>0.709</v>
       </c>
       <c r="N7" t="n">
-        <v>0.486</v>
+        <v>0.674</v>
       </c>
       <c r="O7" t="n">
-        <v>0.448</v>
+        <v>0.624</v>
       </c>
       <c r="P7" t="n">
-        <v>0.419</v>
+        <v>0.555</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.372</v>
+        <v>0.511</v>
       </c>
       <c r="R7" t="n">
-        <v>0.326</v>
+        <v>0.446</v>
       </c>
       <c r="S7" t="n">
-        <v>0.243</v>
+        <v>0.352</v>
       </c>
       <c r="T7" t="n">
-        <v>0.185</v>
+        <v>0.257</v>
       </c>
       <c r="U7" t="n">
-        <v>0.116</v>
+        <v>0.18</v>
       </c>
       <c r="V7" t="n">
-        <v>0.038</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dinov2_PC1</t>
+          <t>xrai</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.829</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.921</v>
       </c>
       <c r="D8" t="n">
-        <v>0.795</v>
+        <v>0.917</v>
       </c>
       <c r="E8" t="n">
-        <v>0.78</v>
+        <v>0.916</v>
       </c>
       <c r="F8" t="n">
-        <v>0.773</v>
+        <v>0.914</v>
       </c>
       <c r="G8" t="n">
-        <v>0.746</v>
+        <v>0.897</v>
       </c>
       <c r="H8" t="n">
-        <v>0.731</v>
+        <v>0.889</v>
       </c>
       <c r="I8" t="n">
-        <v>0.71</v>
+        <v>0.874</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.859</v>
       </c>
       <c r="K8" t="n">
-        <v>0.673</v>
+        <v>0.838</v>
       </c>
       <c r="L8" t="n">
-        <v>0.641</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.608</v>
+        <v>0.769</v>
       </c>
       <c r="N8" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="O8" t="n">
-        <v>0.53</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.463</v>
+        <v>0.632</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.393</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.314</v>
+        <v>0.482</v>
       </c>
       <c r="S8" t="n">
-        <v>0.245</v>
+        <v>0.385</v>
       </c>
       <c r="T8" t="n">
-        <v>0.156</v>
+        <v>0.279</v>
       </c>
       <c r="U8" t="n">
-        <v>0.068</v>
+        <v>0.162</v>
       </c>
       <c r="V8" t="n">
-        <v>0.038</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dinov2_attention</t>
+          <t>guided_gradcam</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.829</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C9" t="n">
-        <v>0.82</v>
+        <v>0.913</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.899</v>
       </c>
       <c r="E9" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.797</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.772</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.705</v>
-      </c>
       <c r="K9" t="n">
-        <v>0.672</v>
+        <v>0.778</v>
       </c>
       <c r="L9" t="n">
-        <v>0.656</v>
+        <v>0.764</v>
       </c>
       <c r="M9" t="n">
-        <v>0.61</v>
+        <v>0.731</v>
       </c>
       <c r="N9" t="n">
-        <v>0.569</v>
+        <v>0.704</v>
       </c>
       <c r="O9" t="n">
-        <v>0.533</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0.478</v>
+        <v>0.627</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.417</v>
+        <v>0.581</v>
       </c>
       <c r="R9" t="n">
-        <v>0.343</v>
+        <v>0.506</v>
       </c>
       <c r="S9" t="n">
-        <v>0.262</v>
+        <v>0.416</v>
       </c>
       <c r="T9" t="n">
-        <v>0.191</v>
+        <v>0.335</v>
       </c>
       <c r="U9" t="n">
-        <v>0.106</v>
+        <v>0.209</v>
       </c>
       <c r="V9" t="n">
-        <v>0.038</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dinov2_COMBO_FIXED</t>
+          <t>occlusion</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.829</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C10" t="n">
-        <v>0.827</v>
+        <v>0.917</v>
       </c>
       <c r="D10" t="n">
-        <v>0.797</v>
+        <v>0.92</v>
       </c>
       <c r="E10" t="n">
-        <v>0.788</v>
+        <v>0.915</v>
       </c>
       <c r="F10" t="n">
-        <v>0.771</v>
+        <v>0.916</v>
       </c>
       <c r="G10" t="n">
-        <v>0.748</v>
+        <v>0.911</v>
       </c>
       <c r="H10" t="n">
-        <v>0.739</v>
+        <v>0.905</v>
       </c>
       <c r="I10" t="n">
-        <v>0.725</v>
+        <v>0.89</v>
       </c>
       <c r="J10" t="n">
-        <v>0.704</v>
+        <v>0.882</v>
       </c>
       <c r="K10" t="n">
-        <v>0.679</v>
+        <v>0.868</v>
       </c>
       <c r="L10" t="n">
-        <v>0.649</v>
+        <v>0.866</v>
       </c>
       <c r="M10" t="n">
-        <v>0.622</v>
+        <v>0.836</v>
       </c>
       <c r="N10" t="n">
-        <v>0.588</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.533</v>
+        <v>0.782</v>
       </c>
       <c r="P10" t="n">
-        <v>0.476</v>
+        <v>0.751</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.426</v>
+        <v>0.719</v>
       </c>
       <c r="R10" t="n">
-        <v>0.354</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.243</v>
+        <v>0.632</v>
       </c>
       <c r="T10" t="n">
-        <v>0.166</v>
+        <v>0.54</v>
       </c>
       <c r="U10" t="n">
-        <v>0.078</v>
+        <v>0.409</v>
       </c>
       <c r="V10" t="n">
-        <v>0.038</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>inputxgradient_u2net_fill</t>
+          <t>guided_backprop</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.829</v>
+        <v>0.9199199199199199</v>
       </c>
       <c r="C11" t="n">
-        <v>0.822</v>
+        <v>0.912</v>
       </c>
       <c r="D11" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.163</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:V11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>attribution_method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>random_baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>inputxgradient</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.8139999999999999</v>
       </c>
-      <c r="E11" t="n">
+      <c r="M3" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>saliency</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.372</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>integrated_gradients</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gradientshap</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>grad_cam</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.804</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.5629999999999999</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.038</v>
+      <c r="P7" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.31</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>xrai</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>guided_gradcam</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>occlusion</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>guided_backprop</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8179999999999999</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.796</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.698</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.038</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>guided_gradcam</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.829</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.038</v>
+      <c r="B11" t="n">
+        <v>0.98998998998999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V13">
+  <conditionalFormatting sqref="B2:V11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -369,134 +369,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Top-1 Accuracy'!A8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Top-1 Accuracy'!$B$8:$V$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Top-1 Accuracy'!A9</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Top-1 Accuracy'!$B$9:$V$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'Top-1 Accuracy'!A10</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Top-1 Accuracy'!$B$10:$V$10</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'Top-1 Accuracy'!A11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Top-1 Accuracy'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Top-1 Accuracy'!$B$11:$V$11</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -786,134 +658,6 @@
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'Top-5 Accuracy'!A8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Top-5 Accuracy'!$B$8:$V$8</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Top-5 Accuracy'!A9</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Top-5 Accuracy'!$B$9:$V$9</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'Top-5 Accuracy'!A10</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Top-5 Accuracy'!$B$10:$V$10</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'Top-5 Accuracy'!A11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Top-5 Accuracy'!$B$1:$V$1</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Top-5 Accuracy'!$B$11:$V$11</f>
-            </numRef>
-          </val>
-        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -987,7 +731,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1014,7 +758,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9000000" cy="5400000"/>
@@ -1324,11 +1068,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1424,50 +1168,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9199199199199199</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.882</v>
+        <v>0.775</v>
       </c>
       <c r="D2" t="n">
-        <v>0.829</v>
+        <v>0.76</v>
       </c>
       <c r="E2" t="n">
-        <v>0.784</v>
+        <v>0.705</v>
       </c>
       <c r="F2" t="n">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="G2" t="n">
-        <v>0.698</v>
+        <v>0.604</v>
       </c>
       <c r="H2" t="n">
-        <v>0.634</v>
+        <v>0.553</v>
       </c>
       <c r="I2" t="n">
-        <v>0.547</v>
+        <v>0.496</v>
       </c>
       <c r="J2" t="n">
-        <v>0.479</v>
+        <v>0.431</v>
       </c>
       <c r="K2" t="n">
-        <v>0.399</v>
+        <v>0.365</v>
       </c>
       <c r="L2" t="n">
-        <v>0.328</v>
+        <v>0.286</v>
       </c>
       <c r="M2" t="n">
-        <v>0.256</v>
+        <v>0.217</v>
       </c>
       <c r="N2" t="n">
-        <v>0.181</v>
+        <v>0.154</v>
       </c>
       <c r="O2" t="n">
-        <v>0.129</v>
+        <v>0.113</v>
       </c>
       <c r="P2" t="n">
         <v>0.08799999999999999</v>
@@ -1476,19 +1220,19 @@
         <v>0.061</v>
       </c>
       <c r="R2" t="n">
-        <v>0.042</v>
+        <v>0.034</v>
       </c>
       <c r="S2" t="n">
-        <v>0.037</v>
+        <v>0.018</v>
       </c>
       <c r="T2" t="n">
-        <v>0.027</v>
+        <v>0.017</v>
       </c>
       <c r="U2" t="n">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="V2" t="n">
-        <v>0.163</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="3">
@@ -1498,277 +1242,277 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9199199199199199</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.905</v>
+        <v>0.795</v>
       </c>
       <c r="D3" t="n">
-        <v>0.886</v>
+        <v>0.753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.862</v>
+        <v>0.71</v>
       </c>
       <c r="F3" t="n">
-        <v>0.845</v>
+        <v>0.666</v>
       </c>
       <c r="G3" t="n">
-        <v>0.829</v>
+        <v>0.632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.798</v>
+        <v>0.575</v>
       </c>
       <c r="I3" t="n">
-        <v>0.75</v>
+        <v>0.518</v>
       </c>
       <c r="J3" t="n">
-        <v>0.734</v>
+        <v>0.462</v>
       </c>
       <c r="K3" t="n">
-        <v>0.681</v>
+        <v>0.387</v>
       </c>
       <c r="L3" t="n">
-        <v>0.637</v>
+        <v>0.316</v>
       </c>
       <c r="M3" t="n">
-        <v>0.578</v>
+        <v>0.228</v>
       </c>
       <c r="N3" t="n">
-        <v>0.516</v>
+        <v>0.182</v>
       </c>
       <c r="O3" t="n">
-        <v>0.461</v>
+        <v>0.135</v>
       </c>
       <c r="P3" t="n">
-        <v>0.406</v>
+        <v>0.095</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.348</v>
+        <v>0.062</v>
       </c>
       <c r="R3" t="n">
-        <v>0.291</v>
+        <v>0.033</v>
       </c>
       <c r="S3" t="n">
-        <v>0.243</v>
+        <v>0.018</v>
       </c>
       <c r="T3" t="n">
-        <v>0.174</v>
+        <v>0.016</v>
       </c>
       <c r="U3" t="n">
-        <v>0.12</v>
+        <v>0.015</v>
       </c>
       <c r="V3" t="n">
-        <v>0.163</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9199199199199199</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>0.908</v>
+        <v>0.803</v>
       </c>
       <c r="D4" t="n">
-        <v>0.896</v>
+        <v>0.773</v>
       </c>
       <c r="E4" t="n">
-        <v>0.882</v>
+        <v>0.734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.864</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.829</v>
+        <v>0.648</v>
       </c>
       <c r="H4" t="n">
-        <v>0.799</v>
+        <v>0.615</v>
       </c>
       <c r="I4" t="n">
-        <v>0.765</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.73</v>
+        <v>0.508</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.443</v>
       </c>
       <c r="L4" t="n">
-        <v>0.652</v>
+        <v>0.384</v>
       </c>
       <c r="M4" t="n">
-        <v>0.612</v>
+        <v>0.311</v>
       </c>
       <c r="N4" t="n">
-        <v>0.556</v>
+        <v>0.239</v>
       </c>
       <c r="O4" t="n">
-        <v>0.507</v>
+        <v>0.188</v>
       </c>
       <c r="P4" t="n">
-        <v>0.45</v>
+        <v>0.141</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.401</v>
+        <v>0.102</v>
       </c>
       <c r="R4" t="n">
-        <v>0.336</v>
+        <v>0.063</v>
       </c>
       <c r="S4" t="n">
-        <v>0.276</v>
+        <v>0.031</v>
       </c>
       <c r="T4" t="n">
-        <v>0.244</v>
+        <v>0.016</v>
       </c>
       <c r="U4" t="n">
-        <v>0.191</v>
+        <v>0.015</v>
       </c>
       <c r="V4" t="n">
-        <v>0.231</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>integrated_gradients</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9199199199199199</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.907</v>
+        <v>0.799</v>
       </c>
       <c r="D5" t="n">
-        <v>0.898</v>
+        <v>0.776</v>
       </c>
       <c r="E5" t="n">
-        <v>0.883</v>
+        <v>0.743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.862</v>
+        <v>0.711</v>
       </c>
       <c r="G5" t="n">
-        <v>0.85</v>
+        <v>0.666</v>
       </c>
       <c r="H5" t="n">
-        <v>0.834</v>
+        <v>0.627</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.584</v>
       </c>
       <c r="J5" t="n">
-        <v>0.775</v>
+        <v>0.53</v>
       </c>
       <c r="K5" t="n">
-        <v>0.741</v>
+        <v>0.479</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7</v>
+        <v>0.408</v>
       </c>
       <c r="M5" t="n">
-        <v>0.663</v>
+        <v>0.349</v>
       </c>
       <c r="N5" t="n">
-        <v>0.603</v>
+        <v>0.265</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.216</v>
       </c>
       <c r="P5" t="n">
-        <v>0.493</v>
+        <v>0.155</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.433</v>
+        <v>0.114</v>
       </c>
       <c r="R5" t="n">
-        <v>0.356</v>
+        <v>0.063</v>
       </c>
       <c r="S5" t="n">
-        <v>0.287</v>
+        <v>0.032</v>
       </c>
       <c r="T5" t="n">
-        <v>0.217</v>
+        <v>0.016</v>
       </c>
       <c r="U5" t="n">
-        <v>0.148</v>
+        <v>0.012</v>
       </c>
       <c r="V5" t="n">
-        <v>0.163</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>integrated_gradients</t>
+          <t>smoothgrad</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9199199199199199</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>0.909</v>
+        <v>0.819</v>
       </c>
       <c r="D6" t="n">
-        <v>0.891</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.882</v>
+        <v>0.782</v>
       </c>
       <c r="F6" t="n">
-        <v>0.861</v>
+        <v>0.763</v>
       </c>
       <c r="G6" t="n">
-        <v>0.843</v>
+        <v>0.741</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="I6" t="n">
-        <v>0.795</v>
+        <v>0.665</v>
       </c>
       <c r="J6" t="n">
-        <v>0.783</v>
+        <v>0.625</v>
       </c>
       <c r="K6" t="n">
-        <v>0.747</v>
+        <v>0.58</v>
       </c>
       <c r="L6" t="n">
-        <v>0.706</v>
+        <v>0.547</v>
       </c>
       <c r="M6" t="n">
-        <v>0.654</v>
+        <v>0.472</v>
       </c>
       <c r="N6" t="n">
-        <v>0.605</v>
+        <v>0.41</v>
       </c>
       <c r="O6" t="n">
-        <v>0.553</v>
+        <v>0.346</v>
       </c>
       <c r="P6" t="n">
-        <v>0.49</v>
+        <v>0.276</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.439</v>
+        <v>0.216</v>
       </c>
       <c r="R6" t="n">
-        <v>0.36</v>
+        <v>0.152</v>
       </c>
       <c r="S6" t="n">
-        <v>0.287</v>
+        <v>0.101</v>
       </c>
       <c r="T6" t="n">
-        <v>0.216</v>
+        <v>0.052</v>
       </c>
       <c r="U6" t="n">
-        <v>0.128</v>
+        <v>0.024</v>
       </c>
       <c r="V6" t="n">
-        <v>0.163</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="7">
@@ -1778,351 +1522,71 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9199199199199199</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.904</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.889</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.874</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.853</v>
+        <v>0.799</v>
       </c>
       <c r="G7" t="n">
-        <v>0.849</v>
+        <v>0.796</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>0.794</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.785</v>
       </c>
       <c r="J7" t="n">
-        <v>0.786</v>
+        <v>0.77</v>
       </c>
       <c r="K7" t="n">
-        <v>0.768</v>
+        <v>0.754</v>
       </c>
       <c r="L7" t="n">
-        <v>0.734</v>
+        <v>0.727</v>
       </c>
       <c r="M7" t="n">
         <v>0.709</v>
       </c>
       <c r="N7" t="n">
-        <v>0.674</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.624</v>
+        <v>0.67</v>
       </c>
       <c r="P7" t="n">
-        <v>0.555</v>
+        <v>0.634</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.511</v>
+        <v>0.579</v>
       </c>
       <c r="R7" t="n">
-        <v>0.446</v>
+        <v>0.497</v>
       </c>
       <c r="S7" t="n">
-        <v>0.352</v>
+        <v>0.41</v>
       </c>
       <c r="T7" t="n">
-        <v>0.257</v>
+        <v>0.317</v>
       </c>
       <c r="U7" t="n">
-        <v>0.18</v>
+        <v>0.164</v>
       </c>
       <c r="V7" t="n">
-        <v>0.163</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.9199199199199199</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.916</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.914</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.897</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.874</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.859</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.279</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.163</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>guided_gradcam</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.9199199199199199</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.832</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.764</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.163</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>occlusion</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.9199199199199199</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.916</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.911</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.866</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.782</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.163</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>guided_backprop</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9199199199199199</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.887</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.874</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.727</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.618</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.489</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.317</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.163</v>
+        <v>0.034</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V11">
+  <conditionalFormatting sqref="B2:V7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2145,11 +1609,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -2245,71 +1709,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>random_baseline</t>
+          <t>saliency</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.98998998998999</v>
+        <v>0.952</v>
       </c>
       <c r="C2" t="n">
-        <v>0.975</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.958</v>
+        <v>0.922</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.894</v>
       </c>
       <c r="F2" t="n">
-        <v>0.909</v>
+        <v>0.87</v>
       </c>
       <c r="G2" t="n">
-        <v>0.884</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.832</v>
+        <v>0.769</v>
       </c>
       <c r="I2" t="n">
-        <v>0.786</v>
+        <v>0.709</v>
       </c>
       <c r="J2" t="n">
-        <v>0.711</v>
+        <v>0.651</v>
       </c>
       <c r="K2" t="n">
-        <v>0.639</v>
+        <v>0.597</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.506</v>
       </c>
       <c r="M2" t="n">
-        <v>0.467</v>
+        <v>0.438</v>
       </c>
       <c r="N2" t="n">
-        <v>0.366</v>
+        <v>0.352</v>
       </c>
       <c r="O2" t="n">
-        <v>0.278</v>
+        <v>0.265</v>
       </c>
       <c r="P2" t="n">
-        <v>0.195</v>
+        <v>0.202</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.139</v>
+        <v>0.151</v>
       </c>
       <c r="R2" t="n">
-        <v>0.099</v>
+        <v>0.107</v>
       </c>
       <c r="S2" t="n">
-        <v>0.078</v>
+        <v>0.068</v>
       </c>
       <c r="T2" t="n">
-        <v>0.064</v>
+        <v>0.044</v>
       </c>
       <c r="U2" t="n">
-        <v>0.056</v>
+        <v>0.037</v>
       </c>
       <c r="V2" t="n">
-        <v>0.31</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="3">
@@ -2319,137 +1783,137 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.98998998998999</v>
+        <v>0.952</v>
       </c>
       <c r="C3" t="n">
-        <v>0.986</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.98</v>
+        <v>0.922</v>
       </c>
       <c r="E3" t="n">
-        <v>0.973</v>
+        <v>0.9</v>
       </c>
       <c r="F3" t="n">
-        <v>0.961</v>
+        <v>0.865</v>
       </c>
       <c r="G3" t="n">
-        <v>0.95</v>
+        <v>0.831</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.791</v>
       </c>
       <c r="I3" t="n">
-        <v>0.909</v>
+        <v>0.743</v>
       </c>
       <c r="J3" t="n">
-        <v>0.879</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.854</v>
+        <v>0.602</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.523</v>
       </c>
       <c r="M3" t="n">
-        <v>0.751</v>
+        <v>0.445</v>
       </c>
       <c r="N3" t="n">
-        <v>0.71</v>
+        <v>0.36</v>
       </c>
       <c r="O3" t="n">
-        <v>0.644</v>
+        <v>0.282</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>0.221</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.521</v>
+        <v>0.156</v>
       </c>
       <c r="R3" t="n">
-        <v>0.444</v>
+        <v>0.108</v>
       </c>
       <c r="S3" t="n">
-        <v>0.373</v>
+        <v>0.067</v>
       </c>
       <c r="T3" t="n">
-        <v>0.309</v>
+        <v>0.042</v>
       </c>
       <c r="U3" t="n">
-        <v>0.255</v>
+        <v>0.04</v>
       </c>
       <c r="V3" t="n">
-        <v>0.31</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>saliency</t>
+          <t>gradientshap</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.98998998998999</v>
+        <v>0.952</v>
       </c>
       <c r="C4" t="n">
-        <v>0.985</v>
+        <v>0.945</v>
       </c>
       <c r="D4" t="n">
-        <v>0.982</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.973</v>
+        <v>0.917</v>
       </c>
       <c r="F4" t="n">
-        <v>0.963</v>
+        <v>0.892</v>
       </c>
       <c r="G4" t="n">
-        <v>0.95</v>
+        <v>0.857</v>
       </c>
       <c r="H4" t="n">
-        <v>0.925</v>
+        <v>0.822</v>
       </c>
       <c r="I4" t="n">
-        <v>0.898</v>
+        <v>0.793</v>
       </c>
       <c r="J4" t="n">
-        <v>0.88</v>
+        <v>0.735</v>
       </c>
       <c r="K4" t="n">
-        <v>0.85</v>
+        <v>0.681</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>0.768</v>
+        <v>0.545</v>
       </c>
       <c r="N4" t="n">
-        <v>0.726</v>
+        <v>0.465</v>
       </c>
       <c r="O4" t="n">
-        <v>0.673</v>
+        <v>0.365</v>
       </c>
       <c r="P4" t="n">
-        <v>0.609</v>
+        <v>0.285</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.208</v>
       </c>
       <c r="R4" t="n">
-        <v>0.492</v>
+        <v>0.158</v>
       </c>
       <c r="S4" t="n">
-        <v>0.419</v>
+        <v>0.101</v>
       </c>
       <c r="T4" t="n">
-        <v>0.355</v>
+        <v>0.055</v>
       </c>
       <c r="U4" t="n">
-        <v>0.303</v>
+        <v>0.042</v>
       </c>
       <c r="V4" t="n">
-        <v>0.372</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="5">
@@ -2459,137 +1923,137 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.98998998998999</v>
+        <v>0.952</v>
       </c>
       <c r="C5" t="n">
-        <v>0.986</v>
+        <v>0.946</v>
       </c>
       <c r="D5" t="n">
-        <v>0.977</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.972</v>
+        <v>0.917</v>
       </c>
       <c r="F5" t="n">
-        <v>0.972</v>
+        <v>0.899</v>
       </c>
       <c r="G5" t="n">
-        <v>0.963</v>
+        <v>0.867</v>
       </c>
       <c r="H5" t="n">
-        <v>0.951</v>
+        <v>0.844</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.918</v>
+        <v>0.762</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="L5" t="n">
-        <v>0.866</v>
+        <v>0.664</v>
       </c>
       <c r="M5" t="n">
-        <v>0.835</v>
+        <v>0.579</v>
       </c>
       <c r="N5" t="n">
-        <v>0.798</v>
+        <v>0.484</v>
       </c>
       <c r="O5" t="n">
-        <v>0.745</v>
+        <v>0.407</v>
       </c>
       <c r="P5" t="n">
-        <v>0.677</v>
+        <v>0.318</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.616</v>
+        <v>0.252</v>
       </c>
       <c r="R5" t="n">
-        <v>0.535</v>
+        <v>0.181</v>
       </c>
       <c r="S5" t="n">
-        <v>0.462</v>
+        <v>0.115</v>
       </c>
       <c r="T5" t="n">
-        <v>0.348</v>
+        <v>0.061</v>
       </c>
       <c r="U5" t="n">
-        <v>0.271</v>
+        <v>0.046</v>
       </c>
       <c r="V5" t="n">
-        <v>0.31</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gradientshap</t>
+          <t>smoothgrad</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.98998998998999</v>
+        <v>0.952</v>
       </c>
       <c r="C6" t="n">
-        <v>0.989</v>
+        <v>0.956</v>
       </c>
       <c r="D6" t="n">
-        <v>0.981</v>
+        <v>0.953</v>
       </c>
       <c r="E6" t="n">
-        <v>0.977</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.972</v>
+        <v>0.929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.96</v>
+        <v>0.916</v>
       </c>
       <c r="H6" t="n">
-        <v>0.951</v>
+        <v>0.891</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="J6" t="n">
-        <v>0.923</v>
+        <v>0.83</v>
       </c>
       <c r="K6" t="n">
-        <v>0.898</v>
+        <v>0.796</v>
       </c>
       <c r="L6" t="n">
-        <v>0.883</v>
+        <v>0.757</v>
       </c>
       <c r="M6" t="n">
-        <v>0.84</v>
+        <v>0.695</v>
       </c>
       <c r="N6" t="n">
-        <v>0.802</v>
+        <v>0.645</v>
       </c>
       <c r="O6" t="n">
-        <v>0.75</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.492</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.622</v>
+        <v>0.417</v>
       </c>
       <c r="R6" t="n">
-        <v>0.537</v>
+        <v>0.332</v>
       </c>
       <c r="S6" t="n">
-        <v>0.475</v>
+        <v>0.218</v>
       </c>
       <c r="T6" t="n">
-        <v>0.364</v>
+        <v>0.131</v>
       </c>
       <c r="U6" t="n">
-        <v>0.284</v>
+        <v>0.078</v>
       </c>
       <c r="V6" t="n">
-        <v>0.31</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="7">
@@ -2599,351 +2063,71 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.98998998998999</v>
+        <v>0.952</v>
       </c>
       <c r="C7" t="n">
-        <v>0.985</v>
+        <v>0.951</v>
       </c>
       <c r="D7" t="n">
-        <v>0.982</v>
+        <v>0.95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.978</v>
+        <v>0.948</v>
       </c>
       <c r="F7" t="n">
-        <v>0.967</v>
+        <v>0.944</v>
       </c>
       <c r="G7" t="n">
-        <v>0.955</v>
+        <v>0.947</v>
       </c>
       <c r="H7" t="n">
-        <v>0.95</v>
+        <v>0.952</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.929</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.917</v>
+        <v>0.926</v>
       </c>
       <c r="L7" t="n">
-        <v>0.897</v>
+        <v>0.916</v>
       </c>
       <c r="M7" t="n">
-        <v>0.872</v>
+        <v>0.899</v>
       </c>
       <c r="N7" t="n">
-        <v>0.843</v>
+        <v>0.873</v>
       </c>
       <c r="O7" t="n">
-        <v>0.804</v>
+        <v>0.857</v>
       </c>
       <c r="P7" t="n">
-        <v>0.768</v>
+        <v>0.835</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.713</v>
+        <v>0.779</v>
       </c>
       <c r="R7" t="n">
-        <v>0.657</v>
+        <v>0.741</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.645</v>
       </c>
       <c r="T7" t="n">
-        <v>0.458</v>
+        <v>0.53</v>
       </c>
       <c r="U7" t="n">
-        <v>0.362</v>
+        <v>0.338</v>
       </c>
       <c r="V7" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>xrai</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.98998998998999</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.989</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.884</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.669</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>guided_gradcam</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.98998998998999</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.927</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.907</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.791</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.658</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>occlusion</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.98998998998999</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.952</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.9419999999999999</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.913</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.887</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.732</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>guided_backprop</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.98998998998999</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.983</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.9370000000000001</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.793</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.697</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.31</v>
+        <v>0.112</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:V11">
+  <conditionalFormatting sqref="B2:V7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/excel_reports/resnet50_vgg16_blur.xlsx
+++ b/results/excel_reports/resnet50_vgg16_blur.xlsx
@@ -1072,7 +1072,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C2" t="n">
         <v>0.775</v>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C3" t="n">
         <v>0.795</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C4" t="n">
         <v>0.803</v>
@@ -1382,7 +1382,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C5" t="n">
         <v>0.799</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C6" t="n">
         <v>0.819</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C7" t="n">
         <v>0.8169999999999999</v>
@@ -1613,7 +1613,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C2" t="n">
         <v>0.9370000000000001</v>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C3" t="n">
         <v>0.9429999999999999</v>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C4" t="n">
         <v>0.945</v>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C5" t="n">
         <v>0.946</v>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C6" t="n">
         <v>0.956</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C7" t="n">
         <v>0.951</v>
